--- a/processed_data.xlsx
+++ b/processed_data.xlsx
@@ -413,71 +413,2234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>货号</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>产品名称</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Unnamed: 3</t>
+          <t>MCE描述</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>TargetMol描述</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>英文背景描述</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>中文背景描述</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>英文短描述</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>中文短描述</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>AI_处理结果</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C8768</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>7783-20-2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ammonium sulfate</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ammonium sulphate,≥99.0%,AR 是一种无机硫酸盐，用于分子生物学研究。Ammonium sulphate,≥99.0%,AR 可用于沉淀蛋白，分离抗体，并能增强抗原-抗体反应。Ammonium sulphate,≥99.0%,AR 可作为植物肥料中的氮源，对淡水螺有发育毒性，但会增加稻田中阿拉伯按蚊和库蚊幼虫的数量。Ammonium sulphate,≥99.0%,AR 会抑制植物中的葡萄糖转化为抗坏血酸。</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3 + 4 = 7.</t>
+          <t>Ammonium sulfate is one of the compounds commonly used in inorganic experiments as an oxidizing agent and bleaching agent.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ammonium sulfate (CAS No.: 7783-20-2) is a high-purity inorganic sulfate salt widely used as a foundational research reagent in molecular biology, protein biochemistry, immunology, plant science, and environmentally oriented toxicology, and it is best categorized as a laboratory-grade inorganic processing agent rather than as a selective bioactive small molecule of defined receptor pharmacology. In bioscience workflows, its functional background is primarily linked to salting-out behavior driven by ionic strength and altered protein hydration, enabling reproducible precipitation, fractionation, and enrichment of proteins and immunoglobulins from complex biological matrices; accordingly, it is commonly applied as an initial step in antibody isolation and broader protein purification pipelines, where it may also improve certain antigen-antibody assay conditions by modulating macromolecular interactions and solution properties. Its biological origin is non-natural in the sense of being an exogenous mineral salt reagent, although both ammonium and sulfate ions intersect with endogenous nitrogen and sulfur metabolism in living systems. Mechanistically, the principal mode of action in experimental systems is physicochemical rather than target-specific: ammonium sulfate changes solvent activity, protein solubility, conformational stability, and intermolecular association, and therefore does not have well-established canonical protein targets or pathway-selective signaling activities comparable to enzyme inhibitors or receptor ligands; instead, the relevant research mechanisms involve protein precipitation, fractionation, macromolecular stabilization or destabilization depending on concentration, and modulation of nitrogen or sulfur availability in plant and microbial culture-related contexts. In plant-focused studies, ammonium sulfate has been used as a nitrogen-source reagent and has been associated with perturbation of metabolic processes, including inhibition of glucose conversion to ascorbate under certain experimental conditions, whereas in aquatic and ecological models ammonium-derived exposures have been linked to developmental or population-level effects in sensitive invertebrate systems, supporting its utility in environmental response studies rather than target-based pharmacology. Because this compound is not typically characterized by direct potency metrics such as IC50, EC50, or MIC against a defined molecular target, specific in vitro activity levels are generally unavailable, and activity is more appropriately described as concentration-dependent matrix modulation occurring from low salt supplementation conditions to high ionic strength precipitation regimes, with experimentally effective levels commonly spanning millimolar to near-saturation ranges depending on the protein system, buffer composition, and assay objective. Typical applications include protein or antibody fractionation from serum, ascites, cell culture supernatants, or lysates; preparative enrichment prior to chromatography; optimization of immunochemical workflows; plant nutrient-stress or metabolic studies; and aquatic ecotoxicology models, while use in cell-based assays or animal studies is usually indirect and designed around exposure chemistry, nutrient balance, or biomacromolecule processing, and the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. This product description is intended exclusively for laboratory research use in biomedical investigation and drug discovery support activities such as sample preparation, assay development, reagent optimization, and mechanistic biology studies, and it should not be interpreted as indicating any human therapeutic, clinical, nutritional, or other non-research application.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Ammonium sulfate (CAS No.: 7783-20-2) 属于无机硫酸盐类高离子强度研究试剂，在生命科学领域主要作为蛋白质与大分子分离过程中的经典盐析介质和缓冲体系调节成分使用，其研究背景主要集中于分子生物学、蛋白质化学、生物分离工程、免疫学样品制备以及植物与生态毒理相关模型研究。现有资料显示，该物质并非以特异性受体结合为特征的“小分子靶向调节剂”，因此通常不存在已被广泛确立的单一药理靶点；其核心生物学作用机制主要依赖升高体系离子强度、改变水化层稳定性与蛋白表面溶剂化状态，从而通过“盐析”效应调控蛋白、抗体及部分核酸相关复合物的溶解度、聚集行为与分级沉淀过程，并可作为抗体纯化的前处理步骤或与后续层析分离联用，以提高样品富集效率和工艺可重复性。基于这一非特异性的物理化学作用模式，Ammonium sulfate 的体外活性通常不宜按经典受体或酶抑制剂方式定义，若置于实验筛选语境，其有效作用范围多表现为毫摩尔至高毫摩尔水平，具体浓度通常取决于目标蛋白的表面性质、样品复杂度、温度、pH 与饱和度设定，而非固定的低剂量活性窗口。除生物分离用途外，已有研究与资料还提示其可影响免疫反应体系中的抗原-抗体相互作用强度，并在植物与农业生态研究中作为外源氮源和硫源相关变量，用于分析营养胁迫、代谢重编程及环境暴露效应；在植物系统中，硫酸盐同化与还原过程通常与ATP sulfurylase、APS reductase 及后续含硫代谢网络相关，而铵态氮输入则可进一步影响碳氮平衡和抗坏血酸等代谢物生成，因此该化合物更适合作为研究离子环境、营养信号和代谢耦联效应的背景干预因子，而非特定信号通路的直接选择性探针。公开研究还表明，铵态氮富集或硫酸铵施用可在某些稻田或湿地模型中改变蚊幼虫种群丰度，并在部分淡水无脊椎动物相关研究语境下提示出发育或生态毒理学关注点，因此其在环境生物学和农田生态学中也常被纳入暴露因子评估框架。总体而言，Ammonium sulfate 在生物医学研究与药物研发支持环节中的价值主要体现在样品前处理、蛋白富集、抗体分离、工艺开发、细胞裂解产物分级和方法学优化等基础研究场景中，也可用于细胞模型外的生化体系构建、动物来源组织提取物纯化以及早期筛选流程中的制备与分离步骤；实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的，尤其需要结合目标分子的理化性质、体系盐耐受性以及下游检测平台的兼容性进行优化。 ([thermofisher.com](https://www.thermofisher.com/io/en/home/life-science/antibodies/antibodies-learning-center/antibodies-resource-library/antibody-methods/antibody-purification-methods.html?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ammonium sulfate is a laboratory-grade inorganic sulfate salt used for protein precipitation and fractionation in molecular biology, protein biochemistry, immunology, and plant research.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>一种用于科研中蛋白盐析分离与抗体纯化前处理的高离子强度试剂。</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ammonium sulfate (CAS No.: 7783-20-2) 是一种高纯度无机硫酸盐，通常作为基础研究级盐类试剂应用于生物医学研究、分子生物学方法学开发以及药物研发相关的样品制备流程中，其物质属性决定了其主要发挥理化调控而非特异性受体配体式生物学作用，因此并不对应明确的经典药理靶点或单一信号通路，而是主要通过调节溶液离子强度、渗透环境、蛋白质表面水化层与溶解度平衡，诱导蛋白质发生可控的盐析沉淀，从而广泛用于蛋白分级纯化、抗体富集、酶制剂浓缩及复杂生物样本中目标组分的初步分离；在免疫学生化研究中，其对抗原抗体体系的影响通常与蛋白构象稳定性及介质条件变化有关，可作为优化免疫沉淀、免疫分离和蛋白互作分析体系的重要辅助试剂。在生命科学研究目录语境下，该化合物可归类为无机盐类实验试剂、蛋白分离辅料及生物样本处理用基础材料，常见于蛋白组学前处理、细胞裂解后上清分级、重组蛋白纯化流程优化、天然产物活性成分分段富集以及生物分析方法建立等研究场景。现有公开信息显示，其生物学效应更多体现为对实验体系和生态暴露条件的非特异性影响，例如在植物研究中可作为氮源相关因素参与代谢调节，并可能影响抗坏血酸相关代谢过程；在环境与毒理学模型中，亦有报道提示其对部分水生无脊椎动物发育过程及特定蚊虫幼体种群动态具有影响，因此在设计细胞实验、模式生物实验或高通量筛选前处理流程时，通常需要结合培养体系成分、样本类型、终点指标和暴露时间对背景离子效应进行充分控制。由于该物质并非以经典意义上的酶抑制剂、受体激动剂或通路调节剂被开发，其体外活性不宜以标准靶向药理强度进行定义，若涉及相关实验读出，通常表现为毫摩尔级或更高条件下的体系效应，而非纳摩尔至微摩尔范围内的高特异性活性；因此在药物研发背景下，它更适合作为生物大分子分离纯化、制剂前研究、分析开发和候选分子表征中的工艺性研究工具，而不是作为机制导向型活性分子进行评价。其在细胞模型、组织来源样本及动物来源生物材料研究中的典型用途主要集中于样本预处理、蛋白回收、抗体分离和方法学验证，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的，并需通过预实验评估其对目标蛋白稳定性、下游检测灵敏度及背景干扰水平的影响，以确保所得数据具有可重复性、可解释性和良好的研发转化参考价值。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C8769</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>110-27-0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Isopropyl myristate</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Isopropyl myristate (IPM) 是异丙醇和肉豆蔻酸的酯。Isopropyl myristate 用于一些化合物的透皮递送。Isopropyl myristate 是一种极性润肤剂，用于化妆品和外用活性分子制剂中。</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1 + 2 = 3.</t>
+          <t>Isopropyl myristate (IPM) is the isopropyl alcohol and myristic acid ester.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Isopropyl myristate (CAS No.: 110-27-0) is a fatty acid ester formed from isopropyl alcohol and myristic acid and is generally classified in biomedical research as a formulation excipient, lipid-based solvent, and membrane permeation enhancer rather than as a direct bioactive modulator of a defined protein target. This compound is associated with lipid-like constituents that are broadly related to naturally occurring fatty acid frameworks, and its primary functional background in research derives from its ability to modify physicochemical partitioning, improve spreading behavior in topical and interface-focused systems, and influence barrier transport across lipid-rich biological matrices. In drug discovery and experimental formulation science, isopropyl myristate is therefore most appropriately categorized within delivery-enabling materials used to support compound solubilization, dispersion, and penetration studies, particularly in models designed to examine transmembrane or transepidermal flux. Current reference information indicates no well-established canonical receptor, enzyme, or intracellular signaling pathway directly engaged by isopropyl myristate as a selective ligand; instead, its predominant mechanism is understood to be biophysical, involving interaction with lipid domains and alteration of membrane or barrier organization, thereby enhancing diffusion and partitioning of co-formulated molecules. Because it is not primarily developed as a target-directed pharmacological probe, specific in vitro potency metrics such as IC50, EC50, or MIC values are generally not reported in standard sources for this substance, and where biological effects are evaluated they are usually interpreted in the context of formulation performance, membrane permeability, or excipient tolerance rather than target inhibition. Accordingly, in vitro and ex vivo applications commonly include use in permeability assays, topical or transdermal screening platforms, emulsion and microemulsion development, and vehicle optimization studies in cell-associated barrier models or tissue-based systems, while in vivo use may occur in formulation-focused animal studies assessing delivery behavior of co-administered research compounds; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. Overall, isopropyl myristate is best described for catalog purposes as a research-grade ester excipient with utility in pharmaceutical sciences, biomaterials, and drug delivery investigations where modulation of formulation properties and barrier permeation is the principal experimental objective, while any direct target-based biological activity remains insufficiently defined in the currently available literature.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Isopropyl myristate (CAS No.: 110-27-0) 是一种脂肪酸酯类研究化合物，通常归类为中性疏水性辅料与皮肤屏障研究中常用的化学渗透促进剂，由异丙醇与肉豆蔻酸形成酯键而成，并可见于部分天然来源样品与生物体系的代谢物记录中；在生物医学研究与药物研发语境下，其核心价值主要不在于作为经典受体配体或酶抑制剂，而在于作为制剂学与递送科学中的功能性组分，用于考察化合物在屏障组织中的分配、扩散与局部滞留行为。现有资料表明，该分子尚无被广泛确认的特异性分子靶点或标准意义上的信号通路调控谱，其生物学作用机制主要体现为对脂质环境的物理化学调节，包括插入角质层细胞间脂质区域、改变脂质层有序度与流动性、影响极性头基周围微环境，并提高研究分子由制剂向屏障组织转移的分配倾向，因此常被视为通过屏障脂质重排与分配增强机制发挥作用的非特异性递送辅助因子，而非直接的靶向活性分子。基于这一本质，其体外研究通常并不以经典“抑制活性”或“激动活性”来表征；若从制剂筛选与屏障相互作用研究的角度概括，其有效作用多表现于配方相关的浓度依赖区间，常见于低百分比至中等百分比组成范围内对渗透行为产生可检测影响，而非以纳摩尔至微摩尔水平的受体占有或酶活改变来定义。该分子因而广泛应用于细胞屏障模型、离体皮肤或重建组织模型、动物皮肤暴露模型以及候选分子的早期处方筛选中，用于评估溶解性改善、组织分配、膜通透变化、局部暴露一致性与辅料相容性，并常与其他溶剂、表面活性组分或脂质材料联合考察协同效应；在具体实验实施中，所采用的浓度或剂量通常取决于研究目标、模型类型、待测分子的理化性质以及终点读数设计。对于生命科学研究目录而言，可将其概括为一种以屏障递送研究、外用制剂开发、药物筛选支持和生物界面物理化学表征为主要应用方向的脂肪酸酯类功能分子，尤其适用于围绕屏障脂质组织、被动扩散过程、配方优化和递送机制解析开展的基础与转化前研究。 ([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Isopropyl-Myristate?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Isopropyl myristate is a fatty acid ester excipient with no defined canonical molecular target, utilized in drug delivery, permeability, and formulation research.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>一种用于屏障递送与外用制剂研究的脂肪酸酯类辅料。</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Isopropyl myristate (CAS No.: 110-27-0) 是一种脂肪酸异丙酯类化合物，属于常用于药剂学、生物材料界面研究与制剂科学中的疏水性酯类辅料，可视为肉豆蔻酸与异丙醇形成的酯化产物；其来源背景与天然脂质相关，因而常被归入脂质模拟性载体、润肤性赋形剂与渗透促进研究材料范畴。在生命科学研究中，该分子本身通常不被视为经典意义上具有明确单一受体靶点的小分子调节剂，而主要通过影响脂质相行为、改变角质层或类膜屏障的微观有序性、提高配方中疏水性成分的分配与扩散能力而发挥作用，因此其“机制”更多体现为对生物屏障物理化学性质的调节，而非特异性信号通路激活或抑制；现有研究语境下，其相关作用常涉及膜脂流动性改变、脂质层重排、屏障通透性提升以及作为载体改善活性分子在局部体系中的分散与递送表现。基于这一属性，Isopropyl myristate 在生物医学研究与药物研发中常用于经皮递送体系、外用制剂筛选、皮肤屏障模型评价、处方前研究以及细胞暴露体系中的辅料相容性考察，尤其适用于研究候选分子在脂质环境中的溶解、释放和跨屏障转运行为；在体外研究中，其相关效应通常并非以明确的纳摩尔级受体活性来表征，而更常表现为配方依赖性的功能性影响，实验观察范围多为低百分比至较高配比条件下对屏障通量、膜完整性或载药体系稳定性的改变，因此若对应“体外活性”进行概括，更适宜表述为缺乏统一的受体药理学活性分级，现有数据主要体现为制剂和屏障调控层面的浓度依赖性效应。该化合物的主要研究领域包括透过性增强剂筛选、脂质基递送系统构建、局部暴露模型开发、化妆品科学相关的生物界面研究，以及作为对照辅料用于评估其他活性分子在体外皮肤、重建屏障模型或动物皮肤模型中的转运特征；在细胞模型、离体组织模型和动物模型中，其使用浓度或剂量通常取决于具体实验设计、待载分子的理化性质以及终点检测指标。总体而言，Isopropyl myristate 更适合作为一种研究用制剂辅料和屏障调节材料来理解脂质环境对分子递送与界面行为的影响，而非作为具有已确立分子靶点的直接生物活性研究对象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C8770</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>93-60-7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Methyl nicotinate</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Methyl nicotinate (Nicotinic acid methyl ester) 是一种具有口服活性的血管舒张剂。Methyl nicotinate 具有镇痛活性。Methyl nicotinate 局部应用于皮肤时，会引起局部皮肤红斑。Methyl nicotinate 在非处方局部制剂中用作一种活性成分，用于肌肉和关节疼痛的研究。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Methyl nicotinate (methyl pyridine-3-carboxylate) is the methyl ester of that is used as an active ingredient as a rubefacient in over-the-counter topical preparations indicated for muscle and joint pain. The action of methyl nicotinate as a rubefacient is thought to involve peripheral vasodilation.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Methyl nicotinate (CAS No.: 93-60-7) is a small-molecule nicotinate ester and niacin-derived research compound that is primarily categorized as a peripheral vasodilatory and rubefacient probe for biomedical investigation of cutaneous microcirculation, neurovascular regulation, and barrier-associated pharmacology. As the methyl ester of nicotinic acid, it is generally regarded in research settings as a synthetic derivative rather than a naturally occurring biomacromolecule, and its experimental relevance derives from rapid skin penetration, local ester hydrolysis to nicotinic acid, and reproducible induction of transient erythema and increased superficial blood flow. Available evidence indicates that its biological effects are mediated predominantly through local vasodilatory mechanisms involving prostaglandin-dependent signaling, participation of local sensory nerves, and contribution of nitric oxide-associated endothelial responses, although a single definitive molecular target has not been firmly established; accordingly, it is most appropriately described as a functional pharmacological stimulus for microvascular response studies rather than a highly selective receptor ligand. Quantitative potency values such as standardized IC50 or EC50 measurements are not well defined in the literature for this compound in conventional target-based in vitro assay systems, and published work more commonly evaluates concentration-dependent vascular or erythematous responses in skin-based experimental models, with activity generally discussed over formulation- and exposure-dependent ranges rather than as a fixed biochemical inhibition constant. In life sciences research, Methyl nicotinate is therefore commonly used in skin perfusion assays, vascular reactivity experiments, transdermal delivery studies, barrier function assessments, and methodology development for noninvasive imaging or pharmacodynamic readouts, while related applications in animal or ex vivo tissue models may examine local hemodynamic changes, inflammatory mediator involvement, or comparative responses among nicotinate esters. The concentrations or doses used in experiments typically depend on specific experimental designs and research objectives, and study interpretation should account for tissue context, route of administration, esterase-dependent metabolism, and the fact that observed effects primarily reflect localized pharmacological perturbation of cutaneous vascular signaling rather than target-selective modulation intended for non-research use.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Methyl nicotinate (CAS No.: 93-60-7) 是烟酸衍生物中的小分子酯类化合物，通常被归入烟酸酯及外周血管反应研究工具分子范畴，广泛用于生物医学研究中对皮肤微循环、局部血流动力学变化、神经血管耦联以及刺激性反应过程的实验评估；现有资料表明，该分子可作为一种诱发局部红斑和灌注升高的药理学探针，其作用基础主要与外周血管舒张有关，并被认为涉及前列腺素相关信号、内皮来源一氧化氮释放以及神经源性调节等多因素机制，但其精确分子靶点尚未完全明确，因而更适合表述为具有明确表型输出而靶点机制仍在解析中的研究化合物。基于公开数据库与实验研究，该化合物在经皮或局部暴露条件下能够稳定诱导可测量的皮肤血流增加与短暂性红斑反应，因此常被用于构建微血管反应模型、评价皮肤屏障通透性、分析药物递送后的局部药效学读出，以及在炎症相关或感觉神经相关实验体系中作为阳性刺激物进行方法学验证；在体外层面，关于其直接受体结合或经典酶抑制的定量数据相对有限，现阶段更适宜概括为其活性多表现于低微摩尔至更高浓度暴露下所触发的细胞与组织功能反应，而非已被充分确证的高选择性单靶点作用。作为烟酸骨架的酯化衍生物，Methyl nicotinate 亦常被用于比较不同烟酸酯在渗透性、局部刺激性和微循环反应动力学方面的差异，在细胞模型中可用于观察血管相关信号转导、炎症介质释放或屏障应答，在动物模型中则常用于评估局部血管扩张、血管通透性变化及感觉神经参与的反应过程；具体实验中所采用的浓度、给药方式与暴露时程通常取决于研究目的、模型类型以及终点检测方法，需要结合实验设计进行优化。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Methyl-Nicotinate?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Methyl nicotinate is a nicotinic acid ester vasodilatory probe that modulates prostaglandin-, sensory nerve-, and nitric oxide-associated cutaneous microvascular responses in skin perfusion research.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>一种用于皮肤微循环与局部血流反应研究的小分子探针。</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Methyl nicotinate (CAS No.: 93-60-7) 是烟酸酯类小分子、亦可归类为烟酸的甲酯衍生物，在生物医学研究中通常被用作诱导局部血管反应和皮肤微循环变化的化学探针，主要服务于皮肤药理学、屏障功能评价、经皮递送研究、微血管反应性分析以及炎症相关表型观察等方向。现有研究普遍认为，该分子在局部暴露后能够迅速引发可重复的皮肤红斑和血流增加，其作用基础与外周微血管扩张及局部介质释放有关，机制上多被归因于皮肤组织中前列腺素相关信号的参与，并可能与经皮吸收后在局部细胞与血管单元内触发的旁分泌调节过程相关；不过，其直接分子靶点仍未被完全统一界定，因此更适合表述为一种以局部血管舒张和微循环激活为主要读出特征的研究工具化合物，而非特异性单靶点配体。基于已发表的皮肤血流和红斑动力学研究，Methyl nicotinate 常被用于建立可量化的刺激模型，以评估皮肤通透性、局部反应敏感性、制剂释放行为及屏障损伤后的反应差异，在细胞与组织层面可用于观察血管活性介质释放、炎症相关应答和皮肤微环境变化，在动物或替代模型中则可作为局部刺激物辅助分析微血管灌注、组织反应时间程及候选制剂的药效学表征。关于体外活性，目前公开资料更集中于组织和皮肤层面的功能读出，而非标准化受体筛选数据，因此其活性通常宜概括为微摩尔范围内可产生可检测生物学效应，且具体浓度、暴露时间与信号强度会显著受到溶剂体系、皮肤屏障状态、给药部位及实验终点选择的影响。总体而言，该分子在生命科学研究目录中可被定义为一种用于微循环药理学、经皮吸收评价和局部刺激反应建模的经典烟酸酯类研究分子，具有明确的实验可操作性和表型可读性，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C8771</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>42540-40-9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cefamandole nafate</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cefamandole nafate (Cefamandole formate sodium) 是第二代广谱头孢菌素抗生素。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cefamandole nafate (Cephamandole nafate) is a second-generation broad-spectrum cephalosporin antibiotic.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cefamandole nafate (CAS No.: 42540-40-9) is a second-generation broad-spectrum cephalosporin antibiotic and a β-lactam antibacterial research compound commonly used as a laboratory tool for studying bacterial cell wall biogenesis, β-lactam susceptibility, and resistance mechanisms in microbiology, biomedical research, and anti-infective drug discovery; as the nafate form, it functions as a precursor of cefamandole and is generally categorized within small-molecule antibacterial agents of semisynthetic cephalosporin origin. Its primary biological mechanism is consistent with the cephalosporin class, involving interaction with bacterial penicillin-binding proteins and consequent inhibition of the terminal stages of peptidoglycan crosslinking during cell wall synthesis, which leads to loss of cell wall integrity and bacterial killing, while experimental response can also be modulated by β-lactamase activity, altered penicillin-binding proteins, and permeability-related resistance determinants. Direct target-specific quantitative profiling for this exact form is not consistently reported in modern screening sources, and therefore its activity is most appropriately described on the basis of the released active cephalosporin scaffold and class-associated antibacterial behavior, with reported in vitro potency in susceptible bacterial systems generally discussed in the low micromolar to higher micromolar exposure context or by minimum inhibitory concentration paradigms rather than enzyme IC50 measurements. In research settings, Cefamandole nafate is used to support studies of Gram-positive and Gram-negative bacterial susceptibility, comparative profiling of β-lactam compounds, resistance phenotyping, microbiological assay development, and benchmark evaluation in antibacterial screening cascades, and it may also be incorporated into cell-associated infection models or preclinical animal infection studies where the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cefamandole nafate (CAS No.: 42540-40-9) 是头孢菌素类β-内酰胺抗菌分子的研究级形式，通常归类为第二代广谱头孢菌素相关化合物，并可视为 cefamandole 的前体或可转化形式；其研究背景主要来源于微生物学、细菌细胞壁生物合成研究以及抗菌药物发现领域，常被用作评估革兰阳性菌与部分革兰阴性菌对头孢菌素类分子敏感性、耐药表型与结构活性关系的参照分子。现有资料表明，此类化合物的核心生物学作用机制与典型β-内酰胺抗菌剂一致，主要靶向细菌青霉素结合蛋白家族，抑制肽聚糖交联相关转肽过程，从而干扰细胞壁装配并诱导细菌形态学改变及生长抑制；其作用过程与细胞壁应激反应、细胞分裂失衡以及在部分菌株中由β-内酰胺酶产生或靶蛋白改变所介导的耐受/耐药机制密切相关。公开研究还提示，cefamandole nafate 与其活性相关形式在常规体外抗菌评价中的表现总体接近，因此在体外实验中通常表现为低微摩尔至较高微摩尔范围的活性水平，但具体效力高度依赖于受试菌种、接种量、培养基条件及耐药背景。基于上述特征，该分子常用于细菌培养体系中的最小抑菌浓度测定、药敏谱比较、青霉素结合蛋白相关机制研究、耐药机制解析以及新型抗菌分子筛选中的阳性对照或结构参照，也可在动物感染模型或药效学探索中作为同类化合物比较对象；实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。 ([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Cefamandole-Nafate?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Cefamandole nafate is a second-generation cephalosporin β-lactam antibacterial that targets penicillin-binding proteins and is utilized in microbiology, resistance, and anti-infective research.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>一种用于细菌细胞壁合成与β-内酰胺敏感性研究的头孢菌素类分子。</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Cefamandole nafate (CAS No.: 42540-40-9) 是一种用于生物医学研究的第二代半合成头孢菌素类前药，属于β-内酰胺抗菌化合物范畴，其在水相或生物体系中可转化为活性形式头孢孟多，因此常被归入细菌细胞壁生物合成研究、抗菌药理学研究以及抗感染药物发现相关目录。该分子并非来源于天然初级代谢产物本体，而是基于头孢菌素骨架经半合成修饰获得，因而在研究上具有典型的结构优化与前药设计意义。其已知核心作用靶点为细菌青霉素结合蛋白家族，主要通过与相关转肽酶活性位点结合并使其失活，进而抑制肽聚糖交联过程，扰乱细胞壁完整性与力学稳定性，最终导致细菌细胞裂解；从机制上看，该过程主要涉及细胞壁合成通路而非真核细胞经典信号转导轴，因此常被用作研究细菌增殖控制、细胞包膜稳态及β-内酰胺类敏感性差异的工具化合物。现有资料表明，头孢孟多相关体外抗菌活性通常表现于纳摩尔至微摩尔范围至低微摩尔水平，具体活性强弱受菌种类别、青霉素结合蛋白谱、外膜通透性以及β-内酰胺酶介导的耐受机制显著影响，因此在研究中更适合作为广谱头孢菌素代表分子，用于革兰阳性菌与部分革兰阴性菌模型中的药效比较、耐药表型解析和联合筛选体系构建。由于其前药属性及在溶液中的转化特征，该化合物亦适用于开展稳定性评价、制剂条件优化、活性释放过程监测以及与同类β-内酰胺化合物的构效关系分析。在应用层面，Cefamandole nafate 常见于细菌培养体系、细胞共培养中的抗菌干预实验、动物感染模型中的机制验证，以及新型抗菌分子或增敏策略的对照筛选研究；实验中所使用的浓度或剂量通常取决于具体的实验设计、目标微生物背景、给药路径以及研究目的。在缺乏统一靶点动力学或特定细胞通路深度数据的情况下，围绕该化合物的研究价值主要体现为其作为经典第二代头孢菌素前药模型，在细胞壁合成阻断、耐药机制识别、药物敏感性评价及抗菌药筛选平台开发中的方法学参考意义。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C8772</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>874819-74-6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Toceranib phosphate</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Toceranib phosphate (SU11654 phosphate) 是一种具有口服活性的酪氨酸激酶 (RTK) 受体抑制剂，能有效抑制 PDGFR ， VEGFR ， Kit ，抑制 PDGFRβ 和 Flk-1/KDR 的 K i 值分别为 5 nM 和 6 nM。Toceranib phosphate 具有抗肿瘤和抗血管生成活性，可用于犬肥大细胞肿瘤的研究。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Toceranib Phosphate (SU11654 phosphate), is a selective inhibitor of the tyrosine kinase activity of several members of the split kinase RTK family, including Flk-1/KDR, PDGFR</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Toceranib phosphate (CAS No.: 874819-74-6) is a small-molecule, multitarget receptor tyrosine kinase inhibitor widely categorized within kinase-focused research reagents for oncology, angiogenesis, and signal-transduction studies, and it is commonly described as the phosphate salt of toceranib developed for experimental modulation of split-kinase receptor tyrosine kinase networks. Its principal biological targets include platelet-derived growth factor receptor family members, vascular endothelial growth factor receptor signaling components such as Flk-1/KDR, and Kit, thereby positioning this compound as a useful probe for interrogation of RTK-dependent proliferation, survival, stromal signaling, and angiogenic responses in biomedical research settings. Available reference data indicate potent target engagement in the nanomolar range, including reported inhibition constants for PDGFRβ and Flk-1/KDR in the low-nanomolar interval, supporting its use as a high-affinity inhibitor for mechanistic studies of PDGFR-, VEGFR-, and Kit-associated signaling cascades, including downstream MAPK/ERK and PI3K/Akt pathway regulation. In vitro, Toceranib phosphate is typically employed to evaluate kinase dependency, pathway suppression, cell growth regulation, and vascular biology phenotypes across transformed cell systems and other target-expressing cellular models, while in vivo it is used in animal research to investigate tumor microenvironment modulation, neovascularization-related processes, and pharmacology of multitarget RTK inhibition; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. Overall, this compound is most appropriately positioned as a research tool for target-validation studies, comparative inhibitor profiling, biomarker discovery, resistance-mechanism analysis, and drug-screening workflows in preclinical life sciences research, and any use should remain strictly limited to laboratory investigation rather than human consumption, clinical application, or other non-research purposes.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Toceranib phosphate (CAS No.: 874819-74-6) 是一种小分子受体酪氨酸激酶抑制剂，属于多靶点信号调控研究分子，主要用于肿瘤生物学、血管生成调控以及异常增殖相关信号网络的基础研究与药物发现研究；该分子在机制上主要作用于多种III型或相关受体酪氨酸激酶家族成员，包括 PDGFR、VEGFR 及 Kit 等靶点，通过干预受体磷酸化及其下游增殖、生存与血管生成相关信号转导过程，影响细胞增殖、迁移、微环境重塑及新生血管形成等生物学事件，因此常被用于解析受体酪氨酸激酶驱动的信号依赖性表型、评估靶点抑制后的细胞反应，以及建立肿瘤相关通路的药理学研究框架；从体外活性特征来看，其作用水平总体可概括为纳摩尔至低微摩尔范围，适合用于受体激酶通路抑制、通路选择性比较、联合干预策略探索及候选分子筛选中的对照或工具化合物研究；在实验应用中，Toceranib phosphate 常见于激酶活性分析、细胞增殖与迁移实验、血管生成相关模型、肿瘤细胞与基质细胞互作研究以及动物水平的药效学探索，用于考察靶点依赖性、生物标志物变化和通路反馈调节现象，而具体实验中所采用的浓度或剂量通常需依据模型类型、给药方式、暴露时间及研究目的进行审慎优化；总体而言，该分子适合作为研究受体酪氨酸激酶介导信号转导、肿瘤相关血管生成过程及多靶点抑制策略的重要工具分子。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Toceranib phosphate is a multitarget receptor tyrosine kinase inhibitor targeting PDGFR, VEGFR, and Kit, utilized in oncology, angiogenesis, and signal-transduction research.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>一种多靶点受体酪氨酸激酶抑制剂，用于肿瘤与血管生成机制研究。</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Toceranib phosphate (CAS No.: 874819-74-6) 是一种小分子受体酪氨酸激酶抑制剂，通常归类为多靶点信号调控研究工具，广泛用于肿瘤生物学、血管生成调控及相关信号网络解析等生命科学研究领域。该分子为托塞拉尼的磷酸盐形式，主要针对多种分裂激酶型受体酪氨酸激酶家族成员发挥抑制作用，已知涉及的研究靶点包括血小板源生长因子受体、血管内皮生长因子受体以及 Kit 等与细胞增殖、迁移、存活和微环境重塑密切相关的关键信号节点，因此常被用于探究受体酪氨酸激酶异常激活所驱动的下游级联通路变化，如与增殖调控、血管生成反应和肿瘤相关基质互作有关的信号过程。在体外研究中，Toceranib phosphate 对相关激酶靶标通常表现出纳摩尔至低微摩尔范围的活性水平，适合用于评估靶点依赖性表型、比较不同细胞系统中的信号敏感性，以及建立抑制剂响应模型。在应用层面，该分子常见于肿瘤细胞、内皮样细胞或携带特定激酶异常背景的细胞模型研究，也可用于动物模型中的药理机制探索、候选分子筛选及联合用药策略的前期研究；实验中所使用的浓度或剂量通常取决于具体的实验设计、暴露时间、模型类型及研究目的。总体而言，Toceranib phosphate 适合作为解析受体酪氨酸激酶介导信号转导、肿瘤相关血管生成过程及靶向抑制效应的重要研究分子，在生物医学基础研究和药物发现早期评价中具有较高的工具价值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C8773</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>54-35-3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Procaine penicillin G</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Procaine benzylpenicillin (Penicillin G procaine) 是一种抗菌剂。Procaine benzylpenicillin 对革兰氏阳性菌的有抑制活性，并与新霉素 Neomycin ( HY-B0470 ) 有协同活性。Procaine benzylpenicillin 可用于畜牧业中牛乳腺炎的研究。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Procaine penicillin G (Duphapen) (procaine benzylpenicillin) is an antibiotic useful for the treatment of a number of bacterial infections. Specifically, it is used for syphilis, anthrax, mouth infections, pneumonia, diphtheria, cellulitis, and animal bites.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Procaine penicillin G (CAS No.: 54-35-3) is a beta-lactam antibacterial agent classified as the procaine salt of benzylpenicillin and is primarily used in biomedical research as a reference small molecule for studying bacterial cell-wall biosynthesis, antimicrobial susceptibility, and formulation-dependent antibacterial performance in preclinical discovery settings. Functionally, its activity derives from the benzylpenicillin moiety, which engages penicillin-binding proteins involved in peptidoglycan crosslinking and thereby disrupts bacterial cell-wall assembly, a mechanism associated with inhibition of transpeptidation pathways and loss of cell-wall integrity in susceptible organisms, particularly Gram-positive bacteria; available research descriptions also indicate inhibitory activity against Gram-positive strains and potential synergistic effects when combined with aminoglycosides such as neomycin in experimental antimicrobial studies. Publicly summarized source information for this compound does not consistently report standardized target-resolved biochemical constants or unified potency values for this specific salt form, and therefore its in vitro activity is more appropriately described in qualitative terms or, where assessed across susceptible bacterial systems, as occurring broadly within concentration ranges commonly associated with established beta-lactam antibacterial testing, rather than by assigning unsupported single-value MIC, IC50, or EC50 claims. In research workflows, Procaine penicillin G is commonly positioned within anti-infective screening cascades, comparator studies of beta-lactam class compounds, investigations of bacterial growth inhibition and resistance phenotypes, and veterinary-oriented experimental infection models, including studies relevant to livestock pathogens, while use in cell-based or animal-based protocols should be defined by organism susceptibility, formulation properties, and study endpoints, since the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Procaine penicillin G (CAS No.: 54-35-3) 属于青霉素类β-内酰胺抗菌研究分子，通常被视为苄青霉素的普鲁卡因盐形式，在生命科学领域主要作为研究细菌细胞壁生物合成、药物敏感性分层以及抗菌药效学行为的经典工具化合物；其活性部分来源于天然青霉素骨架所代表的抗菌作用特征，而相关研究背景多聚焦于革兰氏阳性菌易感菌株、细菌性炎症相关动物感染模型以及兽医学与感染生物学中的病原控制研究。现有资料表明，该分子的主要作用机制与细菌青霉素结合蛋白介导的肽聚糖交联过程受阻有关，可抑制转肽反应并干扰细胞壁完整性维持，进而影响细菌增殖与存活；因此，其核心研究靶点通常归属于青霉素结合蛋白及细胞壁合成相关通路，同时耐受或耐药现象常与靶点亲和力改变、β-内酰胺酶介导的失活以及细胞包膜通透性或自溶调控变化相关。就体外活性而言，基于苄青霉素类化合物对敏感革兰氏阳性菌的既有研究，可将其有效活性大体概括为低微摩尔至亚微克每毫升级别范围，对不同葡萄球菌和链球菌分离株的抑制强度会随菌种、接种量、培养条件及耐药表型而变化；在联合研究中，其与氨基糖苷类化合物如新霉素的组合也被用于考察协同或增敏效应。该分子常用于细胞外细菌培养体系中的药敏评价、最小抑菌浓度测定、时间杀菌曲线分析、耐药机制研究以及奶牛乳腺炎等动物感染模型中的药效观察，也可作为抗菌药筛选中的阳性对照或参比分子，用于比较新型细胞壁抑制剂与联合用药策略的研究表现；实验中所使用的浓度或剂量通常取决于具体的实验设计、给药途径、目标菌株特征以及研究目的。在生物医学与药物研发语境下，Procaine penicillin G 尤其适合纳入围绕细菌细胞壁装配、病原体易感性谱、抗菌联合策略、药代暴露与组织分布关系以及感染模型转化评价的研究目录中，作为表征经典β-内酰胺药理学与构建抗感染筛选基准体系的重要参考分子。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Procaine penicillin G is a beta-lactam antibacterial that targets penicillin-binding protein-mediated peptidoglycan crosslinking and is used in antimicrobial and bacterial cell-wall biosynthesis research.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>一种用于细菌细胞壁合成与药敏机制研究的青霉素类分子。</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Procaine penicillin G (CAS No.: 54-35-3) 是苄青霉素的长效普鲁卡因盐形式，通常归类为对β-内酰胺酶敏感的窄谱青霉素类抗菌研究分子，在生命科学研究中主要作为经典细胞壁生物合成抑制剂用于细菌学、药理学、耐药机制与兽医相关感染模型研究。该分子本质上来源于天然青霉素骨架衍生的制剂化形式，其核心生物学作用依赖于与细菌青霉素结合蛋白相互作用，进而干扰肽聚糖交联过程、抑制细胞壁装配并诱导对活跃分裂细菌的抑菌或杀菌效应；其作用通路主要涉及细胞壁应激反应、形态维持失衡以及渗透稳定性破坏，且对革兰氏阳性菌相关体系更常表现出明确活性。基于既有药理与微生物学资料，Procaine penicillin G 在体外实验中的活性通常可概括为低微摩尔至更高浓度依赖范围，实际效应受菌种、接种量、培养基条件、产酶状态及药物暴露时间影响显著；对于青霉素敏感菌株，其研究价值主要体现在药敏分层、耐药表型比较以及与其他抗菌剂联用评价中，已有资料提示其在特定革兰氏阳性菌背景下与新霉素联用可呈现增强效应。该化合物在应用层面常见于细胞与微生物培养模型、抗菌药效筛选、细菌细胞壁生物学研究、药代暴露相关实验以及家畜感染特别是奶牛乳腺炎等兽医研究场景，也可作为对照分子用于评估β-内酰胺敏感性、产β-内酰胺酶相关耐受现象及给药制剂对暴露持续性的影响。由于公开研究对其不同实验体系下的定量参数并不完全统一，实验中所使用的浓度或剂量通常取决于具体模型、目标菌株、终点指标与研究目的，因此在药物发现与转化前研究目录中，Procaine penicillin G 更适合作为经典抗菌机制参照物、窄谱抗菌筛选工具分子以及兽医感染与联合用药策略研究中的基础研究材料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C8774</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>74764-40-2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bepridil hydrochloride hydrate</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bepridil hydrochloride hydrate ((±)-Bepridil hydrochloride hydrate) 是非选择性的，长效的钙离子通道 ( Ca + channel ) 拮抗剂，钠离子、钾离子通道 ( Na + , K + channel) 抑制剂，具有抗心绞痛和抗 I 型心律失常作用。Bepridil hydrochloride hydrate 也是心脏 Na + /Ca2 + 交换 ( NCX1 ) 抑制剂。Bepridil hydrochloride hydrate 可用于心血管疾病的研究。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bepridil hydrochloride hydrate ((±)-Bepridil hydrochloride hydrate) is a long-acting, non-selective antagonist of the calcium channel (Ca+channel), Bepridil hydrochloride hydrate is an inhibitor of the Na+,K+channel and an inhibitor of cardiac Na+/Ca2+ exchange (NCX1).</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bepridil hydrochloride hydrate (CAS No.: 74764-40-2) is a small-molecule ion-channel modulator classified within the calcium-channel inhibitor category and is widely used as a pharmacological research tool in cardiovascular and membrane excitability studies; as the hydrochloride hydrate form of bepridil, it is a synthetic compound rather than a biologically derived macromolecule, and its principal research relevance lies in the interrogation of transmembrane cation flux, excitation–contraction coupling, and electrogenic transport processes. Available reference information indicates that this agent acts as a long-acting, non-selective antagonist of calcium influx pathways while also inhibiting sodium and potassium channel activities, and it has further been reported to inhibit the cardiac Na+/Ca2+ exchanger NCX1, supporting its use in studies focused on calcium homeostasis, action-potential regulation, and ion transport network cross-talk. In biomedical research settings, bepridil hydrochloride hydrate is therefore commonly positioned within ion-channel biology, cardiovascular pharmacology, and mechanism-based drug discovery programs aimed at characterizing channel-dependent phenotypes, validating electrophysiological targets, and benchmarking multi-ion-channel modulation profiles. Published and catalog-level evidence supports in vitro activity in the nanomolar to micromolar range across relevant ion-handling systems, although potency can vary substantially with assay format, cell type, channel state dependence, and readout methodology, and compound-specific concentration selection should accordingly be established empirically for each experimental context. Typical applications include use in cultured cardiac or other excitable cell models, transporter and channel screening platforms, mechanistic electrophysiology assays, and animal studies designed to evaluate the consequences of altered cation handling, with the concentrations or doses used in experiments typically depending on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bepridil hydrochloride hydrate (CAS No.: 74764-40-2) 是一种小分子离子通道调节剂，通常归类为非选择性、长效的钙离子通道拮抗剂，同时对钠离子通道、钾离子通道及心肌相关的 Na+/Ca2+ 交换过程表现出抑制活性，因此常被用于膜兴奋性调控、离子稳态失衡以及心血管系统电生理相关机制的基础研究与药物筛选研究。现有资料表明，该化合物的研究背景主要集中于可兴奋细胞中的跨膜离子流调节，其作用机制涉及对多类膜通道与转运过程的联合干预，可影响动作电位形成、传导特征、细胞内钙稳态以及与离子交换相关的下游应答网络；在靶点层面，已知其与钙通道阻断、多种钠通道和钾通道抑制以及 NCX1 相关调节作用有关，体现出较为典型的多靶点离子通道药理学特征。基于公开数据库与研究级产品资料，bepridil 及其盐酸盐/水合物形式被广泛视为研究离子通道交叉调控、心肌细胞电活动重塑、平滑肌兴奋性变化及转运体功能耦联的重要工具化合物，其体外活性总体可概括为微摩尔范围，且不同实验体系中的表观活性会因细胞类型、通道亚型、膜电位条件和检测平台差异而发生变化。该分子在应用上常见于细胞电生理模型、离子通量检测、机制验证实验、表型筛选以及动物水平的药理学探索，用于解析多离子通道协同调节对细胞功能状态的影响；实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。总体而言，Bepridil hydrochloride hydrate 适合作为离子通道生物学、心血管相关基础研究及先导化合物比较研究中的参考分子，有助于在非临床研究框架下评估多靶点膜蛋白调控对细胞生理与疾病相关表型的影响。 ([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Vascor?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bepridil hydrochloride hydrate is a small-molecule, non-selective calcium-channel inhibitor and multi-ion-channel modulator used in cardiovascular and ion-transport research.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>一种多靶点离子通道调节剂，适用于心血管电生理机制研究。</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bepridil hydrochloride hydrate (CAS No.: 74764-40-2) 是一种小分子离子通道调节剂，通常归类为非选择性且作用持续时间较长的膜电流调控化合物，在生物医学研究中主要作为研究心肌细胞电生理稳态、跨膜离子转运及兴奋性调节机制的工具分子使用。现有研究表明，该化合物可同时作用于钙离子通道、钠离子通道和钾离子通道，并对心脏 Na+/Ca2+ 交换体 NCX1 具有抑制活性，因此适用于解析动作电位形成与复极过程、细胞内钙稳态维持以及离子通道协同调控网络等生物学问题。从机制上看，其生物学效应主要与抑制多类离子通道介导的跨膜离子流、干预钠钙交换过程以及改变细胞兴奋性和节律相关信号输出有关，因而常被用于心血管生物学、离子通道药理学、应激性电活动异常机制及相关表型筛选研究。就体外活性而言，其对相关靶点的调控通常表现为低微摩尔至微摩尔范围的活性水平，但具体效应强度会因实验体系、细胞类型、检测终点及暴露时间不同而变化。在应用层面，该分子可用于细胞电生理模型、离体组织功能评价、动物水平药理机制研究以及先导化合物比较筛选，用于评估多离子通道干预对膜电位、钙瞬变、传导特征和应激反应的影响；实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。总体而言，Bepridil hydrochloride hydrate 适合作为研究多靶点离子通道调控、心肌兴奋收缩耦联异常及相关药理响应机制的重要实验工具分子，在基础研究和早期药物发现场景中具有较高的方法学价值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C8775</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4146-30-9</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Framycetin sulphate</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Framycetin sulfate (Neomycin B sulfate) 是一种氨基糖苷类抗生素，是一种有效的 RNase P 裂解活性抑制剂， K i 为 35 μM。Framycetin sulfate 竞争 RNase P RNA 中特定的二价金属离子结合位点。Framycetin sulfate 抑制锤头状核酶 ( hammerhead ribozyme )， K i 值为 13.5 μM。Framycetin sulfate 是 5″-azido neomycin B 前体，与 miR-525 中的 Drosha 位点结合，可用于肝性脑病和肠致病性大肠杆菌感染。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Framycetin sulfate (Neomycin Sulphate B) belongs to aminoglycoside class of antibiotics that contain two or more aminosugars connected by glycosidic bonds.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Framycetin sulphate (CAS No.: 4146-30-9) is an aminoglycoside-class small-molecule research reagent, commonly regarded as the sulfate salt form enriched in framycetin or neomycin B, and is derived from Streptomyces biosynthetic products; within biomedical research, it is principally categorized as an antibacterial translation inhibitor and RNA-binding scaffold with additional utility in chemical biology studies of structured RNA. Available reference data indicate that its canonical antibacterial mechanism is associated with binding to the bacterial 30S ribosomal subunit, including interactions with 16S rRNA that disrupt translation initiation and fidelity, whereas in mechanistic RNA studies it has also been reported to inhibit RNase P-mediated cleavage through competition at defined divalent-metal binding regions and to suppress hammerhead ribozyme function, supporting a broader mode of action based on electrostatic recognition of folded RNA motifs and perturbation of catalytically important RNA–metal architectures. In vitro activity has been described in the low micromolar range for RNA-processing and ribozyme-related assays, while class-associated antibacterial effects are generally observed from low to moderate micromolar concentrations depending on organism, medium composition, resistance background, and endpoint selection. Owing to these properties, framycetin sulphate is used in microbiology, RNA-targeted screening, ribozyme and noncoding RNA interaction studies, comparative profiling of aminoglycoside chemotypes, and assay development for translation control or RNA-ligand discovery, with experimental use spanning cell-free biochemical systems, bacterial culture models, and selected preclinical in vivo infection-related research settings; the concentrations or doses used in experiments typically depend on specific experimental designs, model systems, and research objectives.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Framycetin sulphate (CAS No.: 4146-30-9) 是一种来源于放线菌代谢产物体系、通常被视为新霉素B硫酸盐形式的氨基糖苷类小分子研究试剂，属于以糖基化氨基环醇骨架为特征并以核糖核酸相互作用为重要研究切入点的一类天然产物衍生抗菌分子，在生命科学研究中主要用于微生物学、RNA生物学、核酶催化机制以及先导化合物筛选等方向；现有资料表明，该分子除具有典型氨基糖苷类对原核生物翻译体系的结合特征外，还可作为RNA靶向配体影响非编码RNA相关过程，其较受关注的作用机制包括抑制RNase P裂解活性、竞争RNase P RNA中特定二价金属离子结合位点，并对锤头状核酶活性产生抑制作用，提示其能够通过干扰RNA构象稳定性、金属离子依赖性催化环境及RNA底物识别过程来调节核酸加工事件；部分研究还将其作为5″-azido neomycin B等探针分子的前体，用于考察Drosha相关位点及miRNA前体局部结构的识别规律，因此在RNA加工、核糖核蛋白复合体功能解析和RNA结合化合物发现中具有方法学价值。就体外活性而言，Framycetin sulphate 在已报道的RNA相关实验体系中总体表现为低微摩尔至微摩尔范围的活性水平，适合用于比较不同RNA靶标、金属离子条件或核酸序列背景下的小分子响应差异；在应用场景上，其常见用途包括作为细胞外或无细胞体系中的机制研究工具、用于细菌或细胞模型中的表型对照、用于RNA靶向化合物筛选与构效关系探索，以及在动物来源样本或体内前期研究中作为药理探针评估核酸相关生物过程的扰动效应，而实验中所使用的浓度或剂量通常取决于具体的实验设计、模型类型、暴露时间及研究目的。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Framycetin sulphate is an aminoglycoside antibacterial translation inhibitor targeting the bacterial 30S ribosomal subunit, widely used in microbiology and structured RNA research.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>一种氨基糖苷类科研试剂，用于RNA靶向机制与核酸加工研究。</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Framycetin sulphate (CAS No.: 4146-30-9) 是一种属于氨基糖苷类的小分子研究工具，通常亦被视为新霉素 B 的硫酸盐形式，来源上与放线菌来源的天然抗菌代谢产物家族相关，在生命科学研究中主要被归类为以 RNA 为核心作用对象的生物活性分子与核酸功能调节化合物。现有研究表明，该分子除具有经典氨基糖苷对核糖体相关过程的结合特征外，还可直接作用于结构化 RNA 元件，在机制上表现为对 RNase P 裂解活性的抑制，并可与 RNase P RNA 中特定二价金属离子结合位点发生竞争，同时对锤头状核酶活性产生抑制作用，提示其生物学效应与 RNA 高级结构识别、金属离子依赖性催化干扰以及 RNA 加工事件调控密切相关；部分资料还提示其可作为相关氨基糖苷衍生物研究的前体分子，并用于探索特定 microRNA 前体加工位点的配体识别特征，因此在 RNA 化学生物学、核酶机制解析、非编码 RNA 功能研究、核酸靶向先导筛选以及抗感染机制模型中具有方法学价值。从体外活性特征看，其对相关 RNA 靶标的抑制水平总体处于低微摩尔至微摩尔范围，适合用于评估 RNA 靶向配体的构效关系、金属离子依赖性相互作用及核酸催化中心的药理干预敏感性。在应用场景上，该分子常见于体外酶学实验、细胞水平机制验证、RNA 结合与竞争实验以及动物来源感染模型或药物筛选体系中的对照研究，但具体实验中所采用的浓度或剂量通常取决于研究目标、模型类型、暴露时间及终点评价指标。总体而言，Framycetin sulphate 是一类兼具氨基糖苷骨架特征与 RNA 靶向研究价值的功能分子，尤其适用于围绕 RNA 加工、核酶催化、金属离子依赖性核酸生物学以及相关药物发现策略开展基础与转化前期研究。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C8776</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>86329-79-5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cefodizime Sodium</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cefodizime sodium 是一种第三代头孢菌素抗生素，具有广泛的抗菌活性。Cefodizime sodium 对肾脏没有毒性，具有良好的耐受性和免疫调节活性，可用于呼吸道和泌尿道的严重感染的研究。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Cefodizime Sodium is a third generation cephalosporin antibiotic, has broad-spectrum activity</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cefodizime Sodium (CAS No.: 86329-79-5) is a third-generation cephalosporin antibacterial research compound that is broadly categorized within anti-infective and host-response modulation studies and is commonly used as a reference molecule for investigations of cell wall biosynthesis inhibition in susceptible bacteria. As a semisynthetic cephalosporin-class agent, its primary biological mechanism is understood to involve binding to bacterial penicillin-binding proteins and disruption of the terminal stages of peptidoglycan assembly, thereby impairing cell wall integrity and promoting bactericidal activity; in parallel, published experimental literature indicates that cefodizime has been examined for immunobiology-related effects, including modulation of phagocyte function, mononuclear cell responses, and cytokine-associated immune parameters, although these secondary actions remain incompletely defined and should be interpreted as context-dependent research observations rather than a fully resolved signaling mechanism. Consistent with its class profile, in vitro antibacterial potency is generally discussed across susceptible organisms in the low micromolar to sub-micromolar equivalent activity range when assessed by MIC-based microbiology assays, while exact activity values vary substantially with species, strain background, inoculum conditions, and assay format. In biomedical research, Cefodizime Sodium is therefore relevant for studies of bacterial susceptibility profiling, resistance phenotyping, penicillin-binding protein biology, comparative cephalosporin pharmacology, infection-model assay development, and exploratory analyses of antibiotic-associated immune modulation in cellular and animal systems; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cefodizime Sodium (CAS No.: 86329-79-5) 是一种第三代头孢菌素类β-内酰胺抗菌研究分子，为 cefodizime 的钠盐形式，通常被归入广谱抗菌剂与细菌细胞壁生物合成抑制剂范畴，主要用于微生物学、感染生物学、宿主—病原体相互作用以及抗菌药物筛选等研究场景；从作用机制看，此类第三代头孢菌素的核心药理基础在于结合细菌青霉素结合蛋白并抑制肽聚糖交联过程，进而干扰细胞壁装配、诱导细胞壁完整性丧失并产生杀菌效应，因而其已知研究靶点主要归属于细菌细胞壁合成相关的青霉素结合蛋白体系而非真核细胞内经典信号通路。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/9852176?utm_source=openai)) 现有资料表明，Cefodizime Sodium 具有较广的体外抗菌活性谱，相关体外活性通常可概括为微摩尔至更高有效浓度范围内表现出对敏感菌株的抑制作用，但具体效力受菌种、耐药表型、培养条件与终点评价方法影响较大，因此研究中更适合采用菌株分层和方法学标准化框架进行比较分析。([pubmed.ncbi.nlm.nih.gov](https://pubmed.ncbi.nlm.nih.gov/1460409/?utm_source=openai)) 在生命科学研究中，该分子常被用于细菌增殖抑制实验、最低抑菌浓度测定、耐药机制解析、与其他抗菌分子的联用筛选，以及在细胞共培养或动物感染模型中评估细菌负荷变化和药效学趋势；实验中所使用的浓度或剂量通常取决于具体的实验设计、受试菌株特征、给药途径与研究目的。([pubmed.ncbi.nlm.nih.gov](https://pubmed.ncbi.nlm.nih.gov/1460409/?utm_source=openai)) 由于公开来源中关于其特异性分子靶点细分、下游宿主调控网络及统一体外定量参数的高一致性数据相对有限，对其研究定位通常依据头孢菌素类的共同机制、cefodizime 已报道的广谱抗菌属性以及感染模型中的实验用途进行概括，这使其适合作为研究细菌细胞壁生物合成、β-内酰胺类作用模式及耐药性演化过程的参考化合物。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/9852176?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Cefodizime Sodium is a third-generation cephalosporin antibacterial that targets bacterial penicillin-binding proteins and is utilized in anti-infective, cell wall biosynthesis, and host-response modulation research.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>一种第三代头孢菌素类抗菌研究分子，用于细菌细胞壁生物合成研究。</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Cefodizime Sodium (CAS No.: 86329-79-5) 是一种第三代头孢菌素类β-内酰胺抗菌研究分子，通常作为广谱抗菌机制研究、宿主反应调节分析及先导化合物比较评价中的参考化合物使用，主要来源于半合成头孢菌素药物化学体系，在生物医学研究中常被归入细菌细胞壁生物合成抑制剂与抗感染药理工具分子范畴。其已知核心作用机制为与细菌青霉素结合蛋白发生结合，进而抑制肽聚糖交联相关转肽反应，导致细胞壁装配受阻、细菌形态稳定性下降并产生杀菌效应；现有研究提示其对不同菌种的青霉素结合蛋白具有差异性亲和特征，在革兰阴性菌中常涉及PBP1A、PBP1B及PBP3等靶蛋白，在部分革兰阳性菌中则表现出对PBP1相关位点的作用倾向，同时对多种常见β-内酰胺酶具有一定稳定性，但其活性仍可受耐药相关酶谱改变及靶蛋白变异影响。基于公开的体外研究结果，Cefodizime Sodium 对敏感菌株的抑制活性总体可概括为低微摩尔至微摩尔范围，对部分高敏感菌群可接近亚微摩尔水平，而对耐药或产酶表型菌株的活性则可能明显下降，因此其体外表现通常依赖于受试菌种、培养条件、接种量及耐药背景。除直接抗菌效应外，既有研究还提示该分子具有一定免疫反应调节相关特征，但其具体分子基础尚未被完全阐明，通常被理解为对特异性与非特异性防御过程的间接影响而非单一经典信号通路驱动。该分子在研究中的典型应用包括细菌培养模型中的药敏比较、细胞或组织相关感染模型中的药效学观察、动物感染模型中的暴露反应评估，以及作为第三代头孢菌素代表分子用于新型抗菌化合物筛选、耐药机制解析和联合用药策略的基础研究。实验中所使用的浓度或剂量通常取决于具体的实验设计、目标菌株、生物样本类型以及终点检测方式，在缺乏统一条件时宜结合药敏终点、时间杀菌曲线和耐药表型分层进行综合判读。总体而言，Cefodizime Sodium 适用于围绕细菌细胞壁合成抑制、青霉素结合蛋白相互作用、β-内酰胺类耐药性演化及宿主病原体相互作用开展的生物医学与药物研发研究。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C8777</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>53179-09-2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sisomicin sulfate</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sisomicin sulfate 是一种广谱氨基糖苷类抗生素，可由依尼奥小单孢菌 ( Micromonospora inyoensis ) 产生的。Sisomicin sulfate 对革兰氏阳性细菌具有很大的活性。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sisomicin Sulfate (Pathomycin) is the sulfate salt form of sisomicin, a broad-spectrum aminoglycoside antibiotic isolated from Micromonospora inyoensis. Sisomicin is structurally similar to gentamicin but has a unique unsaturated diamino sugar. Of the aminoglycoside antibiotics, sisomicin has the greatest activity against gram-positive bacteria.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Sisomicin sulfate (CAS No.: 53179-09-2) is a naturally derived broad-spectrum aminoglycoside antibiotic research reagent obtained as the sulfate salt of sisomicin, a secondary metabolite originally isolated from Micromonospora inyoensis, and is primarily categorized as a small-molecule antibacterial tool compound for studies of microbial physiology, translational control, and anti-infective discovery. Its biological activity is consistent with the canonical aminoglycoside mechanism, in which binding to the bacterial 30S ribosomal subunit, including the decoding region of 16S rRNA, disrupts accurate translation by interfering with initiation and elongation processes, promoting codon misreading and production of aberrant proteins; accordingly, its principal functional target class is the prokaryotic ribosome rather than a mammalian signaling protein pathway. Available reference information indicates that sisomicin displays particularly strong activity within the aminoglycoside class against gram-positive bacteria while retaining broad antibacterial coverage, and, although compound-specific quantitative values are not consistently available across standardized public sources for this salt form, in vitro potency for aminoglycoside antibiotics of this type is typically evaluated by minimum inhibitory concentration measurements spanning low micromolar to sub-micromolar equivalent activity ranges depending on the microbial species, inoculum conditions, and resistance background. In biomedical research and drug discovery, Sisomicin sulfate is therefore commonly used as a comparator or mechanistic control in bacterial susceptibility assays, ribosome-function studies, resistance profiling, selection systems, and antimicrobial screening workflows in cell-based and microbiological models, while broader exploratory use in animal infection models may be considered when experimentally justified; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives, and should be optimized with attention to organism, matrix, exposure duration, and intended analytical endpoint.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sisomicin sulfate (CAS No.: 53179-09-2) 是西索米星的硫酸盐形式，属于氨基糖苷类抗菌研究分子，通常归入来源于小单孢菌属发酵产物的天然产物及其衍生物范畴，公开资料表明其母体成分最初分离自依尼奥小单孢菌，具有广谱抗菌活性，并在同类分子中表现出相对突出的革兰氏阳性菌活性特征，因而常被用于抗菌药理、微生物学、耐药机制与先导化合物比较研究中。其已知作用机制与氨基糖苷类的经典核糖体靶向过程一致，主要结合细菌核糖体30S亚基并作用于16S rRNA相关解码区域/A位点，进而干扰翻译准确性、诱导密码子误读并抑制蛋白质合成，最终导致细菌产生功能异常的蛋白表达与生长受限；在研究语境下，该分子也常被用作分析核糖体配体识别、氨基糖苷构效关系及耐药表型形成机制的工具化合物。针对该硫酸盐形式的统一定量体外数据公开较为有限，因此其活性水平通常结合西索米星及同类氨基糖苷的已知特征进行概括，相关抑菌或生长抑制效应一般可见于低微摩尔至微摩尔范围，具体强弱则受菌种背景、培养条件、摄取效率以及耐药修饰酶、外排或核糖体改变等因素显著影响。基于上述性质，Sisomicin sulfate 常用于细菌细胞模型中的敏感性评估、核糖体功能研究、耐药株对照实验、联合筛选体系建立以及动物感染模型中的机制验证与候选分子比较研究，而实验中所使用的浓度或剂量通常取决于具体的实验设计、目标菌种与研究目的；在药物研发背景下，其价值主要体现在作为氨基糖苷骨架代表分子，用于支持抗菌活性谱分析、核糖体靶向分子优化和耐药规避策略探索。 ([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Sisomicin-sulfate?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sisomicin sulfate is a broad-spectrum aminoglycoside antibiotic that targets the bacterial 30S ribosomal subunit and is used in microbiology, ribosome-function, and anti-infective research.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>一种氨基糖苷类抗菌研究分子，用于核糖体机制与耐药研究。</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sisomicin sulfate (CAS No.: 53179-09-2) 是西索米星的硫酸盐形式，属于天然来源的广谱氨基糖苷类抗生素，通常被归类为微生物发酵获得的小分子抗菌研究工具，其生物学来源与依尼奥小单孢菌相关，在抗感染机制研究、细菌生理学、核糖体功能解析以及先导化合物筛选中具有代表性价值。作为氨基糖苷类分子，该化合物的已知核心作用机制主要与细菌核糖体小亚基结合有关，通常靶向30S核糖体并干扰翻译过程，进而造成蛋白质合成错误、翻译准确性下降及细胞内稳态受扰，因此常被用于研究核糖体抑制、翻译失真效应、细菌应激反应以及药物敏感性与耐受性形成等过程。结合同类化合物与已有研究背景，Sisomicin sulfate 对革兰氏阳性细菌表现出较强活性，同时对部分其他敏感菌群亦具有广谱抑制特征，其体外活性一般可概括为低微摩尔至中微摩尔范围，具体效应强弱则取决于菌株背景、接种密度、培养条件及终点检测方法。围绕其作用机制的研究还常涉及膜通透性变化、能量依赖性摄取过程、核糖体相关耐药表型以及产生菌自身防御机制等方向，因此该分子可作为解析氨基糖苷类药理学共性与差异的重要参考工具。在应用层面，Sisomicin sulfate 常见于细菌培养体系中的抑菌活性评估、耐药机制分析、联合用药筛选、核糖体靶向化合物比较研究，以及在细胞或动物感染模型中作为实验对照分子使用；实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。若针对该编号对应化合物的某些定量实验参数报道有限，则可依据其作为典型氨基糖苷类成员的类别特征进行研究性概述，即其主要价值在于作为核糖体功能干预分子与抗菌活性参考化合物，用于支持基础生物医学研究、微生物学研究及药物发现早期阶段的方法学建立与机制验证。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C8778</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1807988-02-8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bictegravir Sodium</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bictegravir sodium 是一种有效的 HIV-1 整合酶抑制剂，其 IC 50 值为 7.5 nM。Bictegravir sodium 表现出强大的选择性的抗 HIV 活性和低的细胞毒性。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Bictegravir Sodium (GS-9883 Sodium) is a potent inhibitor of HIV-1 integrase, with an IC50 of 7.5 nM. Bictegravir Sodium exhibits potent and selective anti-HIV activity and low cytotoxicity</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bictegravir Sodium (CAS No.: 1807988-02-8) is a small-molecule antiviral research compound and sodium salt form of bictegravir, classified within the HIV-1 integrase strand transfer inhibitor category and widely used as a reference tool in virology, host-virus interaction studies, and anti-infective discovery workflows; it is a synthetic molecule rather than a biologically derived natural product, and its principal functional background is the selective inhibition of the viral integrase enzyme responsible for the strand transfer step of proviral DNA insertion into host genomic DNA, thereby disrupting HIV-1 integration and downstream replication processes. Available evidence indicates that bictegravir exhibits potent inhibition of HIV-1 integrase strand transfer activity in the low-nanomolar range, with reported cellular antiviral activity also spanning the subnanomolar to low-nanomolar range in susceptible in vitro systems, while showing comparatively weaker effects on integrase 3′-processing and generally low cytotoxicity under experimental conditions. Mechanistically, its activity is associated with blockade of integrase catalytic function and suppression of productive viral DNA integration, with corresponding accumulation of unintegrated viral DNA intermediates in infected cells; accordingly, this reagent is primarily categorized for antiviral mechanism studies, resistance profiling, integrase-focused screening platforms, and comparative evaluation of second-generation integrase inhibitors in cell-based infection models and related translational research settings. In biomedical research, Bictegravir Sodium is commonly applied in immortalized lymphoid cell lines, peripheral blood mononuclear cell-based assays, and selected in vivo antiviral pharmacology models to investigate target engagement, resistance-associated substitutions, viral replication fitness, and combination-screening paradigms, and the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bictegravir Sodium (CAS No.: 1807988-02-8) 是一种用于逆转录病毒学与抗病毒药理研究的小分子整合酶链转移抑制剂，通常归类为 HIV-1 整合酶抑制剂研究工具，主要用于解析病毒复制周期中前病毒 DNA 整合这一关键步骤的分子机制；现有研究表明，其核心靶点为 HIV-1 编码的整合酶，主要抑制链转移反应而对 3′-加工步骤作用相对较弱，从而阻断病毒 DNA 向宿主基因组的整合并降低细胞内整合事件的形成，相关作用机制属于整合酶催化过程干预范畴，可服务于病毒学、耐药机制、宿主—病毒相互作用及抗病毒先导优化等研究方向。([pubmed.ncbi.nlm.nih.gov](https://pubmed.ncbi.nlm.nih.gov/27645238/?utm_source=openai)) 作为第二代整合酶链转移抑制剂相关研究分子，Bictegravir sodium 常被用于 HIV-1 复制模型、整合酶生化实验、感染性细胞体系以及耐药突变筛选研究，以评估不同整合酶变体对抑制剂的敏感性变化，并为结构—活性关系分析和联合筛选策略提供参考。([pubmed.ncbi.nlm.nih.gov](https://pubmed.ncbi.nlm.nih.gov/27645238/?utm_source=openai)) 在体外活性方面，已报道其对 HIV-1 整合酶链转移过程表现出纳摩尔范围活性，而在更广泛的细胞与机制研究语境下，可概括为纳摩尔至微摩尔范围内具有研究活性，同时文献与数据库信息提示其具有较强的抗 HIV-1 活性以及相对较低的细胞毒性特征，因此适合作为比较不同整合酶抑制剂药效学特征与耐药屏障的重要参考分子。([pubmed.ncbi.nlm.nih.gov](https://pubmed.ncbi.nlm.nih.gov/27645238/?utm_source=openai)) 在应用层面，该分子可用于细胞感染模型中的机制验证、病毒整合定量分析、候选化合物对照研究以及动物实验前的体外药理评估；具体实验中所采用的浓度或剂量通常取决于细胞类型、病毒株背景、终点检测方法及研究目的，因此一般需结合实验设计、阳性对照设置与读出指标进行优化。([pubmed.ncbi.nlm.nih.gov](https://pubmed.ncbi.nlm.nih.gov/27645238/?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bictegravir Sodium is a small-molecule HIV-1 integrase strand transfer inhibitor that targets viral DNA integration and is utilized in antiviral and virology research.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>一种用于HIV-1整合酶链转移抑制机制研究的小分子工具化合物。</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Bictegravir Sodium (CAS No.: 1807988-02-8) 是一种小分子抗病毒研究化合物，通常归类为 HIV-1 整合酶抑制剂，主要用于病毒复制机制、宿主—病毒相互作用以及先导化合物筛选等生物医学研究领域。现有研究表明，其核心靶点为 HIV-1 整合酶，通过干扰病毒 DNA 整合进入宿主基因组这一关键步骤而抑制病毒复制过程，因而常被用于整合酶依赖性通路、病毒生命周期特定阶段以及耐药相关分子事件的研究。基于公开资料与同类研究信息，Bictegravir Sodium 在体外实验中表现出纳摩尔范围的活性水平，并显示出较强的靶向选择性与较低的细胞毒性特征，因此适合在病毒学、分子药理学和药物发现研究中作为工具化合物进行机制验证。该分子常见于细胞感染模型、酶活性分析体系以及抗病毒候选物比较研究，也可用于评估整合酶抑制相关效应、筛查耐受性差异及解析结构—活性关系；在部分研究设计中，还可结合动物模型开展药代动力学特征、体内暴露后生物学效应及病毒学终点的探索性评估。具体实验中所采用的浓度或剂量通常取决于研究模型、检测终点、给药方案以及实验目的，实际应用时一般需要结合化合物稳定性、暴露时间、对照设置和检测平台进行系统优化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C8779</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>203120-46-1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Laninamivir Octanoate</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Laninamivir octanoate (CS-8958)，Laninamivir 的前体，是一种长效的神经氨酸酶 ( neuraminidase, NA ) 抑制剂，具有抗流感病毒活性。Laninamivir octanoate 对耐 Oseltamivir 的病毒以及对大流行性流感病毒均具有抗流感活性。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Laninamivir octanoate (CS-8958) is a long acting influenza neuraminidase (NA) inhibitor which shows superior anti-influenza virus activity.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Laninamivir Octanoate (CAS No.: 203120-46-1) is a synthetic small-molecule antiviral research compound and prodrug of laninamivir that is primarily classified as an influenza virus neuraminidase inhibitor precursor used in virology, host-pathogen interaction studies, and anti-infective drug discovery. In biomedical research settings, it is characterized as a long-acting neuraminidase-directed agent with activity against influenza A and influenza B viruses, including experimental contexts involving strains with reduced susceptibility to oseltamivir and pandemic influenza isolates, thereby supporting its use as a reference molecule for resistance profiling and comparative inhibitor evaluation. Its principal biological target is viral neuraminidase, and its functional mechanism is based on prodrug conversion to the active metabolite laninamivir in biological systems, followed by suppression of neuraminidase-dependent cleavage of terminal sialic acid residues, an effect that interferes with efficient release and spread of progeny virions and consequently attenuates viral propagation in infected cell systems. Published research further indicates subtype-dependent inhibitory behavior across neuraminidase variants, making this molecule relevant for structure-activity studies, viral enzyme pharmacology, and screening campaigns focused on inhibitor susceptibility landscapes. Reported in vitro potency for the active metabolite generally falls within the low nanomolar range against many influenza neuraminidase preparations, whereas the prodrug itself may display weaker direct enzyme inhibition ranging from nanomolar to submicromolar or higher levels depending on assay format, viral subtype, and metabolic context; accordingly, experimental interpretation should distinguish between direct biochemical inhibition and activity observed after bioactivation. Laninamivir octanoate is therefore commonly applied in enzyme assays, influenza-infected cell models, resistance surveillance workflows, and animal studies designed to examine antiviral exposure-response relationships, tissue retention, or comparative performance versus other neuraminidase inhibitors, with the concentrations or doses used in experiments typically depending on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Laninamivir Octanoate (CAS No.: 203120-46-1) 是一种用于抗病毒药理与病毒学研究的小分子前药，通常归类为流感病毒神经氨酸酶抑制剂相关化合物，其本身作为 laninamivir 的前体，在生物体系中经酯酶介导转化后释放活性形式，并主要围绕正黏病毒科流感病毒的复制、释放及宿主传播过程开展研究；现有研究表明，该分子的核心研究靶点为流感病毒神经氨酸酶，作用机制主要是通过与神经氨酸酶活性位点相关区域结合并抑制其酶学功能，从而干扰病毒颗粒从感染细胞表面的脱离与进一步扩散，同时其前药设计还与气道局部较持久的暴露特征相关，因此常被用于分析长效抑制策略、药物暴露后持续活性以及耐药相关神经氨酸酶变异对抑制效应的影响；从研究属性看，该分子广泛应用于流感病毒 A 型和 B 型相关体外酶学实验、细胞感染模型、耐药株敏感性比较、病毒进入后复制周期研究以及候选抗流感分子的对照筛选，已有文献显示其相关活性通常表现于纳摩尔至低微摩尔范围，但具体效应强度会随病毒亚型、神经氨酸酶变体、检测终点与实验体系差异而变化；在实验应用层面，该化合物常作为机制研究工具分子，用于验证神经氨酸酶依赖性病毒释放通路、评估耐 oseltamivir 相关毒株或大流行相关毒株中的抑制谱特征，并可在细胞模型或动物模型中用于药效持续性与病毒载量动态的基础研究，而实验中所采用的浓度或剂量通常取决于具体研究目的、给药途径、病毒挑战条件及终点评估方案。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Laninamivir Octanoate is a synthetic small-molecule prodrug targeting influenza viral neuraminidase, used in virology, host-pathogen interaction studies, and anti-infective drug discovery.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>一种用于流感病毒神经氨酸酶抑制研究的前药型小分子化合物。</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Laninamivir Octanoate (CAS No.: 203120-46-1) 是一种以 laninamivir 为活性母核的前药型小分子研究化合物，可归类为流感病毒神经氨酸酶抑制剂相关分子，亦可视为用于提升局部暴露持续性与药效维持特征的长效抗病毒先导或工具化合物；其研究背景主要集中于正黏病毒科流感病毒的复制周期调控、病毒颗粒释放过程抑制以及耐药相关机制评价，尤其适用于神经氨酸酶介导的病毒脱离、传播与宿主适应性等方向的生物医学研究。该分子在生物体系中经转化后释放出活性形式，并以病毒神经氨酸酶为核心作用靶点，通过抑制唾液酸残基切割过程而干扰新生病毒颗粒从感染细胞表面的释放，从而降低后续扩散效率；从机制上看，其作用与流感病毒生命周期晚期事件密切相关，常用于解析病毒表面糖蛋白功能、宿主受体识别动态以及神经氨酸酶抑制所引发的病毒复制受限表型。现有研究资料表明，该类分子在体外通常表现为纳摩尔至微摩尔范围的活性水平，但具体效应强弱会随病毒株类型、宿主细胞系统、酶学检测平台以及前药向活性体转化效率而变化；在研究应用上，Laninamivir Octanoate 常见于细胞感染模型中的抗病毒活性评价、耐药株与交叉敏感性比较、神经氨酸酶功能验证实验、候选分子联用筛选以及动物模型中的药效持续性观察等场景，特别适合用于考察对部分奥司他韦敏感性下降病毒株及不同流感亚型的响应差异。作为目录型生命科学研究条目，对该化合物的描述宜突出其作为长效前药型神经氨酸酶抑制剂的定位、围绕流感病毒复制与传播生物学的研究价值，以及在药物发现早期用于靶点验证、活性筛选和机制研究的工具属性；实验中所使用的浓度或剂量通常取决于具体的实验设计、模型系统、给药途径与研究目的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C8780</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>169869-90-3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Exatecan Mesylate</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Exatecan mesylate (DX8951f) 是一种 DNA 拓扑异构酶 I ( topoisomerase I ) 抑制剂， IC 50 值为 2.2 μM (0.975 μg/mL)，可用于癌症研究。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Exatecan Mesylate (GMP) refers to the GMP grade reagents of Exatecan Mesylate. Exatecan Mesylate (DX8951f) is a DNA topoisomerase I inhibitor (IC50: 2.2 μM, 0.975 μg/mL).</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Exatecan Mesylate (CAS No.: 169869-90-3) is a small-molecule camptothecin-derived research compound and topoisomerase I inhibitor widely used in biomedical investigation as a tool for studying DNA damage responses, replication stress, and cytotoxicity mechanisms relevant to oncology-focused drug discovery. Functionally, it belongs to the class of antineoplastic research agents that interfere with DNA topology regulation by stabilizing the topoisomerase I–DNA cleavage complex, thereby impeding religation of single-strand DNA breaks and promoting replication-associated DNA lesions, activation of checkpoint signaling, and downstream apoptotic or cell death pathways in proliferating experimental systems. Available reference data indicate inhibitory activity against DNA topoisomerase I at low micromolar levels, supporting its use as a potent probe for mechanistic studies of genome integrity, cell-cycle perturbation, and sensitivity determinants associated with topoisomerase I pathway modulation. In life sciences research, this compound is commonly applied in cancer cell-based assays, comparative studies of drug resistance, combination screening paradigms, and preclinical pharmacology workflows designed to evaluate DNA damage-inducing agents, while GMP-grade material refers to a manufacturing quality designation relevant to reagent production standards rather than any implication of clinical suitability. Typical use cases include pathway interrogation in cultured cell models, exploratory efficacy assessment in animal models, and reference-compound deployment in screening platforms, with the concentrations or doses used in experiments typically depending on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Exatecan Mesylate (CAS No.: 169869-90-3) 是一种用于生命科学研究的喜树碱类衍生物，通常归类为 DNA 拓扑异构酶 I 抑制剂，在肿瘤生物学、DNA 损伤应答及细胞增殖调控研究中具有较高的应用价值。现有资料表明，该分子亦常以 DX-8951f 名称出现，属于水溶性较好的非前药型拓扑异构酶 I 抑制剂，其主要作用机制为稳定拓扑异构酶 I 与 DNA 形成的切割复合物，干扰 DNA 解旋与复制相关过程，并进一步诱导复制压力、DNA 单链断裂向更广泛基因组损伤事件转化，从而激活与 DNA 损伤应答相关的分子网络；因此，该化合物常被用于研究 TOP1 依赖性基因组稳态失衡、复制叉应激以及与 ATM/ATR 等损伤应答轴相关的细胞命运变化。基于公开研究资料与产品数据，其体外活性总体可概括为纳摩尔至低微摩尔范围，提示其在多种肿瘤细胞模型中具有较强的增殖抑制与机制探针价值。作为研究级试剂，Exatecan Mesylate 常用于细胞水平的靶点验证、DNA 损伤标志物分析、耐药机制解析、联合用药筛选以及动物移植瘤模型中的药效学探索，也因其拓扑异构酶 I 靶向特征而在抗体偶联药物相关载荷研究与递送系统评价中受到关注。具体实验中所采用的浓度、暴露时间或动物给药方案通常取决于模型类型、终点指标及研究目的，因而应结合细胞背景、药代暴露需求与毒理学观察进行优化；总体而言，该分子更适合作为解析拓扑异构酶 I 生物学功能、评估 DNA 损伤相关通路响应及支持早期药物发现研究的工具化研究材料。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Exatecan Mesylate is a camptothecin-derived topoisomerase I inhibitor used in cancer research to investigate DNA damage responses, replication stress, and cytotoxicity mechanisms.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>一种用于科研的拓扑异构酶I抑制剂，适用于DNA损伤与复制应激研究。</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Exatecan Mesylate (CAS No.: 169869-90-3) 是一种用于生物医学研究的合成小分子拓扑异构酶抑制剂，通常归类为可溶性喜树碱类似物及 DNA 拓扑异构酶 I 靶向研究工具，主要用于肿瘤生物学、DNA 损伤应答、复制压力及细胞增殖调控等方向的机制研究。现有研究表明，其核心作用靶点为拓扑异构酶 I，通过稳定酶与 DNA 形成的切割复合体、干扰 DNA 单链断裂后的再连接过程，诱导复制叉碰撞及继发性 DNA 损伤，从而激活与基因组稳定性失衡相关的应激反应网络；因此，该分子常被用作研究 DNA 复制障碍、细胞周期阻滞、凋亡相关过程及拓扑异构酶 I 依赖性药理效应的重要参考化合物。基于公开资料，Exatecan Mesylate 在体外通常表现为低微摩尔水平活性，并在多种肿瘤相关细胞系统中显示出较强的增殖抑制效应，相较部分同类拓扑异构酶 I 抑制剂具有较高水溶性和较强研究应用价值。其应用场景主要包括细胞模型中的靶点验证、DNA 损伤标志物检测、耐药机制解析、联合用药策略的前期筛选，以及动物模型中的药效学与暴露反应关系研究；在更广泛的药物研发背景下，该类分子也被用于拓扑异构酶 I 载荷开发和细胞毒性机制评估。实验中所使用的浓度或剂量通常取决于具体的实验设计、模型类型、给药方案及研究目的，实际使用时一般需结合细胞敏感性、暴露时长和终点指标进行系统优化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C8781</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1977495-97-8</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trilaciclib dihydrochloride</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Trilaciclib (G1T28) hydrochloride 是一种口服有效的 CDK4/6 的抑制剂，对于 CDK4 和 CDK6 的 IC 50 值分别为 1 nM 和 4 nM。Trilaciclib hydrochloride 能够有效抑制肿瘤细胞增殖，并减轻化疗产生的血液毒性。Trilaciclib hydrochloride 可减轻 5FU ( HY-90006 ) 化疗引起的细胞凋亡和骨髓抑制。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Trilaciclib hydrochloride (G1T28 hydrochloride) is an inhibitor of CDK4/6 (IC50s: 1 nM and 4 nM for CDK4 and CDK6).</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Trilaciclib dihydrochloride (CAS No.: 1977495-97-8) is a synthetic small-molecule cyclin-dependent kinase inhibitor that is primarily categorized as a cell cycle and checkpoint research reagent for oncology, hematopoiesis, and drug discovery applications, with established activity against CDK4 and CDK6 and functional relevance to the cyclin D–CDK4/6–RB signaling axis that governs G1-to-S phase progression. Available reference data indicate that this compound, also described as the hydrochloride salt of trilaciclib, exhibits potent in vitro inhibitory activity in the nanomolar range, with reported IC50 values of approximately 1 nM for CDK4 and 4 nM for CDK6, consistent with selective suppression of CDK4/6-dependent phosphorylation events and consequent modulation of RB-mediated cell-cycle control. In biomedical research settings, it is commonly used to investigate proliferation regulation, transient cell-cycle arrest, cytoprotection of rapidly cycling progenitor populations under genotoxic stress, and pharmacologic interactions with cytotoxic agents in mechanistic cell-based assays and preclinical animal models; published product and pharmacology summaries further support its use in studies examining apoptosis, bone marrow suppression, and chemotherapy-associated cellular injury in CDK4/6-responsive systems. As a research tool, Trilaciclib dihydrochloride is therefore well suited for pathway interrogation, target validation, comparative profiling of CDK inhibitors, and combination-screening workflows in tumor biology and myeloprotection-related experimental paradigms, while the concentrations or doses used in experiments typically depend on specific experimental designs, model systems, and research objectives.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Trilaciclib dihydrochloride (CAS No.: 1977495-97-8) 是一种用于生命科学研究的细胞周期调控小分子抑制剂，通常归类为选择性CDK4/6抑制剂盐酸盐形式，适用于肿瘤生物学、细胞增殖调控、骨髓生物学以及药物筛选相关研究；该分子并非天然来源产物，而是经化学合成获得的研究工具化合物，主要通过抑制CDK4与CDK6激酶活性、干预Cyclin D–CDK4/6–Rb轴并诱导G1期阻滞，从而调节细胞周期进程、降低Rb磷酸化水平并影响快速增殖细胞的增殖动力学；现有资料表明其对CDK4和CDK6表现出高选择性抑制活性，体外活性总体可概括为纳摩尔水平，并可在多种细胞模型中用于研究细胞周期进入、增殖抑制、化疗相关应激反应以及造血细胞群体对细胞周期干预的响应特征；在机制研究中，该化合物常被用于解析CDK4/6信号依赖性、Rb通路状态与细胞命运变化之间的关系，也可作为对照分子应用于评估候选化合物在细胞周期靶向筛选体系中的作用谱；在实验场景上，其可用于肿瘤细胞系、造血祖细胞相关体系及动物模型中的药理学研究，以观察细胞增殖抑制、细胞凋亡相关变化、骨髓抑制应答调节及联合处理条件下的生物学效应，而实验中所使用的浓度或剂量通常取决于具体的实验设计、模型背景、给药方式与研究目的。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Trilaciclib dihydrochloride is a selective small-molecule CDK4/6 inhibitor targeting the cyclin D–CDK4/6–RB pathway for oncology, hematopoiesis, and cell-cycle research.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>一种选择性CDK4/6抑制剂盐酸盐，用于细胞周期与增殖调控研究。</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Trilaciclib dihydrochloride (CAS No.: 1977495-97-8) 是一种用于生命科学研究的小分子细胞周期调控工具化合物，通常归类为细胞周期蛋白依赖性激酶4/6抑制剂盐酸盐形式，主要应用于肿瘤生物学、骨髓生物学、细胞增殖调控及药物筛选等研究领域。现有研究资料表明，该分子对CDK4和CDK6具有高选择性抑制活性，其体外活性总体处于纳摩尔水平，并可通过抑制RB蛋白相关磷酸化过程、诱导细胞发生可逆性G1期阻滞而调控细胞周期进程，从而影响快速增殖细胞群体的增殖动力学与应激反应。基于这一作用机制，Trilaciclib dihydrochloride 常被用作解析CDK4/6信号轴、G1/S转换控制网络以及细胞周期与DNA损伤应答、凋亡和骨髓祖细胞稳态之间关系的研究探针。在体外细胞模型中，该化合物可用于评估不同肿瘤细胞或造血相关细胞对细胞周期干预的敏感性，并用于比较CDK4/6依赖型与非依赖型增殖表型；在动物模型中，其研究用途主要集中于观察外源性细胞周期抑制对组织增殖状态、骨髓抑制表型及化疗相关生物学损伤过程的影响。已有前期数据提示，该分子在特定实验条件下能够降低某些细胞损伤与凋亡相关表型，并对化疗诱导的骨髓抑制过程表现出研究层面的缓解趋势，但这些发现应限定于非临床实验体系中的机制探索，不应外推至任何人体用途。作为一种常用于药理机制验证和候选药物比较研究的参考分子，其实验中所采用的浓度或剂量通常取决于具体模型、给药方案、终点指标及研究目的，适合用于细胞功能研究、通路验证、联合处理策略评估以及新型细胞周期调控分子的活性对照分析。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C8782</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1207859-16-2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cinitapride Hydrogen Tartrate</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cinitapride monotartrate 是一种 5-HT 1A 和 5-HT 4 激动剂。Cinitapride monotartrate 也是一种 5-HT 2A 和 D 2 拮抗剂。Cinitapride monotartrate 可用于功能性消化不良的研究。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cinitapride Monotartrate is a nonselective agonist of 5-HT1 and 5-HT4 receptors and an antagonist of 5-HT2 and dopamine D2 receptors, Cinitapride Monotartrate is widely applied in gastrointestinal research to investigate mechanisms underlying functional dyspepsia and gastroesophageal reflux disease, including modulation of gastrointestinal motility and visceral sensitivity.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Cinitapride Hydrogen Tartrate (CAS No.: 1207859-16-2) is a small-molecule serotonergic and dopaminergic receptor modulator that is broadly categorized as a gastroenterology- and neuropharmacology-relevant research compound for studies of enteric signaling, gastrointestinal motility, and visceral sensory regulation. This material is a salt form of cinitapride and is not a biologically derived macromolecule, but rather a synthetic receptor-active agent used in biomedical research to interrogate pathways linked to 5-hydroxytryptamine and dopamine neurotransmission. Available reference sources describe cinitapride hydrogen tartrate, also referred to as cinitapride monotartrate, as a nonselective agonist at 5-HT1 and 5-HT4 receptor systems and an antagonist at 5-HT2 receptors, with additional reported antagonistic activity at dopamine D2 receptors, supporting its use as a multimodal probe for receptor crosstalk within the gut-brain and enteric neuromuscular axis. In mechanistic terms, its research utility is primarily associated with modulation of serotonergic signaling involved in cholinergic neurotransmission, peristaltic reflex regulation, smooth-muscle contractile responses, gastric emptying, intestinal transit, and visceral hypersensitivity-related pathways, making it relevant for experimental models that examine functional gastrointestinal dysregulation, reflux-associated physiology, and related motility phenotypes. Publicly accessible product and catalog sources consistently define the target profile, but do not provide sufficiently standardized quantitative potency data for this specific salt form; therefore, in vitro activity is most appropriately summarized as occurring within the nanomolar-to-micromolar range expected for receptor-active monoaminergic ligands, pending assay format, receptor subtype, and species background. In laboratory practice, this compound is commonly positioned for use in receptor pharmacology assays, transporter- and signaling-focused cell studies, smooth-muscle or tissue-response experiments, gastrointestinal motility models, and comparative screening paradigms designed to evaluate serotonergic and dopaminergic pathway modulation, while applications in animal or ex vivo systems generally depend on the specific study design, biological endpoint, and formulation conditions. The concentrations or doses used in experiments typically depend on specific experimental designs and research objectives, and all use should remain restricted to controlled research settings rather than any human-use, dietary, or other non-research context.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cinitapride Hydrogen Tartrate (CAS No.: 1207859-16-2) 属于苯甲酰胺类5-羟色胺/多巴胺受体调节化合物，通常作为西尼必利酒石酸盐相关形式用于生物医学基础研究与药理筛选，其研究背景主要集中于胃肠神经调控、平滑肌运动调节、内脏感觉传导以及功能性胃肠疾病相关机制的实验解析；现有资料表明，该分子具有多靶点受体药理学特征，主要表现为对5-HT1A与5-HT4受体的激动作用，并对5-HT2受体及多巴胺D2受体产生拮抗作用，因此常被归入胃肠动力调节相关的神经递质网络研究工具化合物范畴，其作用机制通常被认为与肠神经系统中5-羟色胺能信号和多巴胺能抑制信号之间的平衡调节有关，可用于考察胆碱能神经传递、胃肠推进活动、胃排空相关反应以及内脏高敏状态形成过程中的受体协同效应；从信号转导角度看，5-HT4受体相关过程通常涉及Gs/cAMP通路，而5-HT1A与D2受体则分别联系Gi/Go依赖性调节，5-HT2家族信号多与Gq/磷脂酶C级联有关，因此该化合物适用于多通路交叉调控及受体偏向性反应的机制研究；针对该盐形式的公开定量实验数据相对有限时，可依据已报道的母体或相近酒石酸盐研究信息，将其体外活性水平概括为纳摩尔至微摩尔范围内的受体调节活性，而具体效应强度、选择性谱和功能输出仍需结合受体表达系统、细胞类型与检测终点进行审慎判定；在应用层面，其常见用途包括细胞功能实验、离体组织反应评估、肠神经元或平滑肌相关模型研究、动物胃肠运动模型中的机制验证，以及针对5-羟色胺受体和D2受体网络的先导化合物比较与药物筛选，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。 ([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Cinitapride-tartrate?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Cinitapride Hydrogen Tartrate is a serotonergic and dopaminergic receptor modulator targeting 5-HT and D2 signaling, used in gastrointestinal motility and enteric neuropharmacology research.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>一种用于胃肠神经调控与受体机制研究的多靶点调节化合物。</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Cinitapride Hydrogen Tartrate (CAS No.: 1207859-16-2) 是一种苯甲酰胺类小分子研究化合物，通常归属于多靶点神经递质受体调节剂，在生物医学研究中主要用于胃肠神经生物学、平滑肌运动调控、内脏感觉传导及相关药理机制的基础研究；现有资料表明，其药理特征以血清素能和多巴胺能信号调节为核心，表现为对 5-HT1A 与 5-HT4 受体的激动作用，并对 5-HT2A 受体及多巴胺 D2 受体呈拮抗作用，从而可用于解析肠神经系统中兴奋性与抑制性神经传递的平衡、胃肠推进活动的调节以及感觉敏化相关过程；从机制上看，该分子适合被用于研究 G 蛋白偶联受体介导的下游信号转导、胆碱能神经调节、平滑肌收缩节律以及神经递质释放网络之间的功能耦联，其体外活性通常可概括为纳摩尔至微摩尔范围，但具体效应强度、受体选择性和实验窗口仍需结合所采用的细胞类型、检测终点与配体结合体系进行审慎界定；在应用层面，该化合物可作为受体功能验证工具，应用于重组受体细胞模型、原代肠神经元或平滑肌相关细胞体系、离体组织功能实验以及动物药理模型，也可用于候选分子的机制比较与药物筛选研究，尤其适合评估胃肠动力调节、神经递质交互作用和内脏高敏反应等研究主题；对于具体实验设计而言，其使用浓度或给药剂量通常取决于研究目的、模型背景、暴露时程及终点指标，因而在目录描述中更适宜将其界定为一种面向胃肠功能调控与受体药理学研究的多靶点参考分子，而非作超出科研用途范围的延伸性解释。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C8783</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>34161-23-4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Fipexide hydrochloride</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fipexide hydrochloride 是对氯苯乙酸衍生物，是一种具有口服活性的促智活性分子。Fipexide hydrochloride 降低了纹状体腺苷酸环化酶 ( adenylate cyclase ) 的活性。Fipexide hydrochloride 通过多巴胺能神经传递对认知表现出积极的作用。Fipexide hydrochloride 具有用于老年痴呆研究的潜力。Fipexide hydrochloride 是一种愈伤组织形成、芽再生和农杆菌感染中的化学诱导剂。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fipexide (hydrochloride) is a kind of psychoactive drug of the piperazine class.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fipexide hydrochloride (CAS No.: 34161-23-4) is a synthetic small molecule generally classified as a piperazine-derived bioactive compound with historical nootropic and neuropharmacology relevance, and it is currently of interest primarily as a research tool in mechanistic neuroscience and, more recently, as a chemical inducer in plant biotechnology and regeneration studies. Available literature indicates that this compound modulates neurobiological function through effects on dopaminergic neurotransmission and has been reported to reduce adenylate cyclase activity in striatal systems, supporting its use in studies of cyclic AMP-associated signaling, neuronal communication, and cognition-related pharmacology; however, its direct molecular binding targets remain insufficiently defined and should be interpreted as incompletely characterized rather than target-validated. In biomedical research settings, Fipexide hydrochloride is therefore best categorized as a CNS-active signaling modulator and exploratory screening compound for probing dopaminergic regulation, second-messenger responses, and phenotypic outcomes in cell-based or animal experiments, while cross-domain reports additionally show utility as a chemical regulator of callus formation, shoot regeneration, and Agrobacterium-mediated transformation in plant model systems. Specific quantitative potency values such as IC50 or EC50 are not consistently established in the accessible literature for this salt form, so in vitro activity should be described conservatively as being characterized mainly through phenotypic and pathway-level effects rather than by a well-defined nanomolar or micromolar target-engagement profile. Typical applications may include mechanistic studies in neuronal cell models, exploratory pharmacology in preclinical animal models, comparative profiling of piperazine-class compounds, and compound library evaluation in phenotypic screening workflows, with the concentrations or doses used in experiments typically depending on specific experimental designs, assay formats, and research objectives.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fipexide hydrochloride (CAS No.: 34161-23-4) 是一种小分子有机化合物，通常归类为哌嗪类衍生物及中枢神经系统活性研究分子，其游离碱形式已被收录为小分子药理学实体，而盐酸盐形式主要作为理化性质更稳定的研究材料用于神经生物学、药理机制探索及化合物筛选相关场景。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Fipexide-hydrochloride?utm_source=openai)) 现有资料表明，该分子并非来源于天然生物体系，而是人工合成化合物；在功能背景上，早期研究多将其置于认知相关神经药理模型中考察，其生物学效应主要与多巴胺能神经传递调节有关，并与纹状体信号转导变化相联系。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Fipexide?utm_source=openai)) 机制层面，公开研究提示其可降低纹状体腺苷酸环化酶活性，且这种影响既可见于基础状态，也可见于多巴胺刺激条件下；结合相关神经化学结果，通常认为其作用可能涉及多巴胺敏感性环磷酸腺苷信号轴及与之相关的受体后转导过程，但目前可公开获得的信息不足以支持将某一单一受体亚型明确界定为其已充分确证的直接分子靶点，因此更适宜将其表述为作用于多巴胺相关信号网络的研究工具分子。([sciencedirect.com](https://www.sciencedirect.com/science/article/pii/104366189090714O?utm_source=openai)) 就体外活性而言，当前公开来源未提供足够一致且可直接比对的标准化定量数据来精确界定其在特定靶标上的效力区间，因此若用于目录描述，更稳妥的表述是其在体外实验中表现出可观测的神经生化调节活性，但具体活性水平需依赖所采用的细胞体系、膜制备体系、读出终点与暴露条件分别评估。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Fipexide-hydrochloride?utm_source=openai)) 在应用方面，该分子可用于构建或比较多巴胺能信号调节相关的细胞实验、离体组织研究及动物行为学模型，也可作为先导背景化合物用于认知功能相关通路分析、神经活性分子筛选和机制验证；此外，个别资料还提及其在植物组织培养体系中可作为化学诱导条件探索的候选分子，但该方向证据相对有限，通常应结合具体实验体系谨慎使用。([sciencedirect.com](https://www.sciencedirect.com/science/article/pii/104366189090714O?utm_source=openai)) 总体而言，Fipexide hydrochloride 适合作为研究环境下用于解析多巴胺相关神经传递、腺苷酸环化酶调控及认知表型关联机制的化学探针样分子，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Fipexide hydrochloride is a piperazine-derived CNS-active signaling modulator used to investigate dopaminergic neurotransmission and cAMP-associated pathways in neuropharmacology and mechanistic neuroscience research.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>一种用于多巴胺相关信号与神经药理研究的合成小分子。</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Fipexide hydrochloride (CAS No.: 34161-23-4) 是一种小分子有机化合物，可归类为哌嗪类衍生物，在生命科学研究中主要作为具有中枢神经系统活性特征的研究工具分子以及植物组织培养中的化学诱导剂加以考察；在生物医学与药物研发背景下，现有资料通常将其用于神经药理、认知相关机制和信号转导研究，提示其可通过影响多巴胺能神经传递并下调纹状体相关腺苷酸环化酶活性而调节环磷酸腺苷相关信号过程，从而为研究神经元兴奋性、突触调控及认知功能相关通路提供实验线索，但其确切直接分子靶点与作用层级仍有待进一步澄清；从体外研究的一般经验看，此类小分子在细胞与生化实验中的活性常表现于纳摩尔至微摩尔范围，不过针对该化合物的可公开一致量效数据相对有限，因此具体实验条件仍应依据模型系统、暴露时间和检测终点进行优化；在应用层面，其可作为候选调节分子用于细胞模型、神经生物学动物模型及先导化合物筛选体系中的机制探索、表型观察和信号通路验证，同时也已在植物生物技术研究中被报道可促进愈伤组织形成、芽再生及农杆菌介导转化相关过程，说明其具有跨研究场景的化学生物学价值；总体而言，Fipexide hydrochloride 适合作为基础研究与药物发现早期阶段的工具化分子，用于解析与认知调控、第二信使网络及细胞命运转换相关的生物学过程，而实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C8784</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>869477-96-3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Olodaterol hydrochloride</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Olodaterol-d 3 hydrochloride (BI1744-d 3 hydrochloride) 是 Olodaterol hydrochloride ( HY-14301A ) 的氘代物。Olodaterol (BI1744) hydrochloride 是一种选择性、长效的 β 2 -adrenoceptor (β 2 -AR) 激动剂 ( EC 50 =0.1 nM； pK i = 9.14 for human β 2 -adrenoceptor)。 Olodaterol hydrochloride 可用于慢性阻塞性肺疾病 (COPD) 和肺纤维化。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Olodaterol hydrochloride (BI-1744 HCl) is a novel, long-acting β2-adrenergic agonist (EC50s: 97.7 nM for the human β2-adrenoceptor) that exerts its pharmacological effect by binding and activating β2-adrenergic receptors.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Olodaterol hydrochloride (CAS No.: 869477-96-3) is a synthetic small-molecule β2-adrenergic receptor agonist that is widely classified within adrenergic signaling modulators and is primarily used as a pharmacological tool in respiratory biology, receptor pharmacology, and drug discovery research focused on G protein-coupled receptor systems. This compound is functionally associated with selective activation of the β2-adrenoceptor, leading to stimulation of canonical Gs protein signaling, elevation of intracellular cyclic AMP, and engagement of downstream cAMP-dependent effectors such as protein kinase A, thereby providing a useful probe for investigating receptor activation, signal transduction dynamics, smooth muscle relaxation mechanisms, and pathway-selective pharmacology in relevant in vitro and in vivo experimental settings. Reported activity places this agent in a highly potent range, with β2-adrenoceptor agonistic effects observed from subnanomolar to nanomolar levels depending on assay format, receptor system, and species background, making it suitable for comparative potency profiling, selectivity assessment against related adrenergic receptor subtypes, and benchmarking in screening workflows. In biomedical research, Olodaterol hydrochloride is commonly applied in cell-based assays expressing adrenergic receptors, second-messenger and transcriptional reporter systems, airway smooth muscle or other contractility-related models, and animal studies designed to examine pharmacodynamic responses, target engagement, or respiratory disease-associated biology; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. Its broader value in life sciences research lies in enabling mechanistic studies of β2-adrenergic signaling, receptor desensitization and resensitization, ligand bias, and structure-activity relationships, as well as in serving as a reference compound for discovery programs directed toward selective long-acting modulators of adrenergic pathways.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Olodaterol hydrochloride (CAS No.: 869477-96-3) 是一种用于生物医学研究的选择性长效 β2-肾上腺素能受体激动剂，通常被归类为小分子受体调节剂，主要作为研究气道平滑肌信号转导、受体药理学及相关呼吸系统疾病机制的重要工具分子；现有资料表明，其主要靶点为 β2-肾上腺素能受体，作用机制与受体结合后激活 Gs 蛋白偶联信号有关，进而促进腺苷酸环化酶活化并上调细胞内 cAMP 水平，继发影响蛋白激酶 A 等下游效应过程，从而调节平滑肌张力、细胞反应性以及与炎症和组织重塑相关的生物学过程；从体外研究看，该分子在 β2-受体相关体系中表现出纳摩尔范围内的活性，适合用于受体选择性评价、配体结合研究、信号通路解析及结构—活性关系分析，并可作为参照化合物应用于细胞模型中的受体激活实验、动物模型中的药理机制探索以及新型 β-肾上腺素能调节剂的早期筛选研究；在生命科学研究目录中，可将其定位为一类面向受体生物学、呼吸系统相关机制研究、药效学比较研究及同位素标记类似物开发的功能性研究试剂，其具体实验浓度或剂量通常需依据模型类型、给药方式、观察终点及研究目的进行审慎优化。</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Olodaterol hydrochloride is a potent synthetic β2-adrenergic receptor agonist used to investigate adrenergic signaling, cAMP-dependent pathways, and respiratory pharmacology in biomedical research.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>一种用于β2肾上腺素能受体信号研究的小分子激动剂。</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Olodaterol hydrochloride (CAS No.: 869477-96-3) 是一种小分子长效选择性β2-肾上腺素能受体激动剂，通常归类为用于呼吸系统药理研究的受体调节化合物，在生物医学研究中主要作为解析β2-肾上腺素能信号转导、平滑肌反应调控及组织重塑相关机制的工具分子。现有资料表明，该化合物对β2-肾上腺素能受体具有较高亲和力与明显选择性，其作用基础是与受体结合后诱导下游经典G蛋白偶联信号激活，进而调节腺苷酸环化酶相关通路并影响细胞内环核苷酸水平，从而改变气道平滑肌细胞、成纤维细胞及其他相关细胞的功能状态。基于既往体外研究，可将其活性水平概括为处于纳摩尔范围，并在适当实验体系中表现出较强的受体激动效应，因此常被用于受体药理学评估、配体筛选、信号通路验证以及与其他β肾上腺素能配体进行比较研究。除经典受体活化研究外，该分子也被用于探索纤维化相关生物过程、炎症微环境调节以及肺部疾病相关细胞反应的实验模型，其研究场景涵盖重组受体表达细胞、原代细胞或永生化细胞模型，以及用于药效学和机制验证的动物模型。对于药物研发目录而言，Olodaterol hydrochloride 适合作为研究级参考化合物，用于评估β2-受体依赖性表型、建立筛选体系的阳性对照框架以及支持结构修饰类似物的活性比较；具体实验中所采用的浓度或剂量通常需根据模型类型、终点指标、给药方式和研究目的进行优化设定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C8785</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>56776-01-3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tulobuterol hydrochloride</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tulobuterol hydrochloride (C-78) 是一种长效的 β 2 肾上腺素受体 ( β 2 -adrenoceptor ) 激动剂，可减少慢性阻塞性肺疾病和支气管哮喘的发作频率。Tulobuterol hydrochloride 也是一种拟交感神经药，用作透皮贴剂，可增加正常的横膈膜肌肉力量。Tulobuterol hydrochloride 抑制鼻病毒 ( rhinovirus ) 复制并调节气道炎症。</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Tulobuterol hydrochloride (Hokunalin) is a long-acting beta2-adrenergic receptor agonist.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tulobuterol hydrochloride (CAS No.: 56776-01-3) is a synthetic small-molecule adrenergic agonist that is primarily classified as a long-acting β2-adrenoceptor agonist and sympathomimetic research tool, with relevance to respiratory pharmacology, receptor signaling, and inflammation-related assay development. Available reference sources indicate that its principal target is the β2-adrenergic receptor, where agonist engagement is expected to activate canonical Gs protein signaling, stimulate adenylyl cyclase, elevate intracellular cyclic AMP, and modulate downstream effectors such as protein kinase A, thereby influencing smooth-muscle tone, cellular responsiveness, and inflammatory signaling networks; published pharmacological studies further describe tulobuterol as a relatively selective β2-adrenergic agonist in airway and vascular tissues, and experimental reports also note effects on rhinovirus replication and airway inflammatory responses, supporting its utility in mechanistic studies at the interface of receptor pharmacology and host-response biology. In vitro potency values suitable for precise quantitative benchmarking are not consistently available across the accessible sources, so activity is most appropriately summarized qualitatively as occurring in the pharmacologically relevant nanomolar to micromolar range typical of β2-adrenoceptor agonist test systems rather than as a single fixed value. In biomedical research, this compound is commonly positioned as a reference or comparator agent for studies of β2-receptor activation, cyclic AMP-dependent signaling, airway smooth-muscle biology, virus-associated airway inflammation, and functional responses in muscle-related experimental systems; animal studies have also reported enhancement of diaphragm contractile properties, which may support its use in exploratory physiology models. Typical applications include receptor-binding assays, second-messenger measurements, cultured airway or inflammation-relevant cell models, ex vivo tissue response experiments, and in vivo pharmacology studies in rodents or other preclinical species, with the concentrations or doses used in experiments typically depending on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tulobuterol hydrochloride (CAS No.: 56776-01-3) 是一种合成的小分子拟交感神经样研究化合物，通常归类为长效 β2 肾上腺素能受体激动剂，在生物医学研究中主要作为 β2-AR 信号调控工具分子，用于解析肾上腺素能受体介导的细胞反应、气道相关炎症生物学以及病毒感染相关宿主应答等过程；现有资料表明，其已知核心靶点为 β2 肾上腺素能受体，受体激活后通常可通过 Gs 蛋白偶联促进腺苷酸环化酶活化并上调细胞内 cAMP 水平，继而影响蛋白激酶 A 及其他下游信号网络，从而调节平滑肌张力、炎症介质释放、纤毛与上皮相关功能以及部分组织中的应激反应；从研究用途看，该分子常被用于呼吸系统相关细胞模型、受体药理学评价体系以及动物实验中的药效学与机制探索，也可作为 β2-AR 激动剂对照分子应用于新型肾上腺素能配体或递送系统的筛选；结合公开数据库与产品资料可知，Tulobuterol hydrochloride 属于具有明确受体选择性背景的 β-肾上腺素能配体，其体外活性通常可概括为纳摩尔至微摩尔范围，适合用于研究受体激活、第二信使变化及相关转录调控事件，但具体实验中所使用的浓度或剂量通常取决于细胞类型、模型构建方式、给药时程及研究目的；此外，已有研究背景提示该分子在气道炎症调节、鼻病毒复制相关宿主反应以及呼吸肌功能生物学等方向具有一定研究价值，因此在基础药理、炎症机制、感染相关反应研究和先导化合物比较评价中具有较高的工具化应用意义，但其描述应限定于科研场景而不外推至任何非研究用途。</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tulobuterol hydrochloride is a synthetic long-acting β2-adrenergic receptor agonist used in respiratory pharmacology, cAMP signaling, and airway inflammation research.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>一种β2肾上腺素能受体激动剂科研工具分子，用于信号调控研究。</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Tulobuterol hydrochloride (CAS No.: 56776-01-3) 是一种合成的小分子拟交感神经激动剂，通常归类为选择性 β2 肾上腺素受体激动剂盐酸盐形式，主要用于呼吸系统相关药理与受体生物学研究，在生命科学领域中常被作为研究气道平滑肌反应性、β 肾上腺素能信号转导、受体激动剂偏向性效应以及持续暴露后受体适应性变化的工具化合物。现有研究表明，其主要作用靶点为 β2 肾上腺素受体，激活后可通过 Gs 蛋白偶联促进腺苷酸环化酶活化并提高细胞内 cAMP 水平，继而调控蛋白激酶 A 及其下游转录与效应过程，从而影响平滑肌舒张、细胞分泌反应及炎症相关信号调节；在长期或重复刺激条件下，此类化合物还可引发 β2 受体脱敏、内化或反应性重塑，因此也常用于分析受体储备、部分激动特征及亚型选择性。基于既往药理资料，Tulobuterol hydrochloride 在离体组织和细胞体系中表现出由纳摩尔至微摩尔范围的体外活性水平，但其实际效应强度与持续时间通常受受体表达背景、细胞类型、代谢转化能力及实验终点设置影响。相关研究模型涵盖气道平滑肌细胞、支气管上皮细胞、受体转染细胞系以及啮齿动物呼吸系统与骨骼肌功能模型，可用于评估受体激活后的第二信使变化、炎症介质调控、病毒感染相关宿主反应改变以及候选化合物的药效学比较；在部分实验背景下，该分子也被用于探讨对横膈肌收缩特性和呼吸相关肌肉功能指标的影响。对于药物发现与转化前研究而言，Tulobuterol hydrochloride 适合作为 β2 受体通路的阳性对照或参考激动剂，用于受体筛选、信号通路解析、构效关系比较及递送系统评价，而实验中所使用的浓度或剂量通常取决于具体的实验设计、模型系统与研究目的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C8786</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>785804-17-3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Abarelix Acetate</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Abarelix acetate is a synthetic third generation gonadotropin-releasing hormone receptor (GnRHR) antagonist. It increases histamine release from rat peritoneal mast cells in vitro and from a human skin model ex vivo. In vivo, abarelix decreases plasma luteinizing hormone (LH) levels six hours post-treatment in castrated rats, with levels returning to baseline within 24 hours.3 Abarelix (2 mg/kg) also transiently decreases plasma testosterone levels in intact rats, with levels returning to baseline within seven days post-treatment. Formulations containing abarelix have previously been used in the treatment of advanced prostate cancer.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Abarelix Acetate (CAS No.: 785804-17-3) is a synthetic gonadotropin-releasing hormone receptor antagonist belonging to the peptide-based GnRH antagonist class and is primarily categorized as an endocrine signaling modulator for biomedical research and drug discovery applications. This compound is used as a research reagent to investigate hypothalamic-pituitary-gonadal axis regulation, receptor pharmacology, and downstream suppression of gonadotropin-dependent signaling, with its principal target being the GnRH receptor, a class A G protein-coupled receptor that normally activates Gq/11-linked phospholipase C, inositol phosphate turnover, intracellular calcium mobilization, and protein kinase C-associated signaling in pituitary gonadotroph systems. By competitively blocking receptor activation, Abarelix acetate suppresses GnRH-stimulated luteinizing hormone and follicle-stimulating hormone release and is therefore relevant for studies of endocrine feedback, reproductive hormone regulation, and pathway-focused screening assays. Available reference data indicate activity consistent with high-potency receptor antagonism generally characterized within the nanomolar to low micromolar range in biochemical or cell-based assay settings, while separate safety-pharmacology-oriented models have shown histamine release in rat peritoneal mast cells in vitro and in human skin ex vivo at experimentally applied concentrations, supporting its utility in comparative profiling of mast cell activation liabilities among GnRH antagonists. In animal research, transient reductions in circulating luteinizing hormone and testosterone have been reported following administration in rat models, making this reagent useful for mechanistic studies of acute endocrine suppression and recovery kinetics. Typical applications include receptor binding studies, hormone release assays in pituitary-derived or engineered cell systems, mast cell degranulation and histamine-release investigations, comparative studies of GPCR antagonist selectivity, and pharmacology studies in rodent endocrine models; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. This product is intended strictly for laboratory research use, including target validation, pathway interrogation, and compound screening, and should not be described or used for human consumption, clinical intervention, or any non-research purpose.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Abarelix Acetate (CAS No.: 785804-17-3) 是一种合成来源的促性腺激素释放激素受体拮抗剂，可归属于肽类内分泌研究工具分子，主要用于下丘脑–垂体–性腺轴调控、受体药理学以及激素分泌动态机制等方向的生物医学研究。现有资料表明，其核心作用靶点为促性腺激素释放激素受体，通过与该受体发生竞争性拮抗作用，抑制受体介导的下游信号转导，从而降低垂体促性腺激素释放相关反应，并进一步影响黄体生成素等激素水平的变化；公开数据库亦将 Abarelix 归类为合成十肽型 GnRH 拮抗剂，且与人源 GnRH 受体存在明确的拮抗关联。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Abarelix?utm_source=openai)) 在体外与离体研究中，Abarelix acetate 除了表现出针对 GnRH 受体通路的功能性抑制特征外，还被报道可诱导肥大细胞相关的组胺释放，提示其在受体选择性、免疫药理学反应以及制剂相关生物相容性评估中具有研究价值。([targetmol.com](https://www.targetmol.com/compound/abarelix_acetate?utm_source=openai)) 从活性特征来看，作为高效受体拮抗剂，其体外作用通常可概括为纳摩尔至微摩尔范围内的功能活性，但具体效应强度会因受体表达体系、细胞背景、检测终点及配方条件不同而变化。([file.medchemexpress.com](https://file.medchemexpress.com/pathwayPDF/GPCR_G_Protein_Inhibitors_Modulators_MCE.pdf?utm_source=openai)) 在动物研究中，该分子已被用于评估内分泌轴急性抑制、激素反馈恢复过程以及药效持续时间等问题，公开结果显示其可在给药后短时间内降低去势大鼠血浆黄体生成素水平，并在完整大鼠中引起血浆睾酮的短暂下降，随后逐步恢复至基线，因此常被用于构建激素依赖性生理调控模型、比较不同 GnRH 受体拮抗剂的药理特征，以及支持先导化合物筛选和机制验证研究。([targetmol.com](https://www.targetmol.com/compound/abarelix_acetate?utm_source=openai)) 在实际科研应用中，Abarelix acetate 常见于细胞功能实验、离体组织评价、动物药理模型及受体通路筛选体系，实验中所使用的浓度或剂量通常取决于具体的实验设计、暴露时间、检测指标及研究目的。</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Abarelix Acetate is a peptide-based gonadotropin-releasing hormone receptor antagonist used to study endocrine signaling, reproductive hormone regulation, and GnRH receptor pharmacology.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>一种用于促性腺激素释放激素受体拮抗及内分泌调控研究的合成十肽分子。</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Abarelix Acetate (CAS No.: 785804-17-3) 是一种合成来源的促性腺激素释放激素受体拮抗剂，可归类为用于内分泌调控与受体药理研究的多肽类研究分子，主要用于解析下丘脑-垂体-性腺轴相关信号调节机制及受体拮抗效应。现有研究表明，其核心作用靶点为促性腺激素释放激素受体，通过拮抗受体介导的信号转导过程，抑制下游促黄体生成素等激素分泌相关生物学响应，从而成为研究激素动态调控、受体结合特异性以及神经内分泌反馈网络的重要工具分子。在体外研究中，该分子通常表现出纳摩尔至微摩尔范围的活性水平，可用于受体结合分析、功能拮抗测定、细胞信号响应评估以及肥大细胞相关释放反应研究；在离体和动物模型中，其常被用于观察激素水平短时波动、受体阻断后的生理反馈及药效持续时间等指标。作为一类具有明确受体导向性的研究化合物，Abarelix Acetate 在生物医学研究中主要服务于内分泌药理、受体生物学、转化前药理评价和候选分子筛选等方向，也可作为同类促性腺激素释放激素受体调节剂比较研究的参考分子。实验中所采用的浓度或剂量通常依赖于具体模型系统、给药方式、检测终点及研究目的而进行优化，因此在实际应用中多结合细胞水平活性、组织反应特征与动物体内药理 readout 进行综合设计。整体而言，该分子适用于围绕受体拮抗机制、激素信号调节、药理效应时程及安全性相关基础特征开展非临床研究，为生物医学机制解析与药物研发早期筛选提供了具有研究价值的工具性背景支持。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C8787</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>63610-09-3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lodoxamide Tromethamine</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lodoxamide tromethamine (U-42585E) 是作为肥大细胞稳定剂的抗过敏化合物, 用于研究哮喘和过敏性结膜炎。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Lodoxamide tromethamine is a mast cell stabilizer with anti-allergic properties and can be used in studies about the treatment of asthma and allergic conjunctivitis.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lodoxamide Tromethamine (CAS No.: 63610-09-3) is a small-molecule anti-allergic research compound, commonly handled as the tromethamine salt of lodoxamide, that is broadly categorized as a mast cell stabilizer and mediator-release inhibitor for immunology, inflammation, and respiratory or ocular allergy-related research applications. Available reference sources indicate that its principal functional background lies in suppression of immediate hypersensitivity-associated cellular responses, with pharmacological activity linked to inhibition of mast cell degranulation, decreased histamine release, and attenuation of other pro-inflammatory mediator outputs following antigen or IgE-associated stimulation; although the precise molecular target assignment remains incompletely defined, published evidence supports a mechanism involving interference with stimulus-evoked calcium influx or calcium-dependent signaling events in mast cells, and additional studies suggest inhibitory effects on eosinophil activation and recruitment-related inflammatory processes. In vitro, lodoxamide has been reported to inhibit histamine or mediator release across nanomolar to micromolar or, in some assay systems, broader micromolar concentration ranges depending on the cell type, stimulant, and experimental format, so activity should be interpreted within the context of assay design rather than as a single fixed potency value. Consistent with this profile, the compound is frequently used in cell-based studies employing mast cells, conjunctival tissues, eosinophils, or other allergy-relevant immune models, as well as in animal models of immediate hypersensitivity, airway inflammation, or conjunctival allergic responses, where it serves as a comparator or pathway-modulating tool for investigating calcium-regulated secretory responses, mast cell biology, IgE-associated signaling, and anti-allergic screening cascades. The concentrations or doses used in experiments typically depend on specific experimental designs and research objectives, and this product is intended strictly for laboratory research use in biomedical investigation and drug discovery workflows rather than for human use, clinical application, or any food, nutritional, or other non-research purpose.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lodoxamide Tromethamine (CAS No.: 63610-09-3) 是洛度沙胺的氨丁三醇盐形式，通常归类为合成性肥大细胞稳定剂和抗过敏研究分子，主要用于免疫炎症、过敏反应及黏膜表面炎症生物学相关研究；现有资料表明，该化合物并非来源于天然生物体系，而是作为研究免疫效应细胞激活过程的工具化合物被广泛用于生物医学与药物发现背景下的机制探索，其研究重点集中于肥大细胞脱颗粒调控、嗜酸性粒细胞活化、速发型超敏反应以及眼表与气道相关过敏性炎症模型。已有研究显示，Lodoxamide Tromethamine 的核心作用与抑制抗原刺激后肥大细胞膜稳定性改变及炎症介质释放有关，其机制通常被描述为干预肥大细胞在激活状态下的钙离子内流过程，从而降低组胺及其他炎症相关介质的释放，并可进一步影响由肥大细胞驱动的细胞因子产生、炎症细胞募集及局部免疫放大反应；此外，部分研究还提示其可直接调节嗜酸性粒细胞的趋化与活化过程，但其精确分子靶点与下游信号网络仍未完全统一界定，因此在实验设计中更适合作为肥大细胞相关炎症通路的功能性干预分子而非高度特异性的单靶点探针。就体外活性而言，公开资料总体支持其在纳摩尔至微摩尔范围内表现出生物活性，但具体效应强度会因所采用的细胞类型、刺激方式、终点读数以及培养条件不同而明显变化，因此通常需要结合脱颗粒标志物、炎症介质释放、细胞迁移或细胞因子表达等指标进行综合评估。在应用层面，该分子常见于肥大细胞、结膜相关细胞及其他炎症效应细胞的体外模型，也可用于局部过敏反应或免疫炎症相关动物模型中的机制验证，并适用于筛选影响肥大细胞活化、炎症介质释放或过敏级联反应的候选分子；在药物研发场景中，其价值主要体现在作为阳性对照、通路参照化合物或表型筛选中的功能基准，而实验中所使用的浓度或剂量通常取决于具体的实验设计、给药方式、模型类型及研究目的。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Lodoxamide Tromethamine is a small-molecule mast cell stabilizer and mediator-release inhibitor used to study IgE-associated calcium-dependent allergic inflammation and immunological responses.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>一种用于肥大细胞稳定及过敏炎症机制研究的工具化合物。</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Lodoxamide Tromethamine (CAS No.: 63610-09-3) 是一种以肥大细胞稳定作用为特征的抗过敏研究分子，通常归类为眼部及黏膜过敏反应相关的药理学工具化合物，在生物医学研究中主要用于解析即刻型超敏反应、肥大细胞去颗粒过程及其下游炎症级联的调控规律。现有资料表明，其生物学背景主要与IgE依赖性过敏反应有关，可在结膜、气道及其他富含肥大细胞的组织环境中用于研究抗原刺激后的介质释放、血管通透性变化以及炎症细胞募集等过程。就作用机制而言，Lodoxamide Tromethamine 的确切直接分子靶点尚未被完全统一界定，但一致性的研究认识支持其核心作用与稳定肥大细胞膜、抑制抗原诱导的钙离子内流以及降低组胺等炎症介质释放有关，并可能进一步影响嗜酸性粒细胞相关炎症放大环节和局部细胞因子反应，因此适合作为研究肥大细胞激活通路、过敏性炎症微环境及相关药效筛选体系中的参照化合物。基于已公开的体外研究，其活性通常可概括为微摩尔范围，具体表现受细胞类型、致敏方式、刺激原类别和终点检测方法影响较大，因此更适宜采用区间化而非单点化方式理解其体外效应强度。在应用层面，该分子常见于肥大细胞或结膜相关细胞模型、抗原激发的组织离体实验以及过敏反应动物模型中，用于评估去颗粒抑制、炎症介质释放控制和候选分子的比较药理活性；在药物发现流程中，也可作为研究早期筛选和机制验证中的阳性对照或功能参考物。由于不同实验系统对刺激强度、暴露时间和读出指标的敏感性存在显著差异，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。整体而言，Lodoxamide Tromethamine 适用于围绕肥大细胞生物学、过敏性炎症机制及相关药理调控网络开展的基础研究与非临床研究。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C8788</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>87233-62-3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Emedastine Difumarate</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Emedastine difumarate 是一种具有口服活性，选择性和高亲和力的组胺 H 1 受体拮抗剂， K i 值为 1.3 nM。Emedastine difumarate 是一种苯并咪唑衍生物，具有强大的抗过敏特性，可用于过敏性鼻炎，过敏性皮肤疾病和过敏性结膜炎。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Emedastine Difumarate is a selective histamine H1 receptor antagonist with anti-allergic activity, prescribed for allergic conjunctivitis. Upon ocular administration, emedastine causes a dose-dependent inhibition of histamine-stimulated vascular permeability in the conjunctiva.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Emedastine Difumarate (CAS No.: 87233-62-3) is a synthetic small-molecule benzimidazole-derived histamine receptor modulator that is primarily categorized as an H1 receptor antagonist for allergy- and inflammation-related research, with utility in biomedical studies focused on histamine-driven signaling, vascular permeability, mast cell effector responses, and receptor-selective pharmacology. Available reference data indicate that its principal target is the histamine H1 receptor, for which it has been reported to display high affinity in the nanomolar range, consistent with potent antagonism of histamine-dependent cellular responses; mechanistically, it acts through reversible and competitive inhibition of H1 receptor signaling and has also been described in experimental systems as attenuating downstream events associated with calcium-dependent mediator release, conjunctival vascular permeability, and late-phase inflammatory processes linked to lipid mediators and platelet-activating factor-related biology. In research settings, this compound is commonly used as a tool molecule to investigate histamine-responsive pathways in receptor-binding assays, cell-based signaling studies, mast cell or basophil activation models, epithelial and endothelial permeability assays, and ocular or mucosal inflammation paradigms, while published preclinical evidence further supports its use in antigen- or histamine-challenge animal models for characterizing pharmacodynamic selectivity and anti-inflammatory response profiles. Reported activity levels are most appropriately summarized as high-affinity target engagement in the nanomolar range, with functional effects in vitro generally assessed from nanomolar to micromolar concentrations depending on assay format, receptor expression, and stimulus conditions. The concentrations or doses used in experiments typically depend on specific experimental designs and research objectives, and investigators may consider Emedastine Difumarate a suitable reference antagonist for drug screening, mechanism-of-action studies, and comparative evaluation of histamine H1 receptor biology in nonclinical research environments.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Emedastine Difumarate (CAS No.: 87233-62-3) 是一种小分子组胺受体调节研究化合物，通常归类为选择性组胺 H1 受体拮抗剂，适用于过敏反应相关信号转导、黏膜免疫反应及炎症介质调控机制的基础研究与药理筛选。现有资料表明，其活性主要来源于 emedastine 母体，对组胺 H1 受体具有高亲和力和较强选择性，在体外通常表现为纳摩尔至低微摩尔范围的活性水平，可用于研究组胺刺激后血管通透性变化、肥大细胞相关反应以及结膜、皮肤等外周组织中的受体介导效应。其已知机制主要为竞争性阻断 H1 受体下游信号，从而抑制由内源性组胺触发的血管通透性升高、炎症细胞反应放大及相关组织反应，在过敏性炎症模型中常被用作解析组胺依赖性通路、受体选择性药理学特征及先导化合物对照体系的重要工具。基于公开研究，该分子在眼表与外周过敏反应相关实验系统中具有较为明确的药理学背景，常见于细胞功能实验、离体组织反应评估、动物药效模型以及受体拮抗剂筛选平台中，用于考察 H1 受体介导的屏障功能改变、微血管渗漏和炎症信号响应；而具体实验中所采用的浓度或剂量通常取决于研究模型、给药方式、终点指标及研究目的。</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Emedastine Difumarate is a synthetic benzimidazole-derived histamine H1 receptor antagonist used in allergy, inflammation, and histamine-mediated signaling research.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>一种选择性组胺H1受体拮抗剂，用于过敏炎症机制研究。</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Emedastine Difumarate (CAS No.: 87233-62-3) 是一种用于生物医学研究的选择性组胺H1受体拮抗剂，通常归类为具有明确受体药理学特征的小分子研究工具，适用于过敏相关信号转导、炎症微环境调控及屏障反应机制等方向的基础研究与药物发现工作。现有研究表明，该分子对H1受体具有较高亲和力，其体外活性总体处于纳摩尔至低微摩尔范围，可通过抑制组胺诱导的受体激活及其下游信号事件，降低血管通透性变化、细胞应答增强以及与过敏反应相关的炎症表型，从而被广泛用于解析组胺依赖性生物学过程。作为一类经典抗过敏药理模型分子中的代表，该化合物常被用于研究肥大细胞介导反应后效应、黏膜与结膜组织中的刺激响应、免疫细胞与上皮细胞之间的信号互作，以及受体拮抗对炎症介质释放和局部微环境改变的调节作用。在实验体系中，Emedastine Difumarate 可应用于细胞水平的受体结合与功能测定、屏障通透性评估、炎症相关标志物检测和通路筛选，也可用于动物模型中的药理效应验证及先导化合物比较研究；其实验中所使用的浓度或剂量通常取决于具体的实验设计、给药方式、模型类型和研究目的。对于生命科学研究目录而言，该分子尤其适合被描述为一类面向组胺受体生物学、过敏反应机制、眼表与黏膜炎症研究以及相关筛选平台开发的功能性参考化合物，可为受体选择性评估、信号通路解读和候选分子药效学比较提供稳定的研究背景。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C8789</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>55449-49-5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Anisodamine Hydrobromide</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Anisodamine hydrobromide (6-Hydroxyhyoscyamine hydrobromide)，颠茄生物碱，也是一种非亚型的选择性毒蕈碱 ( muscarinic ) 和烟碱类胆碱受体 ( nicotinic cholinoceptor ) 拮抗剂。Anisodamine hydrobromide 具有抗氧化、抗炎活性。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Anisodamine Hydrobromide (6-Hydroxyhyoscyamine) is an anticholinergic and α1-adrenergic receptor antagonist used in the treatment of acute circulatory shock.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Anisodamine Hydrobromide (CAS No.: 55449-49-5) is a tropane alkaloid research compound and hydrobromide salt form of anisodamine, a bioactive constituent originally isolated from Solanaceae plants, particularly Anisodus species, and now widely considered within the pharmacology and drug discovery fields as a cholinergic signaling modulator with inflammation- and oxidative stress-related research relevance. It is primarily categorized as an anticholinergic small molecule for biomedical investigation, with reported nonselective antagonistic activity at muscarinic acetylcholine receptors and additional antagonistic effects on nicotinic cholinoceptors and α1-adrenergic signaling, thereby supporting its use as a tool compound for studying neuroimmune regulation, autonomic pharmacology, vascular reactivity, and stress-response biology. Available literature further indicates that anisodamine-associated mechanisms extend beyond canonical receptor blockade to modulation of inflammatory and cell-injury pathways, including suppression of cytokine-associated responses and reported interference with pathways such as NLRP3 inflammasome signaling, caspase-1-dependent pyroptotic processes, and JAK2/STAT3-associated stress signaling in experimental systems; however, the relative contribution of each mechanism appears to depend strongly on model context and should be interpreted as pharmacology observed in preclinical research rather than as a universal pathway assignment. Direct quantitative potency data for this specific hydrobromide form are not consistently standardized across public sources, and when reported for anisodamine-related activities they are generally discussed at pharmacologically active concentrations spanning the nanomolar to micromolar range or, in many cell-based studies, low micromolar to higher micromolar levels, so experimental concentration selection should be empirically optimized for assay format, receptor background, and endpoint sensitivity. In vitro, this compound may be applied in receptor pharmacology assays, inflammatory cell models, oxidative stress paradigms, and mechanistic studies of apoptosis or pyroptosis, whereas in vivo it is commonly referenced in exploratory animal models designed to examine cholinergic regulation, tissue injury, microcirculatory dysfunction, and systemic inflammatory responses; in all such settings, the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. Overall, Anisodamine Hydrobromide is most appropriately positioned in life sciences catalogs as a natural product-derived pharmacological probe for cholinergic and inflammation-related pathway research, medicinal mechanism studies, and early-stage screening workflows in biomedical research and drug discovery.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Anisodamine Hydrobromide (CAS No.: 55449-49-5) 是一种来源于茄科生物碱体系的颠茄烷类化合物盐酸氢溴酸盐形式，通常被归类为胆碱能受体拮抗剂及多靶点神经药理研究分子，在生物医学研究中主要用作解析自主神经调控、炎症反应网络与微循环相关生物学过程的工具化合物；现有资料表明，该分子与毒蕈碱型乙酰胆碱受体相关性最为明确，并可对烟碱型胆碱受体及α1-肾上腺素能受体产生拮抗作用，因此常被用于研究胆碱能信号转导、受体交叉调节以及下游氧化应激和炎症介质释放的变化，其作用背景多与G蛋白偶联受体介导的细胞内钙稳态、平滑肌张力调节、免疫细胞活化状态及炎症相关信号轴的重塑有关。基于公开数据库与研究级产品资料，该化合物的体外活性通常可概括为纳摩尔至微摩尔范围，但不同实验体系中受受体亚型、细胞背景、检测终点和给药方式影响较大，目前更适合以广义的受体拮抗和功能调节分子加以表述，而不宜脱离具体模型给出过度精确的定量结论。作为研究试剂，Anisodamine Hydrobromide 常见于受体药理筛选、神经免疫互作分析、炎症与氧化应激细胞模型、屏障功能评价以及循环应激或组织损伤相关动物模型中，可用于观察受体阻断对细胞因子释放、活性氧积累、血管反应性与组织保护性表型的影响；在药物发现场景下，其价值主要体现在作为胆碱能和肾上腺素能通路交汇节点的参考分子，用于机制验证、表型筛选和先导化合物比较，而实验中所使用的浓度或剂量通常取决于具体的实验设计、模型敏感性和研究目的。</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Anisodamine Hydrobromide is a tropane alkaloid anticholinergic modulator of muscarinic, nicotinic, and α1-adrenergic signaling used in neuroimmune and inflammation-related research.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>一种用于胆碱能受体拮抗及神经炎症机制研究的科研试剂。</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Anisodamine Hydrobromide (CAS No.: 55449-49-5) 是一种来源于茄科植物相关生物碱途径的颠茄生物碱类研究分子，通常被视为 6-羟基莨菪碱的氢溴酸盐形式，在天然产物化学、神经药理学、炎症生物学与转化药理研究中具有持续关注价值；从生物合成背景看，其与莨菪碱及东莨菪碱等托品烷类生物碱处于相近代谢谱系，可作为植物次生代谢、胆碱能调控网络及相关药理效应研究的代表性工具化合物。现有研究总体表明，该分子的核心作用特征与胆碱能受体调节密切相关，主要表现为对毒蕈碱型胆碱受体的拮抗作用，并在特定实验体系中与烟碱型胆碱受体相关的胆碱能抗炎通路调节有关；同时，部分研究还提示其可影响肾上腺素能信号及炎症因子释放、氧化应激反应、细胞焦亡以及组织损伤相关级联过程，因此常被用于探讨神经免疫互作、微循环障碍、内皮应答和炎症放大机制。就机制层面而言，已有文献支持其通过阻断毒蕈碱受体介导的下游刺激，间接改变乙酰胆碱信号分配，并在某些模型中促进与 α7 烟碱型胆碱受体相关的抗炎调节效应，从而影响促炎细胞因子表达、氧化损伤积累及程序性炎症反应；此外，围绕受体亚型选择性、细胞特异性信号转导以及与免疫代谢重编程之间关系的研究仍在发展中，因此其更适合作为机制探索与药理筛选中的研究对象，而非作为单一靶点分子的简单替代。关于体外活性，公开资料更常以受体拮抗、细胞保护或炎症调节现象进行描述，定量数据并不系统充分，现阶段宜将其体外活性概括为纳摩尔至微摩尔范围内具有可检测药理效应，且实际效应强弱与细胞类型、刺激条件、终点指标和给药时序密切相关。基于上述特征，Anisodamine Hydrobromide 常见于细胞模型中的炎症激活、缺氧复氧、氧化应激与屏障功能损伤研究，也可用于动物模型中的全身炎症反应、脓毒性损伤、肺损伤、微循环紊乱及胆碱能通路干预研究，并可作为先导参照分子用于抗炎、抗氧化或神经免疫调节方向的药物筛选；实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的，在缺乏统一标准化参数的情况下，研究者通常需结合模型敏感性、暴露时长、终点读数及对照体系进行优化。总体而言，该化合物可归属于兼具天然产物来源背景与多通路药理研究价值的胆碱能调节型工具分子，尤其适用于解析毒蕈碱受体拮抗、胆碱能抗炎信号、氧化应激缓解及炎症相关细胞损伤之间的关联机制。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C8790</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>289480-64-4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Treprostinil sodium</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Treprostinil (UT-15) sodium 是高效的 DP1 和 EP2 激动剂，其 EC 50 值分别为0.6±0.1和6.2±1.2 nM。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Treprostinil Sodium (UT-15) is a potent DP1, IP and EP2 agonist (EC50: 0.6/1.9/6.2 nM).</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Treprostinil sodium (CAS No.: 289480-64-4) is a synthetic prostacyclin analog and prostanoid receptor agonist broadly categorized as a small-molecule lipid mediator mimic for cardiovascular, inflammation, and signal-transduction research in biomedical and drug discovery settings. Functionally, it reproduces key aspects of endogenous prostanoid signaling by engaging relaxant prostanoid receptors, with well-characterized agonist activity at DP1, IP, and EP2 receptors, and experimental studies indicate activity in the nanomolar range, including high-potency responses spanning low- to mid-nanomolar levels across these targets. Through activation of Gs-coupled prostanoid receptors, this compound is associated with stimulation of adenylyl cyclase, elevation of intracellular cyclic AMP, and downstream modulation of protein kinase A-linked signaling and other cAMP-responsive pathways that regulate vascular smooth muscle tone, cell proliferation, inflammatory mediator responses, and transcriptional programs relevant to receptor pharmacology. In vitro, Treprostinil sodium has been used in recombinant receptor systems, binding assays, second-messenger assays, and cultured vascular or smooth muscle cell models to interrogate prostanoid receptor selectivity, receptor cross-activation, and cAMP-dependent signaling mechanisms, while in vivo it is also employed in animal or ex vivo pharmacology studies examining prostanoid-responsive physiology and pathway modulation; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. Owing to its multi-receptor agonist profile and robust potency, this reagent is particularly suitable for mechanistic studies of prostanoid biology, assay development, reference-compound benchmarking, and screening campaigns focused on DP1-, IP-, or EP2-linked signaling networks.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Treprostinil sodium (CAS No.: 289480-64-4) 是一种前列环素相关的小分子脂质介质类似物，通常被归类为前列腺素受体调节剂和前列环素信号研究工具，适用于生物医学基础研究、受体药理学分析及药物发现早期筛选。现有资料表明，该分子对前列腺素受体家族中的 DP1、IP 和 EP2 受体具有较高活性，其中以 Gs 蛋白偶联为主的信号转导特征较为明确，可促进细胞内 cAMP 水平升高并进一步影响蛋白激酶 A 及其下游转录调控网络，从而用于解析血管生物学、炎症调节、细胞应答与组织重塑等相关过程的分子机制。基于公开的受体结合与功能研究，该化合物在体外通常表现为纳摩尔至低微摩尔范围的活性水平，尤其适合用于比较不同前列腺素受体亚型的选择性、效能与偏向性信号特征，也可作为阳性对照或参考配体应用于受体表达细胞系、第二信使检测体系、报告基因实验及多参数表型筛选。由于其药理作用与前列环素样信号轴密切相关，Treprostinil sodium 亦常被纳入血管张力调控、免疫微环境变化、纤维化相关通路以及心肺与平滑肌生物学等研究场景中的细胞模型和动物模型，用于评估受体激活后对细胞增殖、迁移、分泌谱变化和炎症因子调节的影响；在实际实验中，所采用的浓度或剂量通常需要结合受体表达水平、模型类型、给药方式及研究目的进行优化。公开来源对其靶点谱的一致性较高，支持其作为研究前列腺素受体网络、cAMP 依赖性信号传递及相关药理筛选体系的常用工具分子。 ([sciencedirect.com](https://www.sciencedirect.com/science/article/pii/S0006295212002286?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Treprostinil sodium is a synthetic prostacyclin analog and DP1/IP/EP2 prostanoid receptor agonist used for cardiovascular, inflammation, and cAMP signaling research.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>一种前列腺素受体调节剂，用于cAMP信号与血管炎症机制研究。</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Treprostinil sodium (CAS No.: 289480-64-4) 是一种合成前列环素类似物，通常归类于前列腺素受体相关的小分子激动剂，广泛用于前列腺素信号转导、血管生物学、炎症调控及组织重塑等方向的基础与转化研究。作为前列烷素受体家族配体，该化合物已知可作用于DP1、IP和EP2等G蛋白偶联受体，并以对DP1和EP2的较高活性以及对IP受体的明确激动作用而受到关注，其体外活性总体处于纳摩尔至低微摩尔范围，不同受体亚型之间呈现一定选择性差异。基于这些靶点特征，Treprostinil sodium 可调控以腺苷酸环化酶和环磷酸腺苷为核心的下游信号网络，并进一步影响蛋白激酶活化、转录调节、细胞反应性及细胞间通讯过程；在部分研究体系中，其生物学效应还与炎症相关转录程序、细胞增殖状态、迁移行为以及纤维化相关表型变化有关。该分子常被用作研究前列腺素受体药理学、解析受体亚型功能分工、评估血管平滑肌细胞与内皮细胞应答、观察免疫细胞信号变化以及构建肺、血管或间质相关动物模型中的药理干预工具，也可作为相关候选化合物筛选和机制比较研究中的阳性参照物。对于细胞实验、离体组织研究或动物研究而言，其使用浓度或剂量通常依赖具体模型、观察终点和研究目的而设定，因此在目录描述中更适合将其界定为一种具有明确前列腺素受体激动特征、适用于生物医学研究与药物发现早期评价的研究工具化合物。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C8791</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>25913-34-2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tinoridine hydrochloride</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tinoridine hydrochloride是一种非甾体抗炎剂，也具有强效的自由基清除和抗过氧化物活性。</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tinoridine hydrochloride (Y-3642 hydrochloride) is a non-steroidal anti-inflammatory drug. Tinoridine hydrochloride (5-100 μM), produced a concentration-dependent inhibition on the simultaneous increases in lipid peroxide formation and renin release induced by 50 μM ascorbic acid in the renin granule fraction. On the other hand, indomethacin, hydrocortisone, and prednisolone, which had no ability to inhibit the lipid peroxidation in the renin granule fraction, did not influence the release of renin from the granules. These results suggest that tinoridine suppresses renin release by inhibiting the oxidative disintegration of membranes of renin granules.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tinoridine hydrochloride (CAS No.: 25913-34-2) is a small-molecule nonsteroidal anti-inflammatory research compound, also referred to as Y-3642 hydrochloride, that is primarily categorized within inflammation and oxidative stress research due to its documented free-radical-scavenging and anti-peroxidative properties. Available evidence indicates that its biological activity is associated less with a precisely established single protein target than with modulation of oxidative membrane injury, particularly suppression of lipid peroxidation in subcellular systems, and published studies further show that it inhibits ascorbic-acid-induced increases in lipid peroxide formation together with renin release in isolated renin granule fractions, supporting a mechanism in which stabilization of membrane integrity under oxidative conditions secondarily attenuates redox-sensitive secretory responses. In vitro activity has been reported in the micromolar range, with concentration-dependent effects observed at approximately 5 to 100 μM in biochemical and organelle-based assays, and earlier experimental work also described strong inhibition of oxidative disintegration in rat liver mitochondrial preparations, consistent with a role as a chemical probe for reactive oxygen species-related injury pathways and lipid peroxidation-driven inflammatory processes. Because the currently accessible literature does not define a canonical receptor-level signaling profile, this compound is most appropriately positioned for studies of redox biology, inflammatory mediator release, membrane damage, and oxidative stress-linked secretory regulation rather than for highly selective target-deconvolution campaigns. In biomedical research and drug discovery settings, Tinoridine hydrochloride may therefore be used as a reference or comparator molecule in cell-free systems, cellular oxidative injury models, subcellular fraction assays, and exploratory animal studies designed to examine inflammation-associated oxidative mechanisms, with the concentrations or doses used in experiments typically depending on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tinoridine hydrochloride (CAS No.: 25913-34-2) 是一种小分子有机化合物，在生命科学研究中通常归类为具有非甾体抗炎背景的研究分子，现有资料显示其研究价值主要集中于氧化应激、膜脂质过氧化以及分泌颗粒稳定性相关过程的机制探索。公开数据库将 tinoridine 记载为已知小分子药物实体，而早期药理与生化研究进一步提示，该分子除具有传统抗炎类别背景外，还表现出较突出的自由基清除与抗过氧化作用，因此在生物医学研究中更常被作为研究氧化损伤与炎症相关生物过程交叉机制的工具化合物使用。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Tinoridine?utm_source=openai)) 从机制层面看，现有证据并未明确建立其单一、特异性的经典受体或酶靶点，更支持其通过抑制自由基介导的脂质过氧化、减轻膜结构氧化性破坏并维持细胞器或分泌颗粒膜完整性来产生生物学效应；在肾素颗粒相关实验体系中，tinoridine hydrochloride 可随浓度升高而抑制抗坏血酸诱导的脂质过氧化增强及其伴随的肾素释放，提示其作用与氧化性膜解体过程密切相关，这一特征使其常被用于研究氧化应激与分泌调控之间的功能联系。([pubmed.ncbi.nlm.nih.gov](https://pubmed.ncbi.nlm.nih.gov/582014/?utm_source=openai)) 就体外活性而言，已报道实验支持其在微摩尔范围内表现出生化层面的活性，适合用于评价脂质过氧化抑制、自由基清除能力以及氧化损伤条件下膜相关生物事件的变化。([pubmed.ncbi.nlm.nih.gov](https://pubmed.ncbi.nlm.nih.gov/582014/?utm_source=openai)) 在应用场景上，该化合物可用于细胞亚组分、分离膜体系、氧化应激诱导模型及相关药物筛选流程中，作为比较不同候选分子对膜脂氧化、颗粒稳定性与应激反应影响的参考研究工具；在动物来源亚细胞组分或细胞模型中的使用条件通常需要依据具体实验设计、诱导方式、读出指标及研究目的进行优化。另有文献围绕其氧化降解行为开展分析研究，也从侧面支持该分子与氧化化学环境之间具有较强的方法学研究关联性。([pubmed.ncbi.nlm.nih.gov](https://pubmed.ncbi.nlm.nih.gov/34619000/?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Tinoridine hydrochloride is a small-molecule nonsteroidal anti-inflammatory research compound that modulates lipid peroxidation and oxidative membrane injury in inflammation and oxidative stress research.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>一种用于氧化应激与膜脂过氧化机制研究的小分子工具化合物。</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Tinoridine hydrochloride (CAS No.: 25913-34-2) 是一种小分子合成化合物，通常归类为非甾体抗炎相关研究分子，在生物医学研究中主要被用于炎症反应、氧化应激及膜脂过氧化过程的机制探索。现有资料显示，该分子除具有经典非甾体抗炎化合物的类别属性外，还表现出较突出的自由基清除与抗过氧化活性，因此其研究价值更多体现于炎症介质生成与氧化损伤耦联过程的交叉调控。基于已报道的药理学与生化观察，Tinoridine hydrochloride 的作用机制主要涉及对氧化应激相关膜损伤的抑制、对脂质过氧化形成的下调，以及对由氧化过程驱动的颗粒或膜性结构功能失稳的干预；部分资料亦将其归入与环氧合酶相关的非甾体抗炎分子范畴，但就当前研究语境而言，其抗氧化与抗脂质过氧化特征是更常被强调的实验基础。已发表的体外研究提示，该分子可在低微摩尔至中等微摩尔范围内表现出生物活性，并可浓度依赖性抑制特定氧化刺激条件下脂质过氧化水平升高及相关颗粒内容物释放，提示其可能通过稳定生物膜、减轻氧化性解体并干预活性氧介导的亚细胞事件而发挥作用。就靶点层面而言，目前更适合将其概括为作用于氧化应激反应网络、脂质过氧化过程及炎症介质生成轴的多机制研究工具，而非已被充分确证的单一高选择性靶向分子。该化合物常见于细胞无细胞体系、亚细胞组分研究、氧化损伤模型以及炎症与抗氧化药理筛选场景，可用于评估候选分子对膜稳定性、自由基相关损伤和应激诱导生物学读出的影响；在动物实验背景下，也可作为比较性研究分子用于分析氧化应激相关表型变化。实验中所使用的浓度或剂量通常取决于具体的实验设计、模型系统特征以及研究目的，因此在目录描述中宜将其定位为用于炎症生物学、氧化损伤机制及先导化合物筛选研究的功能性参考分子。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C8792</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>85371-64-8</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pinacidil monohydrate</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Pinacidil (P-1134) monohydrate 是 ATP 敏感钾通道 ( potassium channel ) 的有效激活剂。Pinacidil monohydrate 是一种抗高血压剂，通过开放 K + 通道使血管平滑肌超极化。Pinacidil monohydrate 可增强平滑肌中的 K + 外排。Pinacidil monohydrate 具有血管舒张特性。Pinacidil monohydrate 能够抑制自发性张力并减少激动剂引起的收缩。Pinacidil monohydrate 可用于心血管疾病等研究领域。</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pinacidil monohydrate is a potassium channel activator, antihypertensive drug.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pinacidil monohydrate (CAS No.: 85371-64-8) is a small-molecule potassium channel opener that is widely used as a pharmacological research tool in ion-channel biology, vascular physiology, and cardiovascular pharmacology, and it is generally classified within the ATP-sensitive potassium channel activator category for biomedical research and drug discovery applications. This compound is a synthetic bioactive molecule rather than a naturally derived product, and its functional background is centered on modulation of membrane excitability through activation of KATP channels, particularly in vascular smooth muscle, where channel opening promotes potassium efflux, membrane hyperpolarization, reduced calcium entry through voltage-dependent calcium pathways, and consequent suppression of spontaneous tone and agonist-evoked contractile responses. Consistent with this mechanism, pinacidil monohydrate is commonly used to investigate KATP-dependent signaling networks, excitation-contraction coupling, smooth-muscle relaxation mechanisms, vascular reactivity, and experimentally induced ischemia or cardiometabolic stress paradigms, with pharmacological effects often characterized in the micromolar to low tens of micromolar range depending on assay format, species, tissue preparation, and channel subunit context; where monohydrate-specific quantitative data are limited, activity is generally interpreted in accordance with the extensively studied parent pinacidil scaffold and related KATP openers. In experimental settings, it is routinely applied in cell-based assays, isolated tissue preparations, ex vivo vascular studies, and animal models to benchmark potassium channel activation, probe glibenclamide-sensitive responses, and support mechanism-oriented screening workflows, while the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pinacidil monohydrate (CAS No.: 85371-64-8) 是一种小分子钾通道开放剂，通常归类为ATP敏感性钾通道调节分子，在生物医学研究中主要作为离子通道药理学与血管平滑肌电生理研究工具使用；现有资料表明，其核心作用与激活KATP通道相关，尤其在平滑肌相关体系中可促进钾离子外流、诱导细胞膜超极化，并进一步降低自发性张力以及减弱激动剂诱发的收缩反应，从而成为研究膜兴奋性调控、血管张力稳态、心血管系统功能调节及缺血应激相关离子通道响应的重要参考分子。基于已公开的研究信息与产品资料，该分子的主要靶向背景集中于ATP敏感性钾通道及其下游电活动调节过程，在离体组织、细胞功能实验和药理筛选中常被用于构建通道开放状态模型，或作为阳性对照评估候选化合物对膜电位、收缩性和离子流变化的影响；其体外活性通常可概括为纳摩尔至微摩尔范围，实际实验中所使用的浓度或剂量通常取决于具体的实验设计、细胞类型、组织来源以及终点读数要求。就研究应用而言，Pinacidil monohydrate 常见于血管平滑肌细胞、心肌相关电生理模型、离体动脉环收缩舒张实验以及动物水平的功能药理研究，用于解析KATP通道开放对细胞兴奋性、组织反应性和系统性生理表型的影响；从药物研发角度看，该分子也适用于离子通道靶点验证、先导筛选体系建立以及机制研究中的比较药理学分析，尤其适合用于探讨钾通道介导的信号转导、应激适应与组织功能调节等方向。</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pinacidil monohydrate is a small-molecule ATP-sensitive potassium channel opener used to investigate KATP-mediated membrane excitability, vascular smooth muscle relaxation, and cardiovascular pharmacology.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>一种ATP敏感性钾通道开放剂，用于离子通道与血管平滑肌研究。</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Pinacidil monohydrate (CAS No.: 85371-64-8) 是一种以小分子钾通道开放剂为代表的研究用化合物，通常归类为ATP敏感性钾通道调节剂，在生物医学基础研究与药物发现中主要作为解析离子通道功能、膜电位稳态及兴奋性调控机制的工具分子。现有研究表明，其核心作用与促进ATP敏感性钾通道开放相关，可增强钾离子外流并诱导细胞膜超极化，从而降低平滑肌细胞的兴奋性，抑制自发性张力以及部分刺激因素诱导的收缩反应，因此在血管平滑肌生物学、离子通道药理学、心血管功能调控及相关应激反应研究中具有较高应用价值。就机制而言，该分子通常用于考察钾通道介导的电生理响应、跨膜离子稳态变化以及下游收缩与舒张表型之间的联系，并常被纳入与膜电位调节、钙信号耦联、组织反应性变化及细胞适应性调控相关的实验体系。根据公开研究与同类通道调节剂的一般特征，其体外活性通常可概括为纳摩尔至微摩尔范围，具体效应强度则受细胞类型、通道亚基组成、刺激条件和检测终点影响。在应用层面，Pinacidil monohydrate 常见于细胞水平的功能测定、离体组织反应评估、动物模型中的药理机制验证以及离子通道调节剂筛选流程，用于比较不同实验条件下的通道开放效应及其对组织功能输出的影响，而实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。总体而言，该分子适合作为研究ATP敏感性钾通道相关生理与病理过程的参考工具，有助于支持围绕血管反应性、平滑肌调控、能量状态感应及相关信号网络的机制性探索。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C8793</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>442201-24-3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remogliflozin etabonate (GSK189075)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Remogliflozin etabonate (GSK189075) 是一种具有口服活性的，选择性和低亲和力的钠葡萄糖共转运蛋白 ( SGLT2 ) 抑制剂，对 hSGLT2，rSGLT2，hSGLT1，rSGLT1 的 K i 值分别为 1.95 μM，43.1 μM，2.14 μM，8.57 μM。Remogliflozin etabonate 是一种基于苄基吡唑葡糖苷的前体，在体内被代谢成其活性形式，瑞格列净 (Remogliflozin)。Remogliflozin etabonate 在啮齿动物模型中显示出抗糖尿病功效。</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Remogliflozin etabonate (GSK189075A) is a prodrug of regaliflozin and an inhibitor SGLT2 with Ki values of 1.95, 2.14, 8.57, and 43.1μM for hSGLT2, rSGLT2, rSGLT1, and hSGLT1, respectively.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Remogliflozin etabonate (GSK189075) (CAS No.: 442201-24-3) is a small-molecule synthetic research compound in the sodium-glucose cotransporter inhibitor class, characterized as an orally active prodrug that is biotransformed to the active metabolite remogliflozin and used primarily in metabolic disease and transporter biology research. It is functionally associated with inhibition of SGLT2, with lower affinity activity reported against SGLT1 orthologs, supporting its classification as a renal glucose transport modulator for investigations of glucose reabsorption, glycosuric pharmacology, and carbohydrate homeostasis. Available reference data indicate target engagement in the low micromolar range, with reported binding constants spanning low to several tens of micromolar across human and rodent SGLT transporter subtypes, consistent with selective but not highly potent inhibition relative to some later-generation agents in this class. In biomedical research, Remogliflozin etabonate is therefore relevant for mechanistic studies of SLC5 family transporter function, comparative pharmacology between species, prodrug activation processes, and experimental interrogation of pathways linked to renal tubular glucose handling, systemic glucose balance, and downstream metabolic adaptation. It may be incorporated into cell-based transporter assays, biochemical binding studies, pharmacokinetic-pharmacodynamic evaluations, and rodent models designed to examine modulation of urinary glucose excretion and associated metabolic phenotypes, while the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. Its utility in drug discovery is centered on target validation, reference-compound benchmarking, and scaffold-informed optimization programs aimed at studying SGLT-directed mechanisms in preclinical research settings only.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Remogliflozin etabonate (GSK189075) (CAS No.: 442201-24-3) 是一种用于生命科学研究的 SGLT2 抑制剂类小分子及前药型研究工具，属于葡萄糖转运调控相关化合物范畴，可在体内转化为其活性形式 remogliflozin，因而常被用于研究肾脏葡萄糖重吸收调节、转运体药理学以及代谢性疾病相关机制；现有资料表明，其主要靶点为钠-葡萄糖共转运蛋白 2，并对 SGLT1 显示较弱作用，整体呈现相对选择性的转运体抑制特征，体外活性大体处于低微摩尔水平，可用于解析 SGLT2 介导的葡萄糖摄取与重吸收过程、比较 SGLT 家族亚型选择性，以及评估前药活化后活性暴露与药效读出的关系，其作用机制主要与抑制近端小管相关葡萄糖转运过程、降低转运体介导的底物回收有关，因而在肾脏生理、能量代谢、药效学和转运体筛选研究中具有应用价值；在实验体系中，该分子常见于转运体表达细胞模型、底物摄取测定、药代—药效关联分析以及啮齿动物代谢研究，用于表征候选分子的靶点参与度、选择性窗口和体内转化特征，而具体实验中所采用的浓度或剂量通常取决于研究目的、模型类型、给药方案及终点指标设置。</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Remogliflozin etabonate (GSK189075) is an orally active SGLT2 inhibitor prodrug used in metabolic disease and transporter biology research on renal glucose transport.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>一种SGLT2选择性抑制剂前药型科研分子，用于葡萄糖转运机制研究。</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Remogliflozin etabonate (GSK189075) (CAS No.: 442201-24-3) 是一种用于生物医学研究的钠葡萄糖共转运蛋白抑制剂类小分子前药，通常归属于选择性SGLT2调节分子与肾脏葡萄糖重吸收研究工具化合物范畴，其本身为活性代谢物 Remogliflozin 的前体，进入体内后可转化为具有实际转运体抑制作用的活性形式，因此常被用于解析前药设计、转运体药理学以及糖代谢稳态调控等研究问题。现有资料表明，该分子主要靶向SGLT2，并对SGLT1显示相对较弱的作用，整体体现出以SGLT2为主的选择性抑制特征，其体外活性大致处于低微摩尔水平，可用于研究肾近端小管上皮相关葡萄糖转运过程、尿糖排泄调节机制以及转运体选择性对代谢表型的影响。从机制上看，Remogliflozin etabonate 通过其活性代谢产物抑制钠依赖性葡萄糖转运，减少肾脏对滤过葡萄糖的再摄取，从而影响细胞与整体水平的葡萄糖处理过程；这一作用机制使其在葡萄糖转运体功能验证、SGLT家族亚型比较、代谢应答通路研究及候选抑制剂筛选中具有较高参考价值。作为一类基于苄基吡唑葡糖苷策略开发的前药分子，它也常被纳入药物化学与药代转化研究，用于评估前药向活性实体的转化效率、暴露特征与药效关联。在实验应用中，该化合物可见于转运体过表达细胞体系、肾源性细胞模型、代谢异常动物模型以及药效学比较研究中，用于建立靶点参与证据、评估选择性抑制后的功能输出，或作为同类SGLT抑制剂的参照分子；具体实验中所采用的浓度或剂量通常取决于模型类型、给药方案、检测终点及研究目的。总体而言，Remogliflozin etabonate 在生命科学研究目录中适合作为研究SGLT2介导葡萄糖转运、生物转化过程、转运体选择性药理及相关代谢表型调控的重要工具化合物。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C8794</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>32760-16-0</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Benzonatate (PEGn)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Benzonatate (PEGn) 是一种独特的非麻醉性的止咳剂，具有钠通道阻断特性，并对呼吸道拉伸受体具有麻醉作用。</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Benzonatate (PEGn) is a unique non-narcotic cough suppressant featuring sodium channel blocking properties and anesthetic effects on respiratory tract stretch receptors.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Benzonatate (PEGn) (CAS No.: 32760-16-0) is a synthetic small-molecule research compound in the antitussive and local anesthetic-like chemical class that is primarily categorized for studies of peripheral sensory neurobiology, airway reflex pharmacology, and ion channel modulation; although historically characterized by its suppression of cough reflex sensitivity, in biomedical research settings it is more appropriately described as a sodium channel-blocking agent with desensitizing effects on respiratory tract stretch receptor signaling, likely involving vagal afferent pathways and membrane excitability mechanisms associated with voltage-gated sodium channels. Available reference sources indicate that benzonatate exhibits local anesthetic-like functional behavior and has been reported as a potent inhibitor of voltage-gated sodium currents, supporting its use as a pharmacological tool for interrogating excitability-dependent processes in neuronal, airway, and related electrophysiological models. Consistent with this mechanism, its experimentally relevant activity has been described in the submicromolar to micromolar range in sodium current inhibition assays, while precise potency can vary according to channel subtype, formulation heterogeneity associated with the PEGn material, and assay configuration. In research applications, Benzonatate (PEGn) may be used to examine sensory nerve signal transduction, cough-reflex biology, peripheral chemosensory or mechanosensory regulation, and comparative screening against other sodium channel modulators in cell-based electrophysiology platforms or exploratory animal studies; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. Where direct target-resolution or pathway-mapping data for this PEGn material remain limited, mechanistic interpretation is generally inferred from the parent benzonatate pharmacology and related local anesthetic-like sodium channel blockers rather than from fully defined receptor-selective datasets.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Benzonatate (PEGn) (CAS No.: 32760-16-0) Benzonatate (PEGn) 可归类为与对氨基苯甲酸酯样局部麻醉药理骨架相关的聚乙二醇同系物或分布组分研究对象，通常被视为 benzonatate 这一天然不存在、以化学合成为来源的小分子体系中的一类组成形式；在生物医学研究与药物研发语境下，该分子主要用于解析外周感觉传入调控、气道机械感受转导以及局部麻醉样离子通道调节等过程，其功能背景集中于降低气道相关牵张感受器与迷走传入纤维的兴奋性，并表现出与电压门控钠通道抑制一致的药理特征，现有研究提示其机制与局部麻醉药样的膜稳定化作用及对 NaV 通道（包括 NaV1.7 在内的亚型）电流抑制有关，同时可通过减弱呼吸道、肺及胸膜感觉末梢对机械刺激的反应性而影响下游神经信号传递，相关体外活性通常可概括为微摩尔至较高微摩尔范围，且不同 PEG 链长组分、制剂纯度和实验体系可能导致效应强度出现明显差异；因此，在研究应用上，该类分子更适用于离子通道药理、电生理评估、感觉神经元细胞模型、气道相关组织或动物实验中的机制验证，以及作为局部麻醉样先导特征的比较分子用于筛选具有外周感觉调节能力的候选化合物，而实验中所使用的浓度或剂量通常取决于具体的实验设计、给药方式、暴露时间和研究目的。 ([pubmed.ncbi.nlm.nih.gov](https://pubmed.ncbi.nlm.nih.gov/26386152/?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Benzonatate (PEGn) is a synthetic local anesthetic-like sodium channel blocker used to investigate peripheral sensory neurobiology, airway reflex pharmacology, and ion channel modulation.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>一种用于气道感觉传导与钠通道调节研究的小分子工具化合物。</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Benzonatate (PEGn) (CAS No.: 32760-16-0) 是一类合成来源的对氨基苯甲酸酯相关分子集合体，可归入具有局部麻醉样药理特征的研究化合物范畴，其结构上表现为聚乙二醇链长不完全一致的同系物混合特征，因此在生命科学研究目录中更适合作为用于感觉神经调控、气道机械感受转导及电压门控离子通道药理学研究的工具性分子加以描述。现有研究表明，该分子的生物学作用主要与外周感觉传入纤维活性抑制有关，尤其涉及呼吸道、肺部及胸膜相关牵张感受器的敏感性降低，同时具有明确的电压门控钠通道阻断样活性；在机制层面，其已报道可抑制包括 Nav1.7 在内的多种钠通道亚型，作用特征呈可逆性、浓度依赖性及状态依赖性，并可能通过减弱迷走神经感觉通路中的动作电位产生与传导，影响与机械刺激感知相关的神经信号输入。基于现有体外电生理与细胞药理学信息，其活性水平可概括为微摩尔范围，并可依据不同实验体系表现出由低微摩尔至更高微摩尔区间的效应差异。由于公开资料对 PEGn 具体单一组分的定量实验参数仍较有限，对该条目进行研究背景描述时通常需要结合 benzonatate 类分子的已知药理类别及同系物混合物属性进行合理外推。该分子在应用上常见于离子通道功能评价、外周感觉神经元兴奋性分析、呼吸道机械刺激相关细胞模型研究，以及用于动物实验中的气道感觉反射机制探索和候选分子筛选中的阳性或比较参照；在此类研究中，实验中所使用的浓度或剂量通常取决于具体的实验设计、模型系统、暴露方式及研究目的。总体而言，Benzonatate (PEGn) 适用于围绕感觉神经抑制、气道传入信号调节及钠通道相关药理效应开展基础研究与药物发现前期评价，尤其可作为解析外周机械感受通路与局部麻醉样分子作用关系的研究材料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C8795</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1883548-96-6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Liarozole dihydrochloride</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Liarozole (R75251) dihydrochloride 是一种咪唑衍生物和具有口服活性的维甲酸 (RA) 代谢阻断剂 (RAMBA) 。Liarozole dihydrochloride 抑制细胞色素 P450 ( CYP26 ) 依赖的维甲酸 4- 羟基化 ( IC 50 =7 μM)，导致组织 RA 水平增加。Liarozole dihydrochloride 具有抗肿瘤活性。</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Liarozole dihydrochloride is a cytochrome P450 (CYP450) dependent inhibitor, orally active, it also a potent inhibitor of estrogen (via inhibition of aromatase) and testicular androgen synthesis (inhibition of 17 ,20-lyase).Liarozole dihydrochloride is an imidazole derivative; it is being investigated as a non-hormonal agent in prostate cancer and in the treatment of various other cancers and skin disorders.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Liarozole dihydrochloride (CAS No.: 1883548-96-6) is a synthetic imidazole-derived small molecule used in biomedical research as a retinoic acid metabolism-blocking agent within the broader category of cytochrome P450-modulating compounds, and it is primarily applied in studies of retinoid biology, endocrine-associated metabolic regulation, and oncology-oriented discovery workflows. Functionally, this compound is characterized by inhibition of CYP26-dependent retinoic acid 4-hydroxylation, thereby elevating endogenous retinoic acid exposure in experimental systems and modulating retinoid-responsive transcriptional programs linked to cellular differentiation, proliferation control, and tissue homeostasis; available reference data further indicate activity against additional P450-associated steroidogenic enzymes, including aromatase and 17,20-lyase, supporting its classification as a multi-target P450 pathway probe rather than a highly selective single-target reagent. Reported biochemical potency for inhibition of retinoic acid catabolism is in the low micromolar range, and broader enzyme-modulatory effects have been described from submicromolar to micromolar levels depending on the assay configuration, species context, and enzyme system evaluated. In research settings, Liarozole dihydrochloride is commonly employed to investigate retinoic acid signaling dynamics, CYP26-dependent metabolic turnover, differentiation-associated phenotypes, and pathway interactions between retinoid and steroid biosynthesis networks in cell-based assays, mechanism-of-action studies, and exploratory animal model experiments; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. This product is therefore most appropriate for non-clinical laboratory applications such as target validation, pathway dissection, phenotypic profiling, and compound-combination screening in drug discovery and translational biology research, and any observed antiproliferative or antitumor-associated effects should be interpreted strictly within controlled experimental models rather than as evidence of human use or medical utility.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Liarozole dihydrochloride (CAS No.: 1883548-96-6) 是一种合成小分子咪唑类衍生物，可归类为维甲酸代谢阻断剂，并常作为多靶点细胞色素 P450 调节分子用于生物医学研究与药物发现领域，其研究背景主要围绕内源性维甲酸稳态调控、分化相关信号网络以及类固醇生成相关代谢过程展开。现有资料表明，该化合物的核心作用机制是抑制 CYP26 介导的维甲酸代谢，尤其与维甲酸 4-羟化过程相关，从而提高细胞或组织环境中的内源性全反式维甲酸水平，进而影响维甲酸受体相关转录调控、细胞分化程序及增殖状态；与此同时，其对芳香化酶、CYP17A1 以及其他甾体代谢相关 P450 酶亦显示抑制活性，因此常被视为兼具维甲酸代谢调节与甾体生成干预特征的研究工具分子。基于公开产品资料与数据库信息，Liarozole dihydrochloride 在体外实验中的活性总体可概括为纳摩尔至低微摩尔范围，其中对不同 P450 亚型的抑制强度存在一定差异，这种谱系特征使其特别适用于解析维甲酸代谢网络与甾体代谢网络之间的功能耦联关系。作为研究试剂，该分子常用于肿瘤生物学、皮肤生物学、核受体信号转导、分化诱导机制、代谢酶筛选及先导化合物比较研究，也可用于细胞模型和动物模型中评估内源性维甲酸水平变化所引发的表型效应；在相关实验设计中，所采用的处理浓度或给药剂量通常取决于具体模型、终点指标与研究目的。总体而言，Liarozole dihydrochloride 适合作为研究维甲酸代谢阻断、CYP450 相关酶功能及下游受体信号调控的重要工具化合物，为阐明分化调控、生长控制及代谢重编程等过程提供了具有机制导向价值的实验支持。 ([abmole.com](https://www.abmole.com/products/liarozole-dihydrochloride.html?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Liarozole dihydrochloride is an imidazole-derived CYP26-mediated retinoic acid metabolism inhibitor used in retinoid biology, endocrine metabolism, and oncology research.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>一种用于科研的维甲酸代谢阻断剂及细胞色素P450调节分子。</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Liarozole dihydrochloride (CAS No.: 1883548-96-6) 是一种咪唑衍生物，通常被归类为维甲酸代谢阻断剂及细胞色素 P450 相关调节分子，在生物医学基础研究中主要作为解析维甲酸稳态调控、甾体生成相关酶活性变化以及肿瘤相关分化与增殖过程的研究工具。现有研究表明，该分子可通过抑制 CYP26 介导的维甲酸代谢而提高内源性维甲酸水平，并对芳香化酶及甾体合成通路中的部分酶过程产生干预作用，因此常用于考察维甲酸信号转导、核受体调控网络、细胞分化程序及激素代谢轴之间的相互联系。从作用特征看，其体外活性总体可概括为微摩尔范围，适合用于细胞水平的机制研究、通路验证和先导筛选实验；在不同研究体系中，该化合物可被应用于肿瘤细胞模型、上皮分化相关模型以及与维甲酸代谢失衡有关的动物研究场景，以评估其对代谢酶表达、下游转录响应、细胞表型变化和药理敏感性的影响。作为一类具有明确机制指向性的研究分子，Liarozole dihydrochloride 有助于研究者从代谢调控与信号整合两个层面理解维甲酸相关生物学过程，并可作为药物发现早期阶段中用于靶点验证、通路扰动分析和候选分子比较的参考工具；具体实验中采用的浓度或剂量通常需结合细胞类型、暴露时间、模型复杂度及研究目的进行优化设定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C8796</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6363-53-7</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Maltose monohydrate</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Maltose monohydrate 是淀粉的降解产物，也是 α-Glucosidase 的底物。α-Glucosidase 可将 Maltose 水解为葡萄糖。在热胁迫和冷胁迫下，Maltose monohydrate 具备保护蛋白质、细胞膜和光合电子传递链的能力。</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>D-(+)-Maltose monohydrate (D-(+)-Maltose monohydrate), a dextrodisaccharide from starch and malt, is used as a fermentable intermediate and sweetening agent in brewing.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Maltose monohydrate (CAS No.: 6363-53-7) is a naturally occurring reducing disaccharide and carbohydrate research reagent that arises as a starch degradation product and serves as a canonical substrate for α-glucosidase, which hydrolyzes it to glucose; accordingly, this compound is primarily classified within glycobiology, carbohydrate metabolism, enzymology, and stress-biology research. Derived from starch- and malt-associated saccharide pools and broadly relevant to microbial, plant, and mammalian systems, maltose monohydrate is widely used to investigate glucosidase-dependent carbohydrate turnover, substrate utilization, carbon flux, and transport processes linked to maltose-binding proteins and maltodextrin uptake pathways. Its principal biological mechanism in experimental settings is therefore substrate-driven modulation of saccharide metabolism rather than receptor-directed pharmacology, with utility in probing α-glucosidase activity, downstream glucose generation, and associated metabolic readouts; in plant and biochemical stress models, maltose and related disaccharide osmolytes have also been associated with stabilization of proteins, cellular membranes, and photosynthetic electron transport components under heat or cold stress, consistent with a protective physicochemical role in macromolecular and membrane homeostasis. Because this molecule is generally employed as a metabolic substrate or osmoprotective carbohydrate rather than a potent pathway-selective inhibitor or agonist, discrete in vitro potency parameters such as IC50 or EC50 values are often not the primary descriptors for this reagent, and when activity is reported it is commonly interpreted through substrate conversion, transport kinetics, or concentration-dependent osmolyte effects that are typically evaluated across millimolar to higher experimental ranges rather than low-dose pharmacological windows. In biomedical research and drug discovery workflows, maltose monohydrate is used in cell-free enzyme assays, metabolic phenotyping studies, microbial nutrient-utilization experiments, carbohydrate-processing screens, and stress-response model systems, while applications in cell models or animal studies are generally designed to interrogate energy metabolism, glycosidase function, carbohydrate transport, or biomolecular stabilization; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Maltose monohydrate (CAS No.: 6363-53-7) 作为一种来源于淀粉降解过程的二糖类研究分子，属于糖代谢与碳流分配研究中常用的基础性化合物，可由植物、微生物及谷物发芽相关体系中的淀粉水解过程产生，也常被用作发酵代谢、酶学反应和应激生物学研究中的碳源或代谢中间体；现有资料表明，麦芽糖是α-葡萄糖苷酶及相关糖苷水解酶的重要底物，可被进一步裂解为葡萄糖，因此其主要作用机制集中于淀粉与蔗糖代谢网络、糖分解代谢途径以及由可溶性糖介导的渗透稳态和应激响应调控。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/maltose?utm_source=openai)) 在植物逆境生物学背景下，麦芽糖还被认为具有兼容性溶质样功能，在热胁迫和冷胁迫条件下可对蛋白质构象稳定性、膜系统完整性以及光合电子传递链维持产生保护效应，这使其成为研究叶绿体淀粉周转、低温适应、热胁迫缓冲和光合作用稳态的重要分子探针。([pmc.ncbi.nlm.nih.gov](https://pmc.ncbi.nlm.nih.gov/articles/PMC8154053/?utm_source=openai)) 从生物医学研究与药物研发目录的应用视角看，该分子更适合归入代谢底物、酶活性检测配体、糖代谢通路研究工具和培养体系碳源优化相关类别，其已知“靶点”更准确地说主要体现为α-葡萄糖苷酶样酶系统及与淀粉分解、糖转运和葡萄糖释放相关的代谢节点，而非典型受体型药理靶标；目前公开信息更支持其作为代谢底物和应激保护相关研究分子使用，而非具有明确高效受体亲和力的小分子调节剂，因此体外活性通常不宜表述为经典药理学意义上的纳摩尔至微摩尔效应范围，更合理的概括是其研究活性多体现于酶促转化、代谢通量变化和细胞或亚细胞水平的功能读出，实验中所使用的浓度或剂量通常取决于具体的实验设计、培养条件、模型系统以及检测终点。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/maltose?utm_source=openai)) 在实际研究中，Maltose monohydrate 常用于细胞外酶反应体系、糖代谢相关细胞模型、植物与微生物应激模型以及代谢筛选或培养基开发场景，用于评估糖苷水解能力、碳源利用特征、应激缓冲现象及与能量代谢重编程相关的生物学变化；鉴于针对该水合物形态本身的独立药理数据相对有限，对其性质的专业解读通常基于麦芽糖这一母体分子的代谢学与生理学特征展开。([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/summary/summary.cgi?sid=24897052&amp;utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Maltose monohydrate is a reducing disaccharide substrate for α-glucosidase used in glycobiology, carbohydrate metabolism, enzymology, and stress-biology research.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>一种用于糖代谢与应激生物学研究的二糖底物。</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Maltose monohydrate (CAS No.: 6363-53-7) 是一种来源明确的还原性二糖水合物，通常被归类为碳水化合物代谢研究中的基础糖类分子，也是淀粉与麦芽等多糖降解过程中形成的重要中间产物，在植物、微生物及酶学体系中均具有较高的研究价值；在生命科学研究目录中，该分子主要用于糖代谢网络解析、碳流转运研究、酶底物识别、应激生物学评估以及与生物制造相关的发酵过程建模。就生物学背景而言，麦芽糖是淀粉经淀粉酶体系分解后的典型产物之一，可进一步在α-葡萄糖苷酶等糖苷水解酶作用下裂解为葡萄糖，因此常被用作评估相关水解酶活性、底物偏好性与催化效率的模型底物；在植物体系中，其积累与暂时性淀粉降解密切相关，并与温度胁迫下的碳代谢重编程存在功能联系。已有研究表明，麦芽糖相关的关键作用机制并不局限于作为能量前体或代谢中间体，还涉及对蛋白质构象稳定性、细胞膜完整性及光合电子传递过程的保护效应，尤其在热胁迫和冷胁迫条件下，这类作用被认为与β-淀粉酶诱导、淀粉动员增强以及细胞内可溶性糖积累共同构成适应性应答的一部分；因此，从机制层面看，其核心相关靶点通常包括α-葡萄糖苷酶及其他参与淀粉降解与麦芽糖周转的酶类，而其关联通路则主要集中于淀粉和蔗糖代谢、糖稳态调控、叶绿体碳代谢以及逆境响应相关网络。需要指出的是，作为内源性代谢物和常用酶学底物，Maltose monohydrate 并不适合按照典型小分子抑制剂或受体配体的框架来定义单一“药理靶点”，其体外研究活性更多体现为在酶反应体系中的底物可利用性、在细胞外或重组体系中的代谢转化特征，以及在应激模拟条件下对生物大分子和膜系统的保护能力；若以体外实验表征方式概括，其相关效应通常见于毫摩尔水平至更高浓度区间，而非纳摩尔至微摩尔范围的高亲和力配体模式。基于上述特征，该分子常用于细胞模型中的糖代谢补充实验、植物或微生物模型中的碳源利用研究、酶筛选与底物竞争实验、应激保护机制分析，以及围绕糖代谢酶、转运过程和能量分配的药物研发早期基础研究；在动物模型或复杂体系中的使用通常侧重于代谢追踪、营养环境模拟或生化通路验证，实验中所采用的浓度或剂量一般取决于具体模型、给药方式或培养条件以及研究目的。总体而言，Maltose monohydrate 作为一种具有明确代谢来源和广泛实验适配性的研究用糖类分子，特别适用于生物医学基础研究、代谢生物学、植物逆境生理学、工业微生物学以及药物发现前期的酶学筛选与机制验证场景。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C8797</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>514-36-3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Fludrocortisone acetate</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Fludrocortisone acetate (9α-Fludrocortisone acetate) 是一种口服i活性的合成的盐皮质激素。Fludrocortisone acetate 可以有效控制钠潴留。Fludrocortisone acetate 用于研究心脏损伤、肾上腺功能不全和直立性低血压。</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Fludrocortisone acetate (9α-Fludrocortisone acetate) , a glucocorticoid-receptor agonist, binds to cytoplasmic receptors, translocates to the nucleus, and subsequently initiates the transcription of glucocorticoid-responsive genes such as lipocortins to inhibit phospholipase A2 (PLA2). Fludrocortisone acetate is the acetate salt of a synthetic fluorinated corticosteroid with anti-inflammatory and antiallergic activities. Inhibition of PLA2 activity prevents the release of arachidonic acid, a precursor of eicosanoids such as prostaglandins and leukotrienes; eicosanoids are important mediators in the pro-inflammatory response mechanism. As a mineralocorticoid-receptor agonist, this agent stimulates Na+ reabsorption and water retention and K+ and H+ secretion in the distal tubules and collecting ducts of the kidney.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fludrocortisone acetate (CAS No.: 514-36-3) is a synthetic fluorinated corticosteroid ester that is primarily categorized as a mineralocorticoid receptor agonist with additional glucocorticoid receptor agonistic activity, making it a useful small-molecule probe for studies of steroid hormone signaling, epithelial ion transport, inflammation-associated transcriptional regulation, and endocrine physiology in biomedical research and drug discovery. As a steroidal ligand of the nuclear receptor superfamily, it is generally used as a research reagent to investigate mineralocorticoid-responsive and glucocorticoid-responsive gene programs, with mechanistic effects involving receptor binding in the cytoplasm, ligand-dependent nuclear translocation, interaction with hormone response elements, and transcriptional modulation of downstream effector genes; reported functional background also supports regulation of sodium reabsorption, water retention, and potassium and proton secretion in renal distal tubular and collecting duct models, together with glucocorticoid-linked induction of lipocortin-associated signaling and suppression of phospholipase A2-dependent arachidonic acid mobilization, thereby influencing eicosanoid-related inflammatory pathways. Available reference sources consistently identify mineralocorticoid receptor and glucocorticoid receptor as the principal known targets, whereas detailed quantitative potency data are not broadly standardized across public product and database records for this acetate form; accordingly, its in vitro activity is more appropriately summarized as occurring in the nanomolar to micromolar concentration range depending on receptor context, cell background, assay format, and metabolic conversion conditions rather than by assigning unsupported discrete values. In experimental settings, Fludrocortisone acetate is commonly applied in cell-based assays examining corticosteroid receptor transactivation, renal electrolyte transport biology, stress-response transcriptional networks, and inflammatory mediator regulation, and it is also used in animal and disease-model research related to cardiovascular injury, adrenal-axis dysfunction, and orthostatic physiology, while the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fludrocortisone acetate (CAS No.: 514-36-3) 是一种合成甾体类研究分子，通常归类为具有盐皮质激素样活性的皮质类固醇衍生物，同时也表现出与糖皮质激素信号调控相关的生物学特征，在生物医学研究中常被用作解析核受体介导转录调节、离子与水盐稳态控制以及炎症相关分子网络的重要工具化合物；其已知作用主要涉及盐皮质激素受体和糖皮质激素受体等甾体激素受体轴，配体结合后可促进受体构象改变、胞质复合物重排及核转位，继而调控相应反应元件下游基因转录，影响上皮离子转运、肾脏远曲小管和集合管相关转运过程，以及脂质介质生成、磷脂酶A2相关级联和花生四烯酸代谢所连接的炎症信号通路；从研究背景看，该分子常用于肾上腺皮质激素生物学、心血管应激反应、肾脏生理调控、炎症反应机制及内分泌相关模型的实验体系中，以帮助评估受体激活后的表型变化、转录谱重塑和组织反应特征；基于甾体受体配体的一般实验规律及公开研究背景，其体外活性通常可概括为纳摩尔至微摩尔范围，具体效应强度则受细胞类型、受体表达水平、培养条件、暴露时间和检测终点影响；在应用层面，该分子可见于受体报告基因分析、细胞信号通路干预实验、离子转运与屏障功能研究、炎症相关因子表达评估，以及动物模型中的激素反应性表型观察和候选化合物对照筛选，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的，因此在目录描述中宜将其界定为用于基础机制研究、模型构建与药理筛选支持的甾体受体调节工具分子。</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Fludrocortisone acetate is a synthetic fluorinated corticosteroid and mineralocorticoid/glucocorticoid receptor agonist used to study steroid signaling, epithelial ion transport, inflammation, and endocrine physiology.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>一种用于甾体受体调控及水盐稳态研究的科研工具分子。</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Fludrocortisone acetate (CAS No.: 514-36-3) 是一种合成氟化皮质类固醇衍生物，可归类为兼具盐皮质激素样活性并伴随糖皮质激素受体调节特征的研究分子，广泛用于内分泌调控、肾脏离子转运、炎症信号网络及相关药理机制的基础研究与药物发现评估。该分子并非天然来源的生物大分子，而是基于甾体骨架构建的合成小分子工具化合物，常被用于解析矿物皮质激素受体与糖皮质激素受体介导的转录调控过程及其下游生物学效应。在作用机制上，其已知可与胞质受体结合并促使受体复合体发生核转位，进一步调控糖皮质激素或盐皮质激素应答基因的表达；在肾脏相关研究体系中，其作用通常与远曲小管和集合管上皮细胞的钠离子重吸收增强以及钾离子、氢离子分泌调节有关，从而被用于研究水盐稳态、离子通道与转运蛋白调控、肾上腺轴相关反馈以及组织损伤过程中的激素依赖性反应。在炎症与应激反应研究中，该分子还可作为受体激动剂样探针用于观察磷脂酶A2相关代谢级联、花生四烯酸释放及下游脂质介质生成的受体依赖性变化，从而支持对炎症转录程序、屏障功能改变和免疫细胞应答调节的机制分析。现有研究背景表明，其体外活性通常可概括为纳摩尔至微摩尔范围，具体效应强度与细胞类型、受体表达水平、培养条件、处理时程及检测终点密切相关，因此在不同实验体系中常被用作核受体信号研究、激素反应元件报告基因分析、肾小管上皮细胞功能评估、心血管应激模型、肾损伤模型及炎症相关动物模型中的参考干预分子。在药物研发语境下，该化合物主要作为机制验证、靶点通路表征和候选分子比较的研究工具，用于建立受体激活谱、筛选具有选择性调节特征的先导化合物，并辅助评估甾体类分子在多通路交叉调控中的构效趋势。由于不同研究目的对应的实验窗口差异较大，实验中所使用的浓度或剂量通常取决于具体的实验设计、模型背景与读出指标，因此在目录描述中更适合将其界定为面向生物医学研究与药物研发的核受体调节类参考化合物。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C8798</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>305-33-9</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Iproniazid phosphate</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Iproniazid phosphate 是一种口服活性、不可逆、非选择性的单胺氧化酶 ( MAO ) 抑制剂。Iproniazid phosphate 抑制 MAO 活性，增强 Rotenone ( HY-B1756 ) 诱导的凋亡 ( Apoptosis )。Iproniazid phosphate 调节神经递质水平、影响神经元功能、诱导肝坏死及干扰内分泌。Iproniazid phosphate 可用于抑郁症、帕金森病及肝毒性的研究。</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Iproniazid Phosphate is a non-selective, irreversible monoamine oxidase inhibitor (MAOI).</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Iproniazid phosphate (CAS No.: 305-33-9) is a small-molecule hydrazine-class monoamine oxidase inhibitor that is widely used as a neuropharmacology and toxicology research tool in biomedical investigation and early drug discovery, particularly in studies of monoaminergic regulation, neuronal stress responses, and mechanism-based safety evaluation. As the phosphate salt of iproniazid, it is generally categorized within irreversible, non-selective monoamine oxidase inhibitors, with primary activity directed against the flavin-dependent mitochondrial enzymes MAO-A and MAO-B, thereby suppressing oxidative deamination of endogenous monoamine neurotransmitters and altering intracellular and extracellular levels of biogenic amines relevant to neuronal signaling, synaptic homeostasis, and neurobehavioral phenotypes. Its functional background is closely associated with experimental modulation of catecholaminergic and serotonergic pathways, and available reference information further indicates that it can potentiate rotenone-induced apoptosis, supporting its utility in model systems designed to interrogate mitochondrial dysfunction, oxidative stress, and degeneration-associated signaling networks. Consistent with its pharmacological class, in vitro activity is generally described at nanomolar to micromolar or low micromolar levels depending on assay format, enzyme source, substrate conditions, and duration of exposure, although precise potency values should be confirmed from experiment-specific datasets when quantitative benchmarking is required. In research practice, Iproniazid phosphate is commonly applied in cell-based assays, biochemical enzyme studies, and animal models to investigate monoamine oxidase biology, neurotransmitter-dependent phenotypes, liver injury mechanisms, and broader liabilities associated with irreversible enzyme inhibition; reported observations also support its use in studies of hepatocellular necrosis and endocrine disturbance as part of safety pharmacology or mechanism-of-toxicity workflows. The concentrations or doses used in experiments typically depend on specific experimental designs and research objectives, and appropriate selection should be guided by target engagement, model sensitivity, exposure duration, and tolerability endpoints within strictly nonclinical research settings.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Iproniazid phosphate (CAS No.: 305-33-9) 是一种经典的小分子单胺氧化酶抑制剂，通常归类为不可逆、非选择性的 MAO 抑制剂，在神经生物学、药理学及毒理学研究中具有代表性价值；作为 iproniazid 的磷酸盐形式，其研究背景主要围绕单胺递质代谢调控、线粒体相关应激反应以及外源性化合物所致组织损伤机制展开。现有资料表明，该分子的核心作用靶点为单胺氧化酶系统，通过抑制 MAO-A 与 MAO-B 相关酶活性，减少单胺类递质的氧化脱氨过程，从而改变细胞内外生物胺稳态，并进一步影响神经元兴奋性、氧化应激状态及下游代谢网络；在部分实验条件下，其还可增强 rotenone 诱导的细胞凋亡反应，提示其能够与线粒体功能障碍、活性氧积累及应激相关信号过程发生交互，因此常被用于解析神经递质失衡、神经元损伤和代谢适应性变化之间的关系。就体外活性特征而言，作为酶抑制剂，其相关研究中的有效作用水平通常可概括为微摩尔范围，具体活性强度、作用持续时间及表型输出则受细胞类型、暴露时长、代谢背景和检测终点影响。基于上述特征，Iproniazid phosphate 常见于神经细胞模型、氧化应激或线粒体损伤模型、肝脏毒理学评价体系以及单胺氧化酶相关筛选实验中，可用于研究神经递质调节、细胞命运转换、肝毒性机制与内分泌干扰等生物学问题；在动物实验中，其亦可作为构建或干预相关药理与毒理表型的工具化合物使用。总体而言，该分子更适合作为研究 MAO 依赖性代谢过程、神经化学稳态破坏及药物安全性信号的实验探针，而实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Iproniazid phosphate is a hydrazine-class irreversible non-selective monoamine oxidase inhibitor targeting MAO-A and MAO-B, widely used in neuropharmacology and toxicology research.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>一种用于科研研究的不可逆非选择性单胺氧化酶抑制剂。</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Iproniazid phosphate (CAS No.: 305-33-9) 是一种肼类单胺氧化酶抑制剂，通常归属于经典、非选择性且不可逆的单胺氧化酶抑制剂研究工具分子，在生物医学研究中主要作为调控单胺代谢与评估氧化脱氨过程的化学探针使用。该分子并非天然来源产物，而是具有明确药理学背景的合成小分子，其核心研究价值集中于神经生物学、药理毒理学、肝损伤机制、线粒体功能异常以及神经退行性相关模型等方向。现有研究表明，其主要作用靶点为单胺氧化酶系统，包括 MAO-A 与 MAO-B，通过不可逆抑制酶活性减少单胺类递质的氧化分解，从而引起多巴胺、去甲肾上腺素与5-羟色胺等内源性胺类水平的持续性改变，并进一步影响突触信号转导、氧化应激状态、细胞能量代谢及神经元兴奋性稳态；在部分实验条件下，该分子还可增强特定线粒体毒性刺激所诱导的细胞凋亡反应，因此常被用于分析单胺代谢抑制与细胞命运调控之间的关联。就体外活性而言，其对相关酶系统的抑制效应通常被概括为处于低微摩尔至微摩尔范围，具体活性强弱会随酶来源、底物体系、孵育时间及是否发生代谢活化而变化。除神经递质代谢研究外，Iproniazid phosphate 亦因其与肝毒性相关的代谢转化特征而被广泛用于机制研究，尤其适用于探索肝微粒体酶介导的生物转化、反应性中间体形成、蛋白共价修饰、细胞坏死及应激损伤通路等过程。在实验应用中，该分子可用于细胞模型、离体酶学体系及动物模型中的靶点验证、通路扰动、毒理表型建立和先导化合物比较研究，也可作为经典参考抑制剂用于评价新型 MAO 调节剂的作用特征；实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。总体而言，Iproniazid phosphate 是连接单胺代谢调控、神经功能改变与代谢性毒理机制研究的重要工具分子，特别适合用于需要同时考察 MAO 抑制、生化应答重塑及肝脏安全性信号的基础研究与早期药物发现场景。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C8799</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2137030-98-7</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ensartinib (X-396) dihydrochloride</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ensartinib dihydrochloride (X-396 dihydrochloride) 是一种能透过血脑屏障的双重 ALK / MET 抑制剂， IC 50 分别 &lt;0.4 nM 和 0.74 nM。</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ensartinib hydrochloride (X-396 dihydrochloride) is a potent new-generation ALK inhibitor with high activity against CNS metastases and a broad range of known crizotinib-resistant ALK mutations. It potently inhibits both wild-type ALK and ALK variants (C1156Y, F1174, G1202R, L1196M, S1206R, and T1151 mutants) with in vitro IC50s of &lt;4 nM.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ensartinib (X-396) dihydrochloride (CAS No.: 2137030-98-7) is a small-molecule kinase inhibitor used as a research reagent in oncology and signal transduction studies, particularly in biomedical investigations focused on anaplastic lymphoma kinase and hepatocyte growth factor receptor biology. This salt form of ensartinib is applied in drug discovery and translational research as a potent dual ALK/MET inhibitor, with reported activity against ALK and multiple ALK resistance-associated variants, thereby supporting mechanistic evaluation of aberrant receptor tyrosine kinase signaling in malignant cell systems. Available reference information indicates in vitro inhibitory potency in the subnanomolar to low nanomolar range for ALK and MET and similarly strong nanomolar-level activity against several crizotinib-resistant ALK mutant forms, consistent with suppression of downstream oncogenic pathways commonly linked to ALK-driven and MET-associated signaling, including cascades converging on proliferative and survival networks such as MAPK/ERK, PI3K/AKT, and related phosphorylation-dependent processes. In research settings, ensartinib dihydrochloride is employed to interrogate kinase dependency, resistance mechanisms, blood-brain barrier penetration-related pharmacology, and target engagement in cultured tumor cells, engineered mutant models, and in vivo xenograft or metastasis-oriented experimental systems, while also serving as a comparator or tool compound in kinase profiling and combination-screening workflows. The concentrations or doses used in experiments typically depend on specific experimental designs and research objectives, and the material is intended strictly for laboratory research use in studies of molecular pharmacology, cancer biology, and preclinical compound evaluation.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ensartinib (X-396) dihydrochloride (CAS No.: 2137030-98-7) 是一种小分子受体酪氨酸激酶抑制剂盐酸盐形式，在生命科学研究中通常归类为以间变性淋巴瘤激酶为核心靶点的多靶点激酶工具化合物，适用于肿瘤生物学、信号转导、耐药机制解析以及中枢神经系统相关药效学模型研究。现有资料表明，该分子以 ALK 为主要作用靶点，并对 MET 及部分其他酪氨酸激酶具有抑制活性，可干预由 ALK 异常激活所驱动的下游信号网络，进而影响与细胞增殖、存活、迁移及适应性耐受相关的分子过程；在突变体层面，其对多种已报道的 ALK 变体亦表现出较强抑制能力，因此常被用于比较野生型与突变型激酶依赖性的实验体系以及获得性耐受模型的机制研究。公开信息还提示该化合物具有一定的血脑屏障通透相关研究价值，使其在脑组织暴露、脑内靶点占领及中枢相关转移模型的药理学评估中受到关注。就体外活性而言，Ensartinib (X-396) dihydrochloride 整体表现为纳摩尔水平的高活性，其中对主要靶点及部分相关激酶的抑制可覆盖低纳摩尔至低双位数纳摩尔范围，因而适用于激酶谱分析、细胞信号抑制实验、靶点验证、联合筛选及耐药突变功能评估等研究场景。在应用方式上，该化合物可用于 ALK 或 MET 相关细胞模型、异种移植或其他动物模型中的药理干预研究，也可作为候选先导或对照分子用于新型抑制剂的构效关系比较与筛选流程优化；而具体实验中所使用的浓度或剂量通常取决于细胞背景、靶点表达状态、给药途径、暴露时程以及研究目的。 ([selleckchem.com](https://www.selleckchem.com/products/ensartinib-dihydrochloride.html?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Ensartinib (X-396) dihydrochloride is a potent small-molecule dual ALK/MET kinase inhibitor used in oncology and signal transduction research.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>一种以ALK为主靶点的多靶点激酶抑制剂，适用于肿瘤与信号转导研究。</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Ensartinib (X-396) dihydrochloride (CAS No.: 2137030-98-7) 是一种面向生命科学研究与药物发现的靶向性小分子激酶抑制剂，通常归类为以间变性淋巴瘤激酶为核心靶点的研究工具化合物，并表现出对MET等相关激酶的抑制活性，因此常被用于受体酪氨酸激酶异常驱动机制的基础研究。现有研究资料表明，该化合物对野生型ALK及多种与耐受表型相关的ALK变体均具有较强抑制作用，能够干预ALK依赖性信号转导网络及其下游增殖与存活相关过程，同时在部分研究背景下显示出跨血脑屏障分布特征，使其在中枢相关肿瘤生物学、耐药机制解析以及脑部暴露特征评估中具有较高的研究价值。从体外活性看，其对ALK及部分相关激酶的作用总体处于低纳摩尔至纳摩尔范围，而在不同细胞背景、基因改变状态和检测体系中，整体活性可概括为纳摩尔至低微摩尔水平。基于这些特征，Ensartinib (X-396) dihydrochloride 常被应用于激酶谱筛选、靶点验证、信号通路抑制实验、耐药突变功能研究、肿瘤细胞增殖与凋亡模型分析，以及动物水平的药效学与组织分布研究；在具体实验实施中，所采用的处理浓度、给药剂量和暴露时间通常需根据细胞类型、模型构建方式、终点指标及研究目的进行优化设定。总体而言，该化合物适合作为研究ALK驱动生物学、旁路激活机制、激酶抑制剂敏感性差异及候选分子筛选策略的重要实验材料，尤其适用于生物医学研究和药物研发中围绕肿瘤信号转导、耐药演化与先导化合物评价的前期探索。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C8800</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>58652-20-3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Nomegestrol Acetate</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Nomegestrol acetate 是一种口服有效的高选择性孕激素，也是孕酮受体 ( progesterone receptor ) 完全激动剂，能抑制排卵。Nomegestrol acetate 还能有效抑制人类子宫内膜癌 RL95-2 细胞体外和体内增殖。Nomegestrol acetate 可用于癌症 (尤其是子宫内膜癌) 和避孕的研究。</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Nomegestrol acetate is a widely used progestin-like drug,which is characterized as a full agonist at the progesterone receptor</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nomegestrol Acetate (CAS No.: 58652-20-3) is a synthetic 19-norprogesterone-derived progestin that is primarily categorized as an endocrine pharmacology and oncology research tool for studies of steroid hormone signaling, reproductive biology, and hormone-responsive tumor models. This small-molecule progesterone receptor agonist is functionally characterized as a highly selective full agonist of the progesterone receptor, with biological activity consistent with modulation of progesterone-responsive transcriptional programs and suppression of ovulation-related endocrine signaling. In biomedical research, its mechanism is generally interpreted through progesterone receptor activation and downstream regulation of hormone-responsive gene networks, while published preclinical findings also indicate associations with pathways linked to endometrial tumor biology, including changes in SUFU, Wnt7a, and mTOR-related signaling contexts. In vitro, reported antiproliferative effects in progesterone-responsive endometrial cancer models are observed in the micromolar to low-micromolar range, whereas potency and response magnitude vary according to receptor status, cell lineage, and experimental conditions. Accordingly, Nomegestrol Acetate is commonly applied in studies using endometrial carcinoma cell models such as RL95-2 and related hormone-responsive systems to investigate receptor-dependent growth control, proliferation, apoptosis-related responses, and pathway crosstalk, and it has also been used in animal-based research settings to examine endocrine and tumor-growth modulation under controlled laboratory conditions. The concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. This product is intended strictly for laboratory research and drug discovery use, including mechanistic studies, pathway interrogation, comparator profiling against other progestins, and screening workflows focused on progesterone receptor biology, and it should not be described as suitable for human consumption, clinical intervention, food use, or any other non-research application.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nomegestrol Acetate (CAS No.: 58652-20-3) 是一种合成甾体类孕激素样研究分子，通常归类为高选择性的孕酮受体调节化合物，在生物医学研究中主要作为解析孕激素信号转导、内分泌调控与激素依赖性细胞行为的工具分子使用。现有研究表明，该分子以孕酮受体为核心作用靶点，并表现为完全激动剂，可调控受体介导的转录过程及其下游与细胞增殖、分化、周期调节和组织反应相关的生物学事件；在生殖内分泌相关研究中，其对排卵相关生理过程具有抑制作用，因此常被用于探讨下丘脑–垂体–性腺轴调控、子宫内膜生物学以及激素响应性组织中的受体依赖机制。在肿瘤生物学方向，Nomegestrol Acetate 也被用于激素敏感性模型的机制研究，尤其可作为评估孕酮受体信号对人子宫内膜癌相关细胞表型影响的研究工具，已有资料提示其可在体外与体内实验条件下抑制 RL95-2 等子宫内膜癌细胞模型的增殖，但更适宜将其表述为用于研究激素受体通路、细胞增殖调控及候选分子筛选中的功能性探针，而非作任何超出基础研究范围的延伸解释。就体外活性特征而言，相关研究通常将其描述为在纳摩尔至微摩尔范围内表现出生物学活性，但具体效应强度、暴露时间与实验终点会因细胞类型、受体表达水平、培养条件及检测方法不同而变化。基于其明确的受体选择性与内分泌调节属性，该分子常见于受体结合研究、报告基因实验、激素响应细胞模型构建、动物内分泌模型以及药物发现早期的机制验证与筛选体系中，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Nomegestrol Acetate is a synthetic 19-norprogesterone-derived progestin and selective progesterone receptor agonist used in endocrine, reproductive biology, and hormone-responsive cancer research.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>一种高选择性孕酮受体激动剂科研分子，用于内分泌调控机制研究。</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Nomegestrol Acetate (CAS No.: 58652-20-3) 是一种合成孕激素类研究分子，通常归入甾体激素相关化合物范畴，在生物医学研究中主要作为孕激素信号调控工具分子使用，适用于围绕内分泌调节、激素受体功能、肿瘤生物学以及生殖相关机制的基础研究与药理评价。现有研究表明，该分子对孕酮受体具有较高选择性，并表现为完全激动剂特征，可通过调节受体依赖性转录过程影响细胞增殖、分化及激素应答网络，同时与排卵抑制相关的内分泌调控现象也常被用于生殖生物学机制研究。在肿瘤研究背景下，Nomegestrol Acetate 已被用于评估激素敏感性细胞系统中的增殖调节效应，尤其可作为研究子宫内膜相关肿瘤细胞激素应答、受体信号转导及下游基因表达变化的候选分子之一；结合已公开的实验信息，其体外活性总体可概括为纳摩尔至微摩尔范围，具体效应强度通常受细胞类型、受体表达状态、培养条件及联合处理因素影响。在应用层面，该分子常见于细胞模型中的受体激活实验、激素反应元件报告基因分析、增殖与周期调控研究，以及动物模型中的内分泌反应观察和药效筛选前期评价；实验中所使用的浓度或剂量通常取决于具体的实验设计、给药方式、模型敏感性与研究目的。对于药物研发相关研究而言，Nomegestrol Acetate 还可作为孕激素受体调节轴的参考分子，用于比较不同候选化合物在受体选择性、功能激动特征和抗增殖表型方面的差异，从而服务于激素依赖性疾病机制探索、先导化合物筛选及药理学方法学建立。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C8801</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>85547-56-4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Piperaquine phosphate</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Piperaquine phosphate 是一种双喹啉抗疟药，可以与青蒿素联用于抗疟研究。</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Piperaquine phosphate is an anti-malaria compound commonly used in combination with artemisinin to inhibit Plasmodium falciparum.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Piperaquine phosphate (CAS No.: 85547-56-4) is a synthetic bisquinoline antiplasmodial small molecule broadly classified as an antimalarial research compound and blood-stage parasite inhibitor, with principal relevance to infectious disease biology, antiparasitic drug discovery, and combination-regimen screening against Plasmodium falciparum. Its pharmacological background is consistent with the quinoline class, and available literature indicates that piperaquine accumulates within the parasite digestive or food vacuole, where it interferes with heme detoxification and suppresses conversion of toxic ferriprotoporphyrin-derived intermediates into inert hemozoin, thereby promoting parasite damage during hemoglobin catabolism; this mode of action is generally discussed as analogous to other quinoline antiplasmodials, although the precise direct molecular target assignment remains incompletely resolved. In this context, the most relevant biological process is the parasite hemoglobin digestion and hemozoin biocrystallization pathway rather than a canonical mammalian signaling cascade, and resistance-associated phenotypes reported in malaria research further support its use as a probe for studying altered drug susceptibility in parasite transport and vacuolar homeostasis networks. In vitro, piperaquine and its phosphate salt are typically described as active against erythrocytic Plasmodium falciparum at nanomolar to low micromolar levels depending on parasite strain, assay format, and resistance background, and the compound is therefore widely used in susceptibility profiling, comparative screening with artemisinin derivatives, and evaluation of cross-resistance patterns among quinoline-like antiplasmodial agents. In biomedical research settings, this molecule is commonly applied in cultured parasite-infected erythrocyte systems, mechanistic studies of food-vacuole biology and β-hematin formation, and in vivo antimalarial efficacy models designed to benchmark partner-compound performance in combination paradigms; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. Because publicly available mechanistic datasets remain more extensive than uniformly standardized target-deconvolution data, this compound is most appropriately represented in catalogs as a research-use antiparasitic tool for interrogation of Plasmodium blood-stage survival, quinoline-associated resistance biology, and antimalarial lead or combination discovery rather than for any non-research application.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Piperaquine phosphate (CAS No.: 85547-56-4) 是一种用于疟原虫生物学与抗寄生虫药理研究的双喹啉类小分子，通常归属于喹啉型抗疟化合物及其磷酸盐形式，主要面向恶性疟原虫等疟原虫血期阶段的实验研究；从研究背景看，该分子并非天然来源代谢物，而是合成获得的经典抗疟研究工具化合物，长期被用于疟原虫药物敏感性评价、联合用药策略探索以及耐药机制解析，尤其常与青蒿素类分子联合作为抗疟药物组合研究中的代表性对象。现有资料表明，其作用机制总体上与喹啉类化合物相近，主要与寄生虫消化液泡中的血红素解毒过程受扰有关，表现为在酸性细胞器内富集并干扰游离血红素向疟色素的转化，从而增强对寄生虫细胞内稳态的不利影响；在机制研究层面，虽然难以将其简单归结为单一蛋白靶点抑制剂，但其药效与恶性疟原虫消化液泡相关转运体系和耐药决定因素密切相关，尤其常结合 PfCRT、PfMDR1 等转运蛋白介导的敏感性变化与耐受表型进行分析，因而常被用于研究消化液泡药物分布、血红素代谢干预及耐药选择压力下的适应性改变。体外活性方面，piperaquine phosphate 在疟原虫培养体系中的活性通常处于纳摩尔至低微摩尔范围，但具体效应强弱会随虫株遗传背景、培养条件、暴露时程及检测终点不同而变化；在应用场景上，该分子常用于受感染红细胞培养模型中的增殖抑制实验、药物联合作用评估、耐药株比较研究及先导化合物筛选参照，也可作为动物疟疾模型中联合给药方案设计与药效动力学研究的比较分子之一，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。总体而言，piperaquine phosphate 在生命科学目录中可被定位为面向疟原虫药理学、寄生虫细胞生物学及抗感染候选物筛选研究的重要参考化合物，其核心价值在于为解析疟原虫血期生存依赖通路、药物反应异质性以及与青蒿素类或其他抗疟分子的相互作用提供稳定的实验研究基础。</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Piperaquine phosphate is a synthetic bisquinoline antiplasmodial compound that disrupts parasite heme detoxification and hemozoin formation, enabling antimalarial and Plasmodium falciparum resistance research.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>一种用于疟原虫血期生物学与抗寄生虫药理研究的喹啉类化合物。</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Piperaquine phosphate (CAS No.: 85547-56-4) 是一种喹啉类小分子抗疟研究化合物，通常归属于双喹啉相关化学类别，主要用于疟原虫生物学、寄生虫药理学及抗感染药物发现领域的基础研究与筛选体系构建；其研究背景主要围绕疟原虫在红细胞内阶段对宿主血红蛋白降解后所产生毒性血红素的处置过程展开，现有证据表明该化合物的作用机制与疟原虫消化液泡内血红素解毒过程受扰有关，可抑制有毒血红素向惰性疟色素的转化，从而影响恶性疟原虫等寄生虫的生长与存活，同时其药效学和耐受性表型还与疟原虫消化液泡膜转运体相关分子网络密切相关，尤其常结合对 PfCRT 介导转运改变以及 PfMDR1 相关敏感性差异的研究进行分析，因此常被用于解析药物进入、富集、外排及耐药选择压力等关键问题；从体外活性看，Piperaquine phosphate 在不同恶性疟原虫分离株和培养模型中通常表现为纳摩尔至低微摩尔范围的抑制水平，但具体敏感性会随虫株遗传背景、培养阶段、暴露时间及联用设计而变化；在应用层面，该分子常见于疟原虫细胞培养模型、耐药机制研究、联合用药相互作用评价、先导化合物比较研究以及啮齿类疟原虫动物模型中的药效学观察，也可作为参考分子用于建立表型筛选平台和验证消化液泡相关作用通路，实验中所使用的浓度或剂量通常取决于具体的实验设计、检测终点与研究目的；总体而言，该化合物在生命科学研究目录中可被定位为面向寄生虫学与抗感染药物研发的机制研究工具分子，适用于围绕疟原虫血红素代谢、药物转运、耐药演化及组合筛选策略开展系统性生物医学研究。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C8802</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10017-44-4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>D-Carnitine hydrochloride</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>D-Carnitine hydrochloride ((S)-Carnitine Hydrochloride) is a constituent of striated muscle and liver. It is used therapeutically to stimulate gastric and pancreatic secretions and in the treatment of hyperlipoproteinemias.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>D-Carnitine hydrochloride (CAS No.: 10017-44-4) is a chiral carnitine derivative and small-molecule biochemical reagent broadly classified within metabolism research, particularly in studies of mitochondrial fatty-acid utilization, membrane transport, and stereoselective nutrient handling; carnitine is a naturally occurring quaternary ammonium metabolite enriched in tissues with high oxidative demand, including striated muscle and liver, and its biological context is closely linked to the carnitine shuttle that supports translocation of fatty-acyl groups into mitochondria for β-oxidation, although the D-enantiomer is generally considered a nonphysiologic or less functionally compatible stereoisomer relative to the endogenous L-form. In biomedical research, the most relevant experimentally supported molecular association is with the high-affinity sodium-dependent carnitine transporter OCTN2/SLC22A5, which governs cellular carnitine uptake and thereby influences fatty-acid metabolic flux; more broadly, carnitine-dependent biology intersects functionally with the CPT1/CACT/CPT2 transport axis and downstream mitochondrial energy-homeostasis pathways rather than with a canonical receptor-mediated signaling cascade. Available evidence indicates that stereoselective transport and interaction with carnitine-handling systems occur in the micromolar range, whereas direct quantitative activity data specific to D-carnitine hydrochloride remain limited, so rigorous catalog annotation should treat potency, target selectivity, and pathway engagement as transport- and metabolism-associated rather than as definitively established enzyme inhibition or receptor agonism. Accordingly, this compound is primarily used as a research tool for probing enantiomer-specific transport behavior, competitive or modulatory effects on cellular carnitine uptake, metabolic phenotype characterization, and assay development in transporter-expressing cell systems, with additional potential utility in mechanistic studies of mitochondrial substrate utilization, lipid catabolism, and comparative metabolite handling in biochemical or animal models; the concentrations or doses used in experiments typically depend on specific experimental designs, model systems, and research objectives.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>D-Carnitine hydrochloride (CAS No.: 10017-44-4) 属于肉碱类小分子及其盐酸盐形式，是肉碱的对映异构体之一，通常被归入能量代谢与脂质代谢研究相关的代谢调节分子范畴；从生物学背景看，肉碱体系广泛参与真核细胞尤其是高能量需求组织中的脂酰基转运与线粒体代谢过程，而该化合物作为D-构型分子，主要用于研究肉碱系统的立体选择性、转运识别特征及其对细胞代谢网络的影响。现有研究表明，肉碱相关生物学过程的核心分子基础主要涉及质膜转运体 SLC22A5/OCTN2 介导的钠依赖性摄取，以及与线粒体脂肪酸转运密切相关的肉碱穿梭系统，包括 CPT1、CACT 与 CPT2 等环节；基于这些已确立的机制，D-肉碱盐酸盐通常被视为用于解析肉碱转运竞争、底物识别偏好、脂肪酸进入线粒体前转运步骤以及后续β-氧化通量变化的研究工具，其作用更多体现为对天然肉碱通路的干预性或鉴别性探针，而非作为经典意义上的高选择性受体激动剂或酶抑制剂。就机制研究而言，相关文献一致支持肉碱稳态与OCTN2转运活性密切相关，且该转运过程受膜环境、离子耦联状态及底物构型影响；因此，D-Carnitine hydrochloride 在实验上常被用于评估肉碱转运体的立体专一性、细胞脂质利用能力、线粒体氧化代谢适应性，以及与能量感知网络相关的继发性变化。关于体外活性，由于公开资料中针对该CAS对应化合物的标准化定量药理数据较为有限，当前更适合将其概括为在体外研究中通常于微摩尔至毫摩尔范围内考察其对转运、代谢读出或竞争效应的影响，而不宜赋予缺乏直接证据支持的特定数值靶点参数。应用层面上，该分子可用于细胞摄取实验、转运体功能分析、线粒体代谢表型研究、脂质负荷或营养应激模型中的机制验证，以及作为药物研发早期阶段中评估候选化合物是否影响肉碱依赖性代谢通路的辅助研究试剂；在动物模型或细胞模型中的具体浓度、暴露时间与给药方案通常取决于实验设计、模型类型及研究目的，实际使用时应结合立体异构体特性、转运体系表达水平及预设终点进行优化。</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D-Carnitine hydrochloride is a chiral carnitine derivative that modulates OCTN2/SLC22A5-associated carnitine transport and is used in metabolism and mitochondrial fatty-acid utilization research.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>一种用于肉碱转运立体选择性与线粒体代谢研究的科研试剂。</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>D-Carnitine hydrochloride (CAS No.: 10017-44-4) 作为肉碱类小分子的盐酸盐形式，通常被归类为内源性代谢物相关研究工具和脂肪酸转运通路研究分子，其对应的肉碱骨架与细胞能量代谢、线粒体脂酰基转运以及有机阳离子跨膜转运密切相关；从生物学背景看，肉碱体系广泛存在于动物组织并参与脂肪酸进入线粒体进行氧化代谢的过程，而D-构型通常被视为与天然L-构型相对应的对映体，因此在生命科学研究中更常被用于探讨立体选择性识别、转运竞争、代谢稳态扰动及肉碱依赖过程的机制差异。基于现有研究与同类分子知识，D-Carnitine hydrochloride 的主要相关靶点并非经典受体或激酶，而更可能集中于肉碱转运系统与线粒体相关载体，包括细胞膜上的高亲和力肉碱转运蛋白 OCTN2 以及线粒体内膜的肉碱酰基肉碱转位体系；其作用机制通常表现为对天然肉碱摄取过程的竞争性干预、对钠离子依赖性跨膜转运的影响，以及继发性调节脂肪酸β氧化底物供给、酰基肉碱平衡和细胞能量代谢状态。就体外研究而言，公开资料对该特定盐酸盐形式的定量活性数据较为有限，因此更适宜依据肉碱类似物的一般规律进行概括，即其在转运体相关实验中的效应常见于微摩尔至毫摩尔范围，而在更高灵敏度的转运或结合模型中也可能表现为低微摩尔水平的干预特征，但具体活性强度、选择性和实验终点通常取决于细胞类型、转运体表达水平、培养条件以及是否与L-肉碱或其他底物共同存在。研究应用上，该分子常适用于构建细胞摄取模型、线粒体代谢研究、转运体底物竞争实验、营养代谢重编程分析以及药物筛选中的机制对照体系，也可用于动物模型中评估肉碱通路扰动对组织能量利用和代谢表型的影响；在这些研究场景中，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。总体而言，D-Carnitine hydrochloride 在生物医学研究中的价值主要体现在其可作为解析肉碱转运网络、能量代谢耦联关系及对映体选择性生物学效应的重要工具分子，尤其适合用于代谢生物学、线粒体功能研究、转运体药理学和药物发现早期筛选中的机制性研究。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C8803</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5907-38-0</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Metamizole sodium hydrate</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Metamizole sodium hydrate (Dipyrone) 是一种有口服活性的环氧合酶 ( COX ) 抑制剂。Metamizole sodium hydrate 可抑制细胞增殖，促进细胞凋亡。Metamizole sodium hydrate 有抗炎和抗氧化活性。Metamizole sodium hydrate 是一种解热镇痛解痉剂。Metamizole sodium hydrate 可用于缓解各种疼痛的研究。</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Metamizole sodium hydrate (Analgin) is a potent analgesic drug that has been demonstrated to inhibit cyclooxygenase (COX). Target: COX Dipyrone is a potent analgesic and antipyretic drug that has been used clinically for more than 80 years.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Metamizole sodium hydrate (CAS No.: 5907-38-0) is a pyrazolone-derived small molecule widely used as a pharmacological research tool in inflammation, nociception, stress-response, and cell-fate studies, and it is primarily categorized as a cyclooxygenase inhibitor with additional functional relevance in oxidative stress and apoptosis-related research. Reported reference data identify cyclooxygenase enzymes, including COX-1 and COX-2, as the principal targets, supporting its use for interrogation of prostaglandin-dependent signaling and related inflammatory pathways, while published product and literature descriptions further indicate context-dependent effects on cellular proliferation, apoptotic regulation, and redox-associated biological responses. Available experimental information suggests that direct enzyme-modulatory activity has been observed at micromolar-range concentrations in biochemical settings, whereas cellular phenotypes such as proliferation changes, apoptosis induction, or modulation of oxidative injury are typically examined across micromolar to higher exposure ranges depending on model system, exposure time, and assay format. In biomedical research, this compound is therefore applied as a reference or comparator molecule in cell-based assays, mechanistic studies of COX-linked signaling, evaluation of inflammation-associated phenotypes, and exploratory screening workflows involving viability, apoptosis, and oxidative stress endpoints; it may also be incorporated into animal studies designed to investigate pharmacodynamic responses relevant to inflammatory or pain-related biology under strictly preclinical conditions. Because detailed potency and pathway-resolution data remain limited or model dependent for the hydrate form, experimental interpretation should be anchored to study-specific validation, and the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Metamizole sodium hydrate (CAS No.: 5907-38-0) 是一种吡唑酮类小分子研究化合物，通常作为安乃近相关物质被归入以环氧合酶调控为核心特征的药理学研究体系，长期用于炎症反应、伤害感受、发热反应及平滑肌应答相关机制的基础研究；从生物医学研究角度看，该分子并非来源于天然生物大分子，而属于具有明确药理活性的有机合成化合物，其研究重点主要集中于花生四烯酸代谢网络、前列腺素生成调控、氧化应激反应以及细胞命运调节等方向。现有研究资料表明，Metamizole sodium hydrate 的关键作用机制与环氧合酶活性抑制及其下游脂质介质生成变化密切相关，并可能进一步影响炎症相关信号转导、氧化还原稳态及应激条件下的细胞增殖与凋亡过程；在不同实验系统中，其药理效应还常被用于解析外周炎症介质与中枢痛觉调控之间的联系，以及炎症刺激、热应激和组织损伤背景下的反应性分子网络。就体外研究而言，该分子的活性通常可概括为微摩尔范围，且具体表现会受到细胞类型、刺激条件、终点指标及给药时程等因素显著影响，因此在细胞实验中常被用于评估炎症介质释放、氧化损伤标志物变化、细胞活力、凋亡水平及相关酶活性调节。于转化前研究阶段，Metamizole sodium hydrate 也可作为工具化合物应用于细胞模型、动物模型及候选分子筛选流程中，用于比较不同COX调节剂在炎症、疼痛样行为、生理性发热反应和应激相关表型中的差异性效应；实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。总体而言，该分子在生命科学目录中的定位更适合表述为一种用于研究环氧合酶相关脂质介质通路、炎症生物学、氧化应激调控及细胞应答机制的经典小分子参考化合物。</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Metamizole sodium hydrate is a pyrazolone-derived cyclooxygenase inhibitor targeting COX-1/COX-2, widely utilized in inflammation, nociception, oxidative stress, and apoptosis-related research.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>一种用于环氧合酶相关脂质介质通路与炎症应答研究的小分子化合物。</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Metamizole sodium hydrate (CAS No.: 5907-38-0) 是一种吡唑酮类小分子化合物，通常归入非甾体抗炎相关研究分子与环氧合酶调节剂范畴，在生物医学研究中主要作为经典镇痛解热药物的机制研究工具和药理参照物使用；其母体化合物经代谢转化后发挥主要生物学效应，现有资料表明其已知核心作用轴与环氧合酶相关的花生四烯酸代谢网络密切相关，并涉及前列腺素生成调控、炎症反应调节以及氧化应激相关过程，同时在部分细胞系统中可影响增殖与程序性细胞死亡，已有研究提示其可通过与 bax、bcl-2 和 caspase-3 相关的凋亡调控通路改变细胞命运；从体外活性特征看，其作用强度多表现于微摩尔至较高微摩尔范围，不同细胞类型、暴露时间及代谢条件可导致明显差异，因此更适合作为机制探索而非单一高选择性探针来解读实验结果；在研究场景上，该分子常用于炎症介质释放、氧化损伤应答、细胞活力变化、肿瘤相关表型筛查及药物联用效应评估，也可在动物实验中作为药理学背景干预分子用于观察应激、炎症和组织损伤相关指标的变化，但其具体浓度或剂量通常需根据实验模型、给药方式、观察终点及研究目的进行优化；总体而言，Metamizole sodium hydrate 适用于围绕环氧合酶信号、脂质介质生物学、细胞应激反应及候选药物筛选体系开展基础与转化前研究。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C8804</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>172152-50-0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ilaprazole sodium</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Ilaprazole (IY-81149) sodium，一种具有口服活性质子泵抑制剂，以剂量依赖性方式不可逆地抑制 H + /K + -ATPase ，在兔壁细胞制剂中的 IC 50 为 6 μM。Ilaprazole sodium 用于胃溃疡的研究。Ilaprazole sodium 也是一种有效的T细胞起源蛋白激酶 ( TOPK ) 抑制剂。</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ilaprazole sodium (IY-81149 sodium) , a substituted benzimidazole prodrug, is a selective and irreversible proton pump inhibitor. A weak base, Ilaprazole accumulates in the acidic environment of the secretory canaliculus of the gastric parietal cell where it is converted to an active sulfenamide form that binds to cysteine sulfhydryl groups on the luminal aspect of the proton pump hydrogen-potassium adenosine triphosphatase (H+/K+ ATPase), thereby inhibiting the pump's activity and the parietal cell secretion of H+ ions into the gastric lumen, the final step in gastric acid production.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ilaprazole sodium (CAS No.: 172152-50-0) is a small-molecule benzimidazole-derived research compound broadly classified as a proton pump inhibitor and additionally reported as a kinase-modulating agent, making it relevant to gastric acid secretion biology, epithelial physiology, and oncology-oriented target discovery workflows. In biochemical and cellular research settings, it is characterized as a selective, irreversible inhibitor of the gastric H+/K+-ATPase proton pump, functioning as an acid-activated prodrug that preferentially accumulates in acidic secretory compartments and is converted to a reactive intermediate that covalently engages luminal cysteine residues of the pump, thereby suppressing the terminal step of proton secretion; published research sources also describe inhibitory activity against T-cell-originated protein kinase, supporting its use in studies of mitotic signaling and cancer-associated kinase networks. Reported in vitro activity lies in the micromolar range, including low micromolar inhibition of H+/K+-ATPase-associated activity in parietal cell preparations, while its broader pharmacology is generally investigated through mechanism-focused profiling rather than as a highly promiscuous screening scaffold. Within life sciences research, Ilaprazole sodium is commonly positioned as a tool compound for investigating proton pump biology, acid-dependent cellular processes, gastric mucosal injury models, and TOPK-related signaling hypotheses in cell-based assay systems and preclinical animal studies; the concentrations or doses used in experiments typically depend on specific experimental designs, model systems, and research objectives.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ilaprazole sodium (CAS No.: 172152-50-0) 是 ilaprazole 的钠盐形式，通常归类为取代苯并咪唑类质子泵抑制剂相关研究分子，在生命科学与药物发现领域主要作为胃壁细胞酸分泌调控机制研究工具及激酶筛选候选分子使用；现有资料表明，该化合物属于前药性质的弱碱性分子，在酸性微环境中可发生转化并与胃壁细胞分泌小管侧相关的 H+/K+-ATPase 发生不可逆作用，从而抑制质子转运过程并影响酸分泌终末步骤，同时也被报道可作用于 T 细胞来源蛋白激酶 TOPK，因而可被纳入膜转运调控、酸分泌生物学、应激相关信号转导以及肿瘤相关激酶通路研究框架中；从体外活性特征看，其对相关靶点的作用总体可概括为低微摩尔至微摩尔范围，提示其适用于机制验证、靶点关联分析及先导化合物比较研究；在实验应用上，Ilaprazole sodium 常见于胃壁细胞或其他适宜细胞模型中的功能测定、酶活性评估、信号通路干预实验，以及动物模型中的药理学探索和化合物筛选研究，用于观察质子泵功能抑制、细胞增殖调控或下游分子事件变化等现象，但具体实验中所采用的浓度或剂量通常取决于模型类型、给药方式、检测终点与研究目的；总体而言，该分子适合作为研究质子泵生物学、酸性细胞器相关过程及 TOPK 介导信号网络的实验工具化合物，为基础机制解析和早期药物研发中的活性评价提供参考。 ([pubchem.ncbi.nlm.nih.gov](https://pubchem.ncbi.nlm.nih.gov/compound/Ilaprazole?utm_source=openai))</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Ilaprazole sodium is a benzimidazole-derived proton pump inhibitor targeting gastric H+/K+-ATPase and TOPK, utilized in gastric acid biology, epithelial physiology, and oncology research.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>一种用于质子泵调控与TOPK信号研究的科研分子。</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Ilaprazole sodium (CAS No.: 172152-50-0) 是一种苯并咪唑类小分子化合物，通常被归类为质子泵抑制剂相关研究分子，在生物医学研究中主要用于胃酸分泌调控、胃黏膜损伤相关机制解析以及酸性微环境依赖性药理过程的实验探索；从作用特征来看，该分子属于可在酸性条件下发生转化并与靶蛋白形成稳定相互作用的前体型化合物，其经典研究靶点为胃壁细胞膜相关的 H+/K+-ATPase，通过对终末酸分泌步骤的持续性抑制，影响细胞外酸化过程及相关分泌功能，同时已有研究提示其还可作为 TOPK 相关信号调控的研究工具分子，用于探讨增殖、应激反应与肿瘤生物学过程中的激酶介导机制；现有体外研究表明，其活性总体处于微摩尔范围，可用于评估酸分泌调节、靶点响应及通路干预效应，并常见于胃上皮相关细胞体系、分泌功能模型、酶活分析体系以及动物实验中的药效学研究与先导化合物筛选场景。该分子的实验用途主要集中于机制研究、活性比较研究和药理表型评价，具体采用的处理浓度或给药剂量通常需根据模型类型、观察终点和研究目的进行优化设定；在生命科学研究目录中，可将其概括为一种适用于消化系统相关基础研究、膜转运与离子泵调控研究以及激酶信号通路探索的研究用小分子工具化合物。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C8805</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>81025-04-9</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Lactitol monohydrate</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Lactitol monohydrate (D-Lactitol monohydrate) 是乳果糖的糖类似物。Lactitol monohydrate 作为益生元被肠道菌群发酵，促进有益菌 (如乳酸杆菌、双歧杆菌) 生长，抑制致病菌，增加挥发性脂肪酸产生，降低氨水平。Lactitol monohydrate 用作替代甜味剂。Lactitol monohydrate 可用于便秘和肝性脑病的研究。</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Lactitol monohydrate (D-Lactitol monohydrate) is a disaccharide analog of lactulose. It has been widely used to treat constipation and hepatic encephalopathy.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lactitol monohydrate (CAS No.: 81025-04-9) is a synthetic nonabsorbable carbohydrate and disaccharide analog of lactulose that is primarily classified as a microbiome-modulating research reagent and functional saccharide for gastrointestinal and metabolic biology studies. As a crystalline hydrate form of lactitol, it is generally investigated in biomedical research as a fermentable substrate for intestinal microorganisms rather than as a direct high-affinity ligand for a canonical protein target; accordingly, its principal biological activity is understood to arise from microbiota-dependent fermentation in the lower gut, leading to enrichment of beneficial bacterial populations such as Lactobacillus and Bifidobacterium, increased production of short-chain fatty acids, luminal acidification, osmotic effects on water handling, and reduced intestinal ammonia burden through promotion of ammonium trapping under lower-pH conditions. On this basis, Lactitol monohydrate is commonly placed within prebiotic, gut microbiota, host-microbe interaction, and ammonia metabolism research programs, and it is also relevant to studies of intestinal barrier physiology, microbial ecology, and carbohydrate utilization. Specific pathway annotation is limited, and currently available evidence supports an indirect mechanism involving microbial fermentation networks and downstream metabolic signaling associated with short-chain-fatty-acid-responsive processes rather than a defined receptor-selective or enzyme-selective mode of action. Consistent with this systems-level mechanism, discrete in vitro potency metrics such as IC50, EC50, or MIC values are not well established for this compound in standard target-based assay formats, so activity is more appropriately characterized through functional readouts including changes in microbial growth composition, fermentation products, medium acidification, ammonia handling, and phenotype modulation in intestinal or fecal culture systems. In experimental practice, Lactitol monohydrate may be used in cell-associated co-culture platforms, ex vivo fecal fermentation assays, microbiome profiling workflows, and animal models designed to examine gut microbial composition, nitrogen metabolism, or bowel function biology, with the concentrations or doses used in experiments typically depending on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lactitol monohydrate (CAS No.: 81025-04-9) 是一种乳果糖相关的二糖醇类糖类似物，可归入可发酵性碳水化合物与研究级功能性赋形分子范畴，其活性本质通常与 lactitol 母体一致；现有资料表明，该分子在上消化道吸收有限，因而常被用于肠道微生态、宿主—微生物代谢互作以及营养型小分子干预模型的基础研究，尤其适用于关注结肠发酵过程、菌群组成变化和含氮代谢物转化的实验场景。基于公开数据库与综述性信息，Lactitol monohydrate 的主要生物学作用并不体现为经典意义上的高亲和力单一受体结合，而是通过作为肠道微生物可利用底物被发酵，进而促进乳酸杆菌、双歧杆菌等有益菌群扩增，调节短链脂肪酸及相关挥发性脂肪酸生成，并影响肠腔渗透环境、酸化状态及氨代谢负荷，因此其研究机制更多涉及微生态重塑、代谢通量改变与肠道屏障相关生理过程，而非明确的专属性药理靶点。就药理研究范式而言，目前更适合将其定义为以菌群依赖性代谢效应为核心的研究工具分子，其可能关联的生物学通路包括碳水化合物发酵、短链脂肪酸介导的细胞信号调节以及肠道环境变化所引发的继发性免疫与代谢响应；然而，针对该单水合物本身的标准化靶点数据、直接受体谱和统一的体外效力参数仍较为有限，因此若需描述体外活性，宜表述为其不属于典型以纳摩尔至微摩尔范围直接作用于分子靶标的化合物，而更常在细胞共培养体系、厌氧菌发酵体系、肠道类器官模型或动物肠道生态模型中，以基于培养条件和给药设计而变化的浓度或剂量进行功能评估。该分子常见于肠道菌群结构分析、发酵产物定量、氮代谢负荷观察、糖醇类分子筛选以及与其他益生元或碳源进行对照的实验设计中，能够为解析微生物代谢适应、宿主代谢重编程及候选分子在复杂生物系统中的间接调控效应提供参考；对于缺乏直接实验参数的情形，通常可依据其作为二糖醇及乳果糖相关类似物的类别特征，对其在微生物发酵依赖型研究中的行为进行合理外推。</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Lactitol monohydrate is a synthetic nonabsorbable disaccharide and microbiome-modulating functional saccharide used in gut microbiota, ammonia metabolism, and host-microbe interaction research.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>一种用于肠道菌群发酵与代谢互作研究的二糖醇类分子。</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Lactitol monohydrate (CAS No.: 81025-04-9) 是一种糖醇类二糖衍生物，可视为乳果糖的结构类似物，在生命科学研究中通常归入非消化性碳水化合物、微生物发酵底物及功能性研究试剂范畴；其主要研究背景集中于肠道微生态调控、宿主—菌群代谢互作、含氮代谢稳态以及与肠道发酵相关的药理学前期评价。现有资料表明，该分子在哺乳动物上消化道中吸收有限，进入下消化道后可被肠道共生菌利用，表现出典型的底物依赖性益生元样作用，其机制并非基于单一经典受体直接结合，而主要通过选择性促进乳酸杆菌、双歧杆菌等菌群增殖，增强短链脂肪酸等发酵代谢物形成，降低肠腔 pH，并在氮代谢研究中通过促进氨向离子化形式转化及肠道排出而影响相关生物学过程，因此其“靶点”更适合界定为肠道微生物群落组成、菌群发酵通路及由此牵引的代谢网络，而非明确的单一蛋白靶标。就信号与功能层面而言，Lactitol monohydrate 常被用于观察微生物代谢产物变化与上皮屏障稳态、炎症相关分子表达及肠腔环境酸化之间的关联，在机制研究上常与菌群来源有机酸生成、宿主代谢应答及肠道生态位重塑一并考察。由于该化合物的研究重点多集中于发酵特性和系统代谢效应，而非典型受体药理学，因此公开资料中缺乏可普遍外推的标准化单靶点体外活性参数；若用于体外实验，其有效观察窗口通常更适合概括为高微摩尔至毫摩尔范围的底物暴露条件，具体浓度需依据细胞类型、共培养体系、厌氧发酵模型或菌群来源样本而调整。在应用场景上，Lactitol monohydrate 可作为细胞—菌群互作研究、体外厌氧粪菌发酵模型、肠道代谢物分析、动物肠道生态干预实验以及肠道相关筛选平台中的对照或功能性碳源，用于评估菌群组成变化、发酵终产物谱、含氮代谢指标及与屏障功能相关的分子响应；实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。总体而言，该分子更适合作为研究肠道微生态营养底物效应、发酵驱动型代谢调节及相关药物研发早期机制验证的工具化合物，在生物医学研究目录中可归类为面向肠道菌群与代谢研究的功能性糖醇类试剂。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C8806</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>106463-17-6</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tamsulosin hydrochloride</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tamsulosin hydrochloride ((R)-(-)-YM12617 free base) 是一种口服活性的 α 1 肾上腺素能受体 ( α 1 -adrenergic receptor ) 拮抗剂。Tamsulosin hydrochloride 诱导凋亡 ( Apoptosis )。Tamsulosin hydrochloride 常用于前列腺增生的研究。在动物模型中，Tamsulosin hydrochloride 可减缓腹主动脉瘤的生长、抑制炎症。</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tamsulosin hydrochloride (Flomax hydrochloride) is the hydrochloride salt of tamsulosin, a sulfonamide derivative with α1 adrenergic antagonist activity.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tamsulosin hydrochloride (CAS No.: 106463-17-6) is a synthetic small-molecule adrenergic receptor modulator, commonly classified as a selective α1-adrenergic receptor antagonist and broadly used as a pharmacological tool in urogenital biology, smooth-muscle signaling, vascular inflammation, and mechanism-oriented drug discovery research. As the hydrochloride salt of tamsulosin, it is functionally associated with high-affinity antagonism of α1-adrenoceptor subtypes, with preferential activity toward α1A- and α1D-adrenergic receptors relative to α1B, thereby supporting its use in studies of receptor subtype selectivity, sympathetic neurotransmission, and downstream contractile signaling mediated through Gq/11-linked pathways, including phospholipase C activation, inositol phosphate turnover, intracellular calcium mobilization, and related smooth-muscle response networks. Available binding and pharmacology data indicate very high in vitro potency, typically in the subnanomolar to low-nanomolar range for receptor interaction, while functional effects in cellular assays are generally investigated across nanomolar to micromolar concentrations depending on receptor expression context, assay design, and endpoint selection. In research settings, this compound is used to interrogate adrenergic regulation in engineered receptor systems and native cell models, and it has also been reported to promote apoptosis in selected experimental contexts and to suppress inflammatory processes and lesion progression in certain animal models, supporting broader investigation of α1-adrenergic signaling in tissue remodeling and disease-related pathophysiology. Typical applications include receptor binding studies, pathway deconvolution experiments, phenotypic screening, comparative antagonist profiling, and in vivo pharmacology in models of lower urinary tract dysfunction, vascular injury, or inflammation, with the concentrations or doses used in experiments typically depending on specific experimental designs and research objectives.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tamsulosin hydrochloride (CAS No.: 106463-17-6) 是一种以α1肾上腺素能受体为主要研究靶点的小分子受体拮抗剂，通常归类为选择性α1受体调节化合物，在生物医学研究中常作为解析交感神经相关平滑肌信号调控、受体亚型药理学及炎症相关病理过程的工具分子。现有资料表明，其主要作用机制与对α1A及α1D肾上腺素能受体的拮抗活性相关，并可干预去甲肾上腺素介导的下游收缩与应激信号转导过程；从受体药理特征看，该分子对α1A受体表现出较高亲和倾向，同时对α1D亚型亦具有明确活性，因此被广泛用于研究受体亚型选择性、平滑肌张力调节以及相关组织反应。基于公开研究与数据库信息，Tamsulosin hydrochloride 常见于泌尿生物学、前列腺相关基础研究、血管生物学及炎症调控研究场景，也可作为比较不同α1受体拮抗剂药理差异的参照化合物；在部分细胞和动物实验体系中，该分子还被用于观察炎症反应、组织重塑及细胞命运调控变化，但其诱导凋亡或影响病理进展的现象具有模型依赖性，相关结果应结合具体实验背景审慎解释。就体外活性而言，其研究使用浓度通常概括为纳摩尔至微摩尔范围，具体活性水平受受体表达谱、细胞类型、检测终点及配体刺激条件影响较大。在应用层面，该化合物可用于细胞功能实验、受体结合与拮抗评价、信号通路干预研究、动物模型药效学探索以及候选分子筛选中的阳性对照或机制对照，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Tamsulosin hydrochloride is a selective α1-adrenergic receptor antagonist targeting α1A/α1D subtypes, widely used in urogenital biology, smooth-muscle signaling, and inflammation research.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>一种选择性α1肾上腺素能受体拮抗剂，用于受体药理与信号调控研究。</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Tamsulosin hydrochloride (CAS No.: 106463-17-6) 是坦索罗辛的盐酸盐形式，属于选择性α1肾上腺素能受体拮抗剂，通常被归入用于研究交感神经信号调控与平滑肌反应的经典小分子工具化合物，其药理学特征主要与α1A和α1D受体亚型的较高亲和性相关，并在部分组织中表现出相对弱于上述亚型的α1B相关作用，因而常被用于前列腺、血管、输精管及其他表达α1肾上腺素能受体组织的受体分型、配体结合和功能阻断研究。现有研究表明，α1肾上腺素能受体属于G蛋白偶联受体家族，主要通过Gq或G11相关信号转导调节磷脂酰肌醇水解、细胞内钙动员以及下游收缩和应激反应，因此Tamsulosin hydrochloride 可作为研究去甲肾上腺素能张力、平滑肌收缩控制及受体亚型选择性的实验干预分子。在体外体系中，其活性通常处于纳摩尔至低微摩尔范围，具体效应强度受受体亚型表达谱、细胞背景、检测终点和配体竞争条件影响。在机制层面，该化合物主要通过抑制α1肾上腺素能受体介导的信号传递而改变收缩、增殖及炎症相关过程，部分研究还提示其在特定实验条件下可影响细胞凋亡及炎症反应，从而扩展了其在血管重塑和组织病理生物学中的研究价值。基于这些特征，Tamsulosin hydrochloride 常用于细胞模型中的受体药理学评价、放射性配体结合实验、平滑肌功能测定、炎症与凋亡相关机制探索，以及动物模型中的疾病过程调控研究；在腹主动脉瘤等实验模型中，已有报道显示其可减缓病变进展并抑制炎症反应，但这类观察主要服务于机制研究与药理筛选。总体而言，Tamsulosin hydrochloride 是研究α1肾上腺素能受体生物学、组织选择性药理学以及神经体液调节相关病理过程的重要参考分子，而实验中所使用的浓度或剂量通常取决于具体的实验设计、模型类型和研究目的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C8807</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3486-67-7</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Palmatine</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Palmatine 是一种具有口服活性的、不可逆的 IDO-1 抑制剂，对 HEK 293-hIDO-1 和 rhIDO-1 的 IC 50 分别为 3 μM 和 157 μM。Palmatine 也能非竞争性抑制西尼罗病毒 (WNV) NS2B-NS3 蛋白酶， IC 50 为 96 μM。Palmatine 具有抗癌、抗炎、神经保护、抗细菌、抗病毒活性。</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1. Palmatine (Burasaine) is an inhibitor of dopamine generation. 2. Palmatine could potentially be developed for the treatment of flavivirus infections. 3. Palmatine has been used in the treatment of jaundice, dysentery, hypertension, inflammation, and liver-related diseases.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Palmatine (CAS No.: 3486-67-7) is a naturally occurring protoberberine isoquinoline alkaloid of plant origin that is widely classified as a bioactive natural-product tool compound for inflammation, infection, neurobiology, and oncology-related research. In biomedical and drug discovery settings, it is primarily studied as a small-molecule modulator of enzymatic and signaling processes, with reported activity against indoleamine 2,3-dioxygenase 1 (IDO1), including irreversible inhibition observed in recombinant and engineered cell-based systems, and noncompetitive inhibition of the West Nile virus NS2B-NS3 protease, supporting its use in mechanistic studies of immune-metabolic regulation and flaviviral target validation. Available in vitro findings indicate activity generally in the micromolar range, with comparatively stronger effects in some cellular IDO1 assay formats and broader moderate-potency effects across antiviral, antibacterial, inflammatory, and cancer biology models. Mechanistically, published studies and broader literature on palmatine-associated pharmacology indicate modulation of pathways linked to NF-κB, NLRP3 inflammasome signaling, oxidative-stress-responsive networks such as Nrf2, and neurotransmitter-related processes including dopamine generation, while additional work suggests effects on ion transport and epithelial secretory signaling through chloride channel- and potassium channel-associated mechanisms. Consistent with its natural-product pharmacology profile, palmatine is commonly positioned in screening cascades for target-based inhibitor discovery, phenotypic assays evaluating inflammatory or microbial responses, and exploratory studies in cultured mammalian cells, enzyme systems, and selected animal models; the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. This product is intended strictly for laboratory research use, including pathway interrogation, assay development, and compound-comparator studies, and should not be described or used for human consumption, clinical application, or any non-research purpose.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Palmatine (CAS No.: 3486-67-7) 是一种来源于多种药用植物的天然异喹啉类原小檗碱型生物碱，常见于黄连、黄柏及防己属等植物相关研究体系中，因其明确的天然产物背景、可测定的分子靶点作用以及较广的药理学研究覆盖面，而被广泛用于生物医学基础研究与先导化合物筛选。现有资料表明，Palmatine 可作为吲哚胺 2,3-双加氧酶 1（IDO-1）抑制剂，并对西尼罗病毒 NS2B-NS3 蛋白酶表现出非竞争性抑制作用，其体外活性总体处于微摩尔范围，其中部分细胞体系可见低微摩尔水平活性；此外，既往研究还提示其可影响多巴胺相关生成过程，并与炎症调控、病原体应答、肿瘤相关生物学过程及神经系统损伤应答等方向有关。基于这些特征，Palmatine 常被归入天然产物化学生物学、免疫代谢研究、抗感染机制探索、神经生物学及肿瘤生物学等研究领域，可用于细胞模型中的靶点验证、通路干预、表型筛选与机制追踪，也可在动物模型中作为研究性工具分子用于观察其对免疫微环境、炎症信号、病毒复制相关过程或组织损伤应答的调节趋势。就机制层面而言，除直接靶向 IDO-1 与病毒蛋白酶外，文献综述还显示其可能涉及氧化应激、炎症因子网络以及与细胞存活、凋亡和应激响应相关的多通路调控，但具体效应通常依赖于细胞类型、给药方式、暴露时间及实验终点设置。总体而言，Palmatine 适合作为具有多靶点研究价值的植物源小分子，用于天然产物活性评估、作用机制解析和药物研发早期筛选；实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Palmatine is a plant-derived protoberberine isoquinoline alkaloid that inhibits IDO1 and West Nile virus NS2B-NS3 protease for inflammation, infection, neurobiology, and oncology research.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>一种植物源异喹啉生物碱，用于免疫代谢与抗感染机制研究。</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Palmatine (CAS No.: 3486-67-7) 是一种来源于多种药用植物的原小檗碱型异喹啉生物碱，常作为天然产物化学、药理学与生物活性筛选中的研究分子，用于探讨天然小分子在炎症调控、肿瘤相关生物学、神经系统损伤响应、病原微生物抑制及宿主代谢网络中的作用特征。从生物医学研究视角看，Palmatine 主要被归入具有多靶点特征的天然活性分子，其研究背景覆盖免疫代谢、感染生物学、细胞应激反应与天然药物先导发现等方向。已有体外研究表明，该分子可作用于色氨酸代谢相关靶点 IDO-1，并对病毒相关蛋白酶表现出抑制活性，整体活性水平处于微摩尔范围；同时，在不同实验体系中还被报道可影响炎症介质释放、氧化应激平衡、细胞凋亡、自噬调控以及与增殖和迁移相关的信号转导过程，提示其可能通过调节多个相互关联的分子网络发挥生物学效应。基于现有研究，Palmatine 的作用机制通常与免疫炎症通路、氧化还原稳态、线粒体功能状态以及病原体复制所依赖的关键酶活过程有关，并在部分模型中涉及对细胞因子表达、转录调控节点和代谢酶活性的干预。作为实验研究工具，该分子常用于细胞水平的机制验证、天然产物库活性筛选、靶点发现与先导化合物评价，也可用于感染或炎症相关动物模型中的药理学观察，但具体实验中采用的浓度或剂量通常取决于研究目标、模型类型、给药方式及终点指标设置。总体而言，Palmatine 适合作为生命科学与药物研发早期研究中的天然产物候选分子，用于解析多靶点调控特征及其在免疫调节、病原体相关机制研究和复杂疾病基础生物学中的应用潜力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C8812</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>849479-74-9</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Vapreotide acetate</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Vapreotide acetate (RC-160 acetate; BMY-41606 acetate) 是 神经激肽-1 (NK1) 受体拮抗剂，其 IC50 值为 330 nM。</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Vapreotide acetate (BMY-41606 acetate) is an antagonist of the neurokinin-1 (NK1) receptor (IC50: 330 nM).按剂量依赖性，Vapreotide减弱了SP（物质P）引发的HEK293-NK1R和U373MG细胞系内的细胞内钙增加和NF-κB激活。Vapreotide抑制SP诱导的IL-8和MCP-1的产生。体外试验中，Vapreotide能够抑制人MDM的HIV-1感染，此作用通过SP预处理可逆转[1]。Vapreotide在低至10(-12)-10(-14) M的浓度下显著抑制人垂体腺瘤细胞释放GH、PRL和/或α亚单位。Vapreotide抑制GH释放（IC50：0.1 pM）[2]。Vapreotide对SSTR2、-3和-5表现出中等至高亲和力，IC50分别为0.17、0.1和21 nM，而对SSTR1和-4的亲和力较低，IC50分别为200和620 nM。RC-160抑制表达SSTR2和SSTR5的CHO细胞的血清诱导增殖（EC50s：53 和 150 pM）[3]。食管胃静脉曲张破裂出血是肝硬化门脉高压的严重并发症。急性给药实验中，Vapreotide降低大鼠侧支循环的血流量，而长期给药则减缓了其发展[4]。RC-160通过皮下注射，每日每只动物100 μg剂量，可减少肿瘤体积和重量约40%。若在肿瘤发展早期开始治疗，Vapreotide能够抑制雄激素非依赖性前列腺癌的增长[5]。</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vapreotide acetate (CAS No.: 849479-74-9) is a synthetic somatostatin analog and neuropeptide-related research compound broadly used in biomedical investigations of receptor pharmacology, endocrine signaling, inflammatory response modulation, and tumor biology, and it is primarily categorized as a peptide-based signaling modulator with antagonist activity at the neurokinin-1 receptor together with appreciable affinity for selected somatostatin receptor subtypes, most notably SSTR2, SSTR3, and SSTR5. In mechanistic studies, this molecule has been shown to interfere with substance P-driven NK1 receptor signaling, thereby attenuating intracellular calcium mobilization and NF-κB activation in engineered and disease-relevant cell systems, while also reducing downstream production of inflammatory mediators such as IL-8 and MCP-1, supporting its utility for dissecting neuropeptide-dependent inflammatory and transcriptional pathways. Reported in vitro pharmacology places its activity largely in the subnanomolar to nanomolar range for several somatostatin receptor-associated endpoints and in the nanomolar range for NK1 receptor antagonism, with additional functional effects observed across endocrine and proliferation-related assay formats, indicating suitability for potency benchmarking and pathway-selective profiling in receptor-focused screening campaigns. Consistent with its receptor engagement profile, Vapreotide acetate has been applied in studies using HEK293-NK1R cells, U373MG cells, primary or differentiated human cell preparations, pituitary adenoma-derived cellular models, and receptor-transfected proliferation systems, as well as in animal-based exploratory models examining vascular, neuroendocrine, and oncology-related biology; in such settings, the concentrations or doses used in experiments typically depend on specific experimental designs and research objectives. Overall, this compound is most appropriately employed as a research tool for investigating peptide receptor crosstalk, calcium-dependent and NF-κB-linked signaling networks, cytokine and chemokine regulation, somatostatin receptor subtype biology, and mechanism-oriented drug discovery workflows in nonclinical laboratory environments.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Vapreotide acetate (CAS No.: 849479-74-9) 是一种用于生命科学研究的合成肽类分子，可归属于生长抑素类似物相关研究工具，并在神经肽信号调控、受体药理学以及疾病相关细胞反应机制研究中具有较高关注度；现有资料表明，该分子可作为神经激肽-1受体拮抗剂发挥作用，同时对多种生长抑素受体亚型表现出选择性结合特征，尤其涉及SSTR2、SSTR3和SSTR5相关通路，因此常被用于分析物质P介导的钙信号转导、NF-κB活化及下游炎症相关因子释放过程，并用于评估神经内分泌调控、受体交叉调节以及肽能信号网络的功能联系；从体外活性看，其作用水平总体处于皮摩尔至纳摩尔范围，并在部分体系中延伸至低纳摩尔水平，能够在特定细胞模型中调节激素分泌、抑制由物质P诱导的细胞内信号事件及相关趋化因子产生，也被用于观察对病毒相关细胞过程和受体依赖性应答的影响；在更广泛的研究背景下，该分子还可应用于表达特定受体的工程化细胞、原代细胞或肿瘤相关动物模型中，以考察受体激活或拮抗后的增殖、分泌、炎症与组织反应变化，并可作为药物筛选和机制验证中的对照或先导研究分子，实验中所使用的浓度或剂量通常取决于具体的实验设计、模型系统与研究目的。</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Vapreotide acetate is a synthetic somatostatin analog and neurokinin-1 receptor antagonist used to investigate receptor pharmacology, inflammatory signaling, and tumor biology.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>一种用于科研的合成肽类分子，可用于生长抑素受体与NK1受体相关机制研究。</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Vapreotide acetate (CAS No.: 849479-74-9) 是一种用于生命科学研究的合成肽类分子，亦可归属于生长抑素类似物相关研究工具，主要用于受体药理学、细胞信号转导、内分泌调控及肿瘤生物学等方向的基础研究。现有资料显示，该分子具有神经激肽-1受体拮抗活性，并对多种生长抑素受体亚型表现出选择性结合特征，尤其与SSTR2、SSTR3及SSTR5相关的信号调节研究联系较为密切，因此常被用于分析神经肽网络与生长抑素能通路之间的功能耦联关系。在机制层面，Vapreotide acetate 可干预物质P诱导的受体下游反应，抑制细胞内钙动员、NF-κB激活及部分炎症相关因子的产生，同时在生长抑素受体表达系统中影响与分泌调控及细胞增殖相关的信号过程，反映出其在神经内分泌调节、炎症信号研究以及受体介导反应解析中的实验价值。基于公开实验结果，其体外活性总体可概括为皮摩尔至纳摩尔范围，并在部分受体或功能模型中延伸至低微摩尔以下水平，提示其效应强度与受体亚型分布、细胞背景及刺激条件密切相关。该分子常用于受体结合实验、细胞功能抑制实验、分泌反应分析、炎症介质表达检测以及动物体内药效学探索，也可作为先导分子或比较分子用于神经肽受体调节剂和生长抑素相关化合物的筛选与机制评估；在实际研究中，所采用的浓度或剂量通常需结合具体模型、给药方式、观察终点及研究目的进行优化。整体而言，Vapreotide acetate 适合作为研究神经肽信号、生长抑素受体药理特征、细胞应答调控及相关疾病机制模型的实验分子，用于支持生物医学研究和药物发现早期阶段中的靶点验证、通路解析与候选化合物比较研究。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C8813</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>851199-60-5</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Linaclotide acetate </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Linaclotide acetate 是一种有效和选择性的鸟苷酸环化酶 C (guanylate cyclase C) 激动剂；开发用于研究便秘型肠易激综合症 (IBS-C) 和慢性便秘。</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Linaclotide acetate is used as an oral guanylate cyclase C agonist linaclotide; 14 amino acid peptide for the potential treatment of constipation-predominant irritable bowel syndrome and chronic idiopathic constipation.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Linaclotide acetate  (CAS No.: 851199-60-5) is a synthetic peptide research compound and acetate salt form of linaclotide, classified as a potent and selective guanylate cyclase C agonist and structurally related to the endogenous guanylin peptide family, thereby placing it within the gastrointestinal epithelial signaling and cyclic nucleotide modulation categories relevant to translational pharmacology, mucosal biology, and drug discovery research. Its primary validated target is guanylate cyclase C on the luminal surface of intestinal epithelial cells, where receptor activation stimulates intracellular cyclic GMP generation and downstream signaling linked to cystic fibrosis transmembrane conductance regulator activation, chloride and bicarbonate secretion, epithelial fluid transport, and modulation of intestinal barrier and sensory signaling pathways. In biomedical research settings, this molecule is therefore commonly used to investigate GC-C–cGMP axis biology, intestinal secretory regulation, epithelial pharmacodynamics, and peptide agonist structure-function relationships, as well as to support screening paradigms for compounds affecting cyclic nucleotide signaling or gastrointestinal physiology. Publicly available sources consistently describe linaclotide as a highly potent GC-C agonist, although compound-specific quantitative potency values are not uniformly reported for the acetate form; accordingly, its in vitro activity is most appropriately summarized as occurring in the nanomolar range based on the parent active moiety and related GC-C agonist literature rather than assigning unsupported exact values. Typical experimental applications include studies in receptor-responsive cell systems, intestinal epithelial models, ex vivo tissue assays, and animal models designed to characterize pharmacological responses to GC-C stimulation, with the concentrations or doses used in experiments typically depending on specific experimental designs and research objectives. This product is intended strictly for laboratory research use in life sciences and drug discovery, and any description of its biological activity should be interpreted within non-clinical experimental contexts only.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Linaclotide acetate  (CAS No.: 851199-60-5) 是一种合成肽类分子，为 linaclotide 的乙酸盐形式，可归属于鸟苷酸环化酶 C（guanylate cyclase C，GC-C）激动剂一类，其分子设计与内源性 guanylin/uroguanylin 肽家族在功能上相关，因而常被用于肠上皮受体信号、生理性液体转运调控以及黏膜屏障相关机制的研究；现有资料显示，该分子的核心研究价值主要集中于作为外周型 GC-C 信号探针，用于解析受体激活后细胞内环磷酸鸟苷生成、离子转运过程调节及其对肠道微环境稳态的影响。作为已知的高选择性 GC-C 激动剂，Linaclotide acetate 通过作用于肠上皮细胞表面的 GC-C 受体触发下游 cGMP 相关信号事件，并进一步关联 CFTR 介导的分泌调控、上皮跨膜转运变化以及局部感觉神经调节等生物学过程，因此在消化道上皮生物学、黏膜信号转导、肠神经轴功能研究和候选分子筛选中具有较高的工具化应用价值。基于公开研究与产品资料，其体外活性通常可概括为纳摩尔至低微摩尔范围，具体效应强度则取决于受体表达水平、模型来源、读出终点以及肽稳定性等实验条件；在应用层面，该分子常见于表达 GC-C 的细胞体系、肠道类器官、离体组织实验以及相关动物模型中，用于评估受体药理学特征、验证 cGMP 依赖性通路、比较内源性配体类似物之间的功能差异，或支持先导化合物优化与机制导向型药物发现研究，而实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的。</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linaclotide acetate is a synthetic peptide guanylate cyclase-C agonist targeting the GC-C–cGMP pathway, widely used in gastrointestinal epithelial signaling and translational pharmacology research.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>一种高选择性GC-C激动剂科研试剂，用于cGMP信号与离子转运研究。</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Linaclotide acetate  (CAS No.: 851199-60-5) 是一种合成肽类研究分子，可归属于以肠上皮膜受体为作用节点的鸟苷酸环化酶C激动剂，常用于胃肠道上皮信号转导、肠腔分泌调控、黏膜屏障生物学以及相关药理学机制研究；从生物学背景看，该分子属于以内源性肠道肽信号轴为启发而发展的功能性肽类工具分子，其主要作用靶点为鸟苷酸环化酶C，激活后可促进细胞内环磷酸鸟苷相关信号增强，并进一步影响离子转运、液体分泌及上皮稳态调节等过程，因此在研究肠上皮细胞功能、受体依赖性信号放大、分泌型表型构建及肠道微环境响应方面具有较高应用价值；现有研究背景通常将其视为选择性较强的受体激动剂，体外活性总体可概括为纳摩尔至微摩尔范围，具体效应强度则与受体表达水平、细胞类型、培养条件、检测终点以及配伍刺激因素密切相关；在实验应用上，该分子常见于受体活化验证、下游第二信使分析、离子通道或转运过程评估、肠道类器官与上皮细胞模型研究、动物机制模型中的药效学观察以及候选化合物筛选中的阳性对照或通路参照物设置，实验中所使用的浓度或剂量通常取决于具体的实验设计和研究目的；总体而言，Linaclotide acetate 适合作为解析鸟苷酸环化酶C相关信号网络、上皮分泌调控机制及肠道生理病理过程分子基础的研究工具，并可为肽类配体优化、受体药理学评估和转化前药物发现研究提供参考。</t>
         </is>
       </c>
     </row>
